--- a/cache/open_items_2026-06-11.xlsx
+++ b/cache/open_items_2026-06-11.xlsx
@@ -2702,13 +2702,13 @@
       <c r="M43" s="3" t="inlineStr"/>
       <c r="N43" s="8" t="inlineStr"/>
     </row>
-    <row r="44" ht="75" customHeight="1">
+    <row r="44" ht="105" customHeight="1">
       <c r="A44" s="2" t="n">
         <v>43</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>ENTRY-QUAL-REASON-1</t>
+          <t>OVERVIEW-VERDICT-RECON</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
@@ -2723,22 +2723,26 @@
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>Misleading entry_quality WATCH reason</t>
+          <t>Reconcile compute_final_verdict (stage) vs decisions_by_mode</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>make_decision hardcoded 'broke through resistance, wait for next base' for ALL MISSED entries — false when stock is below recent high (BFH: MISSED via &gt;2 ATR over EMA21 but 2.1% BELOW 20d high)</t>
+          <t>Two engines emit different swing score+verdict for the same name (FTNT: stage=BUY/67 vs decisions_by_mode.swing=WATCH/57). decisions_by_mode omits the catalyst-sleeve EXTENDED-entry relaxation that compute_final_verdict applies, so they disagree.</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>classify_entry_quality_detail() returns (label, live-distance reason) naming the actual trigger + honest 'still X% below resistance (not a breakout)' qualifier; threaded entry_quality_reason through make_decision + compute_decisions_by_mode</t>
+          <t>Have decisions_by_mode consume the same relaxation OR emit a diverges-from-composite flag; decide direction after the entry-quality EXTENDED/MISSED A/B validation lands. Display already fixed (overview.js binds stage).</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="5" t="inlineStr"/>
-      <c r="J44" s="5" t="inlineStr"/>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>PATH B (2026-06-09): also propagate the engine per-mode composite_score (analysis.py:8387 mode_score) into decisions_by_mode so composite-verdict.jsx + Overview can BIND a real per-mode score instead of recomputing. composite-verdict.jsx Path A shipped (binds canonical ticker.score as headline, lenses=why only); per-mode engine score is the deferred Path B. Resolve alongside the stage-vs-decisions_by_mode verdict question.</t>
+        </is>
+      </c>
       <c r="K44" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -2748,13 +2752,13 @@
       <c r="M44" s="3" t="inlineStr"/>
       <c r="N44" s="8" t="inlineStr"/>
     </row>
-    <row r="45" ht="105" customHeight="1">
+    <row r="45" ht="75" customHeight="1">
       <c r="A45" s="2" t="n">
         <v>44</v>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>OVERVIEW-VERDICT-RECON</t>
+          <t>KAIROS-TRAFFIC-LIGHT-INPUTS</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
@@ -2764,31 +2768,27 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Decision Engine</t>
+          <t>Detail Lens / Traffic Lights</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>Reconcile compute_final_verdict (stage) vs decisions_by_mode</t>
+          <t>Per-ticker risk/fundamentals inputs for lens dots</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Two engines emit different swing score+verdict for the same name (FTNT: stage=BUY/67 vs decisions_by_mode.swing=WATCH/57). decisions_by_mode omits the catalyst-sleeve EXTENDED-entry relaxation that compute_final_verdict applies, so they disagree.</t>
+          <t>Wire t.f_score · t.altman_z · t.roic · t.wacc · t.sharpe_1y · t.dd_recovery_months · t.peer_rank · t.is_held into build_data.py. _qdComputeLensStatus has cascading fallbacks (PEG → fund_score → F-score; beta → kelly → Sharpe), so dots upgrade automatically as fields land.</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>Have decisions_by_mode consume the same relaxation OR emit a diverges-from-composite flag; decide direction after the entry-quality EXTENDED/MISSED A/B validation lands. Display already fixed (overview.js binds stage).</t>
+          <t>Compute in analysis.py / portfolio.py: Piotroski F (existing data), Altman Z (existing data), ROIC vs WACC, 1y Sharpe from price history, peer_rank from cohort, is_held from portfolio_state.json.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr"/>
       <c r="I45" s="5" t="inlineStr"/>
-      <c r="J45" s="5" t="inlineStr">
-        <is>
-          <t>PATH B (2026-06-09): also propagate the engine per-mode composite_score (analysis.py:8387 mode_score) into decisions_by_mode so composite-verdict.jsx + Overview can BIND a real per-mode score instead of recomputing. composite-verdict.jsx Path A shipped (binds canonical ticker.score as headline, lenses=why only); per-mode engine score is the deferred Path B. Resolve alongside the stage-vs-decisions_by_mode verdict question.</t>
-        </is>
-      </c>
+      <c r="J45" s="5" t="inlineStr"/>
       <c r="K45" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -2798,13 +2798,13 @@
       <c r="M45" s="3" t="inlineStr"/>
       <c r="N45" s="8" t="inlineStr"/>
     </row>
-    <row r="46" ht="75" customHeight="1">
+    <row r="46" ht="60" customHeight="1">
       <c r="A46" s="2" t="n">
         <v>45</v>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>KAIROS-TRAFFIC-LIGHT-INPUTS</t>
+          <t>KAIROS-COHORT-SYMPATHY</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
@@ -2814,22 +2814,22 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Detail Lens / Traffic Lights</t>
+          <t>Earnings Lens / Cohort</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>Per-ticker risk/fundamentals inputs for lens dots</t>
+          <t>Peer cohort sympathy correlations</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>Wire t.f_score · t.altman_z · t.roic · t.wacc · t.sharpe_1y · t.dd_recovery_months · t.peer_rank · t.is_held into build_data.py. _qdComputeLensStatus has cascading fallbacks (PEG → fund_score → F-score; beta → kelly → Sharpe), so dots upgrade automatically as fields land.</t>
+          <t>Wire t.cohort_peers[].er_sympathy_corr + er_sympathy_move_1d + t.sympathy_history in build_data.py. Today: renderEarnings_Sympathy shows scaffold rows from t.cohort_peers if populated, else placeholder.</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>Compute in analysis.py / portfolio.py: Piotroski F (existing data), Altman Z (existing data), ROIC vs WACC, 1y Sharpe from price history, peer_rank from cohort, is_held from portfolio_state.json.</t>
+          <t>Compute 8-quarter rolling correlation of 1d post-print move between this name and each cohort peer's ER date. Persist to data.json under t.cohort_peers + t.sympathy_history.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
@@ -2844,13 +2844,13 @@
       <c r="M46" s="3" t="inlineStr"/>
       <c r="N46" s="8" t="inlineStr"/>
     </row>
-    <row r="47" ht="60" customHeight="1">
+    <row r="47" ht="75" customHeight="1">
       <c r="A47" s="2" t="n">
         <v>46</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>KAIROS-COHORT-SYMPATHY</t>
+          <t>PARITY-IN-APP-TRADING</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
@@ -2860,22 +2860,22 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Earnings Lens / Cohort</t>
+          <t>Execution / Live / Platform Parity</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>Peer cohort sympathy correlations</t>
+          <t>In-app Trading (broker-integrated live execution)</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Wire t.cohort_peers[].er_sympathy_corr + er_sympathy_move_1d + t.sympathy_history in build_data.py. Today: renderEarnings_Sympathy shows scaffold rows from t.cohort_peers if populated, else placeholder.</t>
+          <t>One-click BUY/SELL from the dashboard to a live Schwab/Alpaca brokerage account.</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>Compute 8-quarter rolling correlation of 1d post-print move between this name and each cohort peer's ER date. Persist to data.json under t.cohort_peers + t.sympathy_history.</t>
+          <t>OAuth-link the Schwab API (already paid stack); surface an 'Execute' button on the Trade Plan card; explicit AUTHORIZE LIVE TRADING gate per CLAUDE.md security protocol; route every order through the existing risk checks (max-loss-pct, drawdown haircut, regime gate).</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>PARITY-IN-APP-TRADING</t>
+          <t>KAIROS-LIVE-D1</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
@@ -2906,22 +2906,22 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Execution / Live / Platform Parity</t>
+          <t>Kairos / Audit Ledger</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>In-app Trading (broker-integrated live execution)</t>
+          <t>Live D1 estimate from Schwab quote during RTH</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>One-click BUY/SELL from the dashboard to a live Schwab/Alpaca brokerage account.</t>
+          <t>Replace placeholder D1 (yesterday's close-to-close) with a live Schwab-quote-based intraday estimate during market hours so the audit ledger D1 column is non-stale. Discussed and deferred as semantically muddy (D1 = next-day close, intraday quote is a forecast not a fill).</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>OAuth-link the Schwab API (already paid stack); surface an 'Execute' button on the Trade Plan card; explicit AUTHORIZE LIVE TRADING gate per CLAUDE.md security protocol; route every order through the existing risk checks (max-loss-pct, drawdown haircut, regime gate).</t>
+          <t>Add a SCHWAB_LIVE_D1=1 env flag; when ON and during RTH, compute D1_est = (live_quote - signal_entry) / signal_entry and annotate the cell with an 'est' chip. Effort ~1hr.</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr"/>
@@ -2936,13 +2936,13 @@
       <c r="M48" s="3" t="inlineStr"/>
       <c r="N48" s="8" t="inlineStr"/>
     </row>
-    <row r="49" ht="75" customHeight="1">
+    <row r="49" ht="45" customHeight="1">
       <c r="A49" s="2" t="n">
         <v>48</v>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>KAIROS-LIVE-D1</t>
+          <t>KAIROS-SCANNER-BEARS</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
@@ -2952,22 +2952,22 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Kairos / Audit Ledger</t>
+          <t>Kairos / Signal Scanner</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>Live D1 estimate from Schwab quote during RTH</t>
+          <t>Top 5 Bears panel</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Replace placeholder D1 (yesterday's close-to-close) with a live Schwab-quote-based intraday estimate during market hours so the audit ledger D1 column is non-stale. Discussed and deferred as semantically muddy (D1 = next-day close, intraday quote is a forecast not a fill).</t>
+          <t>Add a 'Top 5 Bears' panel to the Signal Scanner alongside Fresh / Momentum / Earnings / Volume — was proposed but not selected in the initial build.</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>Add a SCHWAB_LIVE_D1=1 env flag; when ON and during RTH, compute D1_est = (live_quote - signal_entry) / signal_entry and annotate the cell with an 'est' chip. Effort ~1hr.</t>
+          <t>Mirror existing 4 panels' structure; sort universe by composite bear-score desc; cap at 5; render in the Scanner grid. Effort ~10min.</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
@@ -2982,13 +2982,13 @@
       <c r="M49" s="3" t="inlineStr"/>
       <c r="N49" s="8" t="inlineStr"/>
     </row>
-    <row r="50" ht="45" customHeight="1">
+    <row r="50" ht="60" customHeight="1">
       <c r="A50" s="2" t="n">
         <v>49</v>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>KAIROS-SCANNER-BEARS</t>
+          <t>KAIROS-SCANNER-FLIPS</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
@@ -3003,17 +3003,17 @@
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>Top 5 Bears panel</t>
+          <t>Today's Flips panel</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>Add a 'Top 5 Bears' panel to the Signal Scanner alongside Fresh / Momentum / Earnings / Volume — was proposed but not selected in the initial build.</t>
+          <t>Add a 'Today's Flips' panel to the Signal Scanner — tickers whose verdict flipped vs yesterday (e.g., BUY -&gt; WATCH, WATCH -&gt; BUY, AVOID -&gt; WATCH). Proposed in the 'what else' menu, not selected.</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>Mirror existing 4 panels' structure; sort universe by composite bear-score desc; cap at 5; render in the Scanner grid. Effort ~10min.</t>
+          <t>Diff today's bundle.verdict against yesterday.verdict per ticker; surface the 5-10 most material flips. Effort ~30min.</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>KAIROS-SCANNER-FLIPS</t>
+          <t>ML-RETRAIN-FINBERT-FEATURE</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
@@ -3044,22 +3044,22 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Kairos / Signal Scanner</t>
+          <t>ML / Features (future)</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>Today's Flips panel</t>
+          <t>Add FinBERT as a GBM training feature (leak-free)</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Add a 'Today's Flips' panel to the Signal Scanner — tickers whose verdict flipped vs yesterday (e.g., BUY -&gt; WATCH, WATCH -&gt; BUY, AVOID -&gt; WATCH). Proposed in the 'what else' menu, not selected.</t>
+          <t>needs historical sentiment series — accumulate forward via cache/ml/sentiment_log.jsonl (asof-stamped); add as feature #18 + retrain once ~3-6mo of leak-free history exists</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>Diff today's bundle.verdict against yesterday.verdict per ticker; surface the 5-10 most material flips. Effort ~30min.</t>
+          <t>ml/feature_extractor + historical backfill</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr"/>
@@ -3080,7 +3080,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>ML-RETRAIN-FINBERT-FEATURE</t>
+          <t>ML-AUTOREFRESH-VALIDATE</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
@@ -3090,22 +3090,22 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>ML / Features (future)</t>
+          <t>ML / Pipeline (validate)</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>Add FinBERT as a GBM training feature (leak-free)</t>
+          <t>Validate ML auto-refresh post-scan + cached-bar reuse</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>needs historical sentiment series — accumulate forward via cache/ml/sentiment_log.jsonl (asof-stamped); add as feature #18 + retrain once ~3-6mo of leak-free history exists</t>
+          <t>ml_edge.run_after_scan=true runs ml.run_ml_edge over the fresh bundle; feature_extractor prefers data_archive (no re-fetch). Confirm end-to-end on next clean scan.</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>ml/feature_extractor + historical backfill</t>
+          <t>swing_trade ML hook + ml/feature_extractor</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
@@ -3126,7 +3126,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>ML-AUTOREFRESH-VALIDATE</t>
+          <t>KAIROS-MACRO-EVENTS</t>
         </is>
       </c>
       <c r="C53" s="10" t="inlineStr">
@@ -3136,22 +3136,22 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>ML / Pipeline (validate)</t>
+          <t>Macro Lens / Calendar</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>Validate ML auto-refresh post-scan + cached-bar reuse</t>
+          <t>14-day high-impact event window flag</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>ml_edge.run_after_scan=true runs ml.run_ml_edge over the fresh bundle; feature_extractor prefers data_archive (no re-fetch). Confirm end-to-end on next clean scan.</t>
+          <t>Wire t.next_macro_event_days = days to next FOMC/CPI/NFP/jobs. _qdComputeLensStatus reads this and downgrades macro lens to amber when event &lt;= 14d even in risk_on_trending regime.</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>swing_trade ML hook + ml/feature_extractor</t>
+          <t>Add macro_calendar fetch in data_fetcher.py (FRED/Trading Economics free tier or EODHD calendar). Persist to t.next_macro_event_days.</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr"/>
@@ -3166,13 +3166,13 @@
       <c r="M53" s="3" t="inlineStr"/>
       <c r="N53" s="8" t="inlineStr"/>
     </row>
-    <row r="54" ht="60" customHeight="1">
+    <row r="54" ht="45" customHeight="1">
       <c r="A54" s="2" t="n">
         <v>53</v>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>KAIROS-MACRO-EVENTS</t>
+          <t>CACHE-RECLAIM</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
@@ -3182,22 +3182,22 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Macro Lens / Calendar</t>
+          <t>Ops / Hygiene</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>14-day high-impact event window flag</t>
+          <t>Reclaim ~6GB cache (stray bak + edgar TTL)</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>Wire t.next_macro_event_days = days to next FOMC/CPI/NFP/jobs. _qdComputeLensStatus reads this and downgrades macro lens to amber when event &lt;= 14d even in risk_on_trending regime.</t>
+          <t>delete 300MB last_bundle.json.bak.precap_promote + add edgar companyfacts prune/TTL (6.1GB)</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>Add macro_calendar fetch in data_fetcher.py (FRED/Trading Economics free tier or EODHD calendar). Persist to t.next_macro_event_days.</t>
+          <t>cache cleanup + edgar_client TTL</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>CACHE-RECLAIM</t>
+          <t>JOBS-MOMENTUM-SNAPSHOT</t>
         </is>
       </c>
       <c r="C55" s="10" t="inlineStr">
@@ -3228,22 +3228,22 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Ops / Hygiene</t>
+          <t>Ops / Launchd</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>Reclaim ~6GB cache (stray bak + edgar TTL)</t>
+          <t>Decide momentum-snapshot job: load or disable</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>delete 300MB last_bundle.json.bak.precap_promote + add edgar companyfacts prune/TTL (6.1GB)</t>
+          <t>valid plist in repo but not currently loaded; decide launchctl bootstrap vs move to disabled/.</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>cache cleanup + edgar_client TTL</t>
+          <t>infra/launchd/com.swingtrade.momentum-snapshot.plist</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
@@ -3258,13 +3258,13 @@
       <c r="M55" s="3" t="inlineStr"/>
       <c r="N55" s="8" t="inlineStr"/>
     </row>
-    <row r="56" ht="45" customHeight="1">
+    <row r="56" ht="60" customHeight="1">
       <c r="A56" s="2" t="n">
         <v>55</v>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>JOBS-MOMENTUM-SNAPSHOT</t>
+          <t>DATA-FUTURE-OPS-TELEMETRY-6</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
@@ -3274,22 +3274,22 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Ops / Launchd</t>
+          <t>Ops / Telemetry (future)</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>Decide momentum-snapshot job: load or disable</t>
+          <t>6 ops telemetry slots — app-side instrumentation</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>valid plist in repo but not currently loaded; decide launchctl bootstrap vs move to disabled/.</t>
+          <t>6 ops telemetry slots remain unbuilt because they require app-side instrumentation: server middleware, git hooks, scan-time emitters, executor probes, sub-tab render timings, fetch-latency probes.</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>infra/launchd/com.swingtrade.momentum-snapshot.plist</t>
+          <t>Build a shared emitter (lib/telemetry.py) writing to a telemetry SQLite; instrument incrementally — server middleware first, then scan emitters; surface in System Status sub-tab.</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>DATA-FUTURE-OPS-TELEMETRY-6</t>
+          <t>SCALE-4</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
@@ -3320,22 +3320,22 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Ops / Telemetry (future)</t>
+          <t>Ops · 500-user</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>6 ops telemetry slots — app-side instrumentation</t>
+          <t>Scan reliability so Home is not sparse</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>6 ops telemetry slots remain unbuilt because they require app-side instrumentation: server middleware, git hooks, scan-time emitters, executor probes, sub-tab render timings, fetch-latency probes.</t>
+          <t>When the daily scan is empty (EODHD quota outage), Home shows honest-empty sections + stale-badged regime; users landing mid-outage see little actionable content</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>Build a shared emitter (lib/telemetry.py) writing to a telemetry SQLite; instrument incrementally — server middleware first, then scan emitters; surface in System Status sub-tab.</t>
+          <t>Ensure morning scan runs reliably + quota headroom; keep STALE badge UX; consider serving last-good bundle with clear age</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr"/>
@@ -3350,13 +3350,13 @@
       <c r="M57" s="3" t="inlineStr"/>
       <c r="N57" s="8" t="inlineStr"/>
     </row>
-    <row r="58" ht="60" customHeight="1">
+    <row r="58" ht="75" customHeight="1">
       <c r="A58" s="2" t="n">
         <v>57</v>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>SCALE-4</t>
+          <t>OV-INVEST-STRUCT</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
@@ -3366,22 +3366,22 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Ops · 500-user</t>
+          <t>Overview / Target Engine</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>Scan reliability so Home is not sparse</t>
+          <t>Real structural invest targets (kill analyst-PT stub)</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>When the daily scan is empty (EODHD quota outage), Home shows honest-empty sections + stale-badged regime; users landing mid-outage see little actionable content</t>
+          <t>Invest-mode targets fall back to analyst 12mo PT (invest_stub) for low-vol names (e.g. AAPL) when no structural level qualifies in the invest R-band off the wider stop -&gt; near T1, poor R:R. Per-mode stop scaling fix (2026-06-08) made invest coherent for higher-vol names (NVDA stub=False) but low-vol names still stub.</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>Ensure morning scan runs reliably + quota headroom; keep STALE badge UX; consider serving last-good bundle with clear age</t>
+          <t>Wire multi-year structural levels (monthly/yearly swing highs, weekly Fib ext) into the invest candidate set so the invest R-band is populated without the analyst-PT fallback; raise invest max_reach_atr to match a 1-5yr horizon.</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
@@ -3396,13 +3396,13 @@
       <c r="M58" s="3" t="inlineStr"/>
       <c r="N58" s="8" t="inlineStr"/>
     </row>
-    <row r="59" ht="75" customHeight="1">
+    <row r="59" ht="60" customHeight="1">
       <c r="A59" s="2" t="n">
         <v>58</v>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>OV-INVEST-STRUCT</t>
+          <t>SCALE-3</t>
         </is>
       </c>
       <c r="C59" s="10" t="inlineStr">
@@ -3412,22 +3412,22 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Overview / Target Engine</t>
+          <t>Portfolio · 500-user</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>Real structural invest targets (kill analyst-PT stub)</t>
+          <t>Per-user portfolio vs shared automated book</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>Invest-mode targets fall back to analyst 12mo PT (invest_stub) for low-vol names (e.g. AAPL) when no structural level qualifies in the invest R-band off the wider stop -&gt; near T1, poor R:R. Per-mode stop scaling fix (2026-06-08) made invest coherent for higher-vol names (NVDA stub=False) but low-vol names still stub.</t>
+          <t>Home AUTOMATED BOOK is the single shared Alpaca-paper auto-trade account; every viewer sees identical positions; no per-user book (NAV is per-user, positions are not)</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>Wire multi-year structural levels (monthly/yearly swing highs, weekly Fib ext) into the invest candidate set so the invest R-band is populated without the analyst-PT fallback; raise invest max_reach_atr to match a 1-5yr horizon.</t>
+          <t>Decide: keep as shared model/track-record book by design, OR add a per-user position store keyed to UserPrefs auth id</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr"/>
@@ -3442,13 +3442,13 @@
       <c r="M59" s="3" t="inlineStr"/>
       <c r="N59" s="8" t="inlineStr"/>
     </row>
-    <row r="60" ht="60" customHeight="1">
+    <row r="60" ht="90" customHeight="1">
       <c r="A60" s="2" t="n">
         <v>59</v>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>SCALE-3</t>
+          <t>QUANT-HMM-FF-LGBM-ROADMAP</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
@@ -3458,22 +3458,22 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Portfolio · 500-user</t>
+          <t>Quant / Modeling Roadmap</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>Per-user portfolio vs shared automated book</t>
+          <t>HMM regime / Fama-French / LightGBM swap (status unclear)</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>Home AUTOMATED BOOK is the single shared Alpaca-paper auto-trade account; every viewer sees identical positions; no per-user book (NAV is per-user, positions are not)</t>
+          <t>Roadmap items pasted as a status table — clarification pending whether user wants execution or just context tracking. Three potential upgrades: (a) HMM-based regime classifier replacing the rule-based 4-regime model, (b) Fama-French factor exposure analysis on closed trades, (c) LightGBM swap-in for HistGradientBoosting in ml/train_historical.py. Each 1-3 days.</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>Decide: keep as shared model/track-record book by design, OR add a per-user position store keyed to UserPrefs auth id</t>
+          <t>Confirm intent before executing. If go: HMM first (decouples regime classifier from heuristics, principle #18), then Fama-French attribution (per-strategy factor exposure), then LightGBM swap (likely-marginal accuracy gain vs current HistGB). Each upgrade gated by Wilson-LB validation vs current baseline.</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr"/>
@@ -3488,13 +3488,13 @@
       <c r="M60" s="3" t="inlineStr"/>
       <c r="N60" s="8" t="inlineStr"/>
     </row>
-    <row r="61" ht="90" customHeight="1">
+    <row r="61" ht="60" customHeight="1">
       <c r="A61" s="2" t="n">
         <v>60</v>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>QUANT-HMM-FF-LGBM-ROADMAP</t>
+          <t>PARITY-SMART-RISK-LEVELS</t>
         </is>
       </c>
       <c r="C61" s="10" t="inlineStr">
@@ -3504,22 +3504,22 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Quant / Modeling Roadmap</t>
+          <t>Risk / Targets / Platform Parity</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>HMM regime / Fama-French / LightGBM swap (status unclear)</t>
+          <t>Smart Risk Levels (auto stop + T1/T2)</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>Roadmap items pasted as a status table — clarification pending whether user wants execution or just context tracking. Three potential upgrades: (a) HMM-based regime classifier replacing the rule-based 4-regime model, (b) Fama-French factor exposure analysis on closed trades, (c) LightGBM swap-in for HistGradientBoosting in ml/train_historical.py. Each 1-3 days.</t>
+          <t>Auto-place stop / T1 / T2 dots on the chart with confluence reasoning (HVN, AVWAP, fractal, ATR, Fib). Already computed by the structural target engine but not surfaced on the new Chart sub-tab.</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Confirm intent before executing. If go: HMM first (decouples regime classifier from heuristics, principle #18), then Fama-French attribution (per-strategy factor exposure), then LightGBM swap (likely-marginal accuracy gain vs current HistGB). Each upgrade gated by Wilson-LB validation vs current baseline.</t>
+          <t>Read cache/target_engine/{TICKER}_{MODE}.json and overlay the levels on the chart canvas with hover tooltips citing the confluence factors; gated by use_structural_targets flag (M2.5 cutover).</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr"/>
@@ -3540,7 +3540,7 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>PARITY-SMART-RISK-LEVELS</t>
+          <t>KAIROS-L2-BOOK</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
@@ -3550,22 +3550,22 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Risk / Targets / Platform Parity</t>
+          <t>Risk Lens / Execution</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>Smart Risk Levels (auto stop + T1/T2)</t>
+          <t>L2 bid/ask depth at price levels</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>Auto-place stop / T1 / T2 dots on the chart with confluence reasoning (HVN, AVWAP, fractal, ATR, Fib). Already computed by the structural target engine but not surfaced on the new Chart sub-tab.</t>
+          <t>Wire t.l2_book from Schwab streaming API → render in renderRisk_LiquidityLadder. Today: ADV-derived size tiers shown as scaffold. Schwab streaming requires WebSocket session — see schwab_client.py.</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>Read cache/target_engine/{TICKER}_{MODE}.json and overlay the levels on the chart canvas with hover tooltips citing the confluence factors; gated by use_structural_targets flag (M2.5 cutover).</t>
+          <t>Subscribe to Schwab Level-II quote stream; persist top-of-book snapshot into t.l2_book = {bid:[{px,size}], ask:[{px,size}]}. Frontend already reads these fields if present.</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr"/>
@@ -3580,13 +3580,13 @@
       <c r="M62" s="3" t="inlineStr"/>
       <c r="N62" s="8" t="inlineStr"/>
     </row>
-    <row r="63" ht="60" customHeight="1">
+    <row r="63" ht="75" customHeight="1">
       <c r="A63" s="2" t="n">
         <v>62</v>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>KAIROS-L2-BOOK</t>
+          <t>TECH-MOM-DIVERGENCE-PENALTY</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
@@ -3596,22 +3596,22 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Risk Lens / Execution</t>
+          <t>Scoring</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>L2 bid/ask depth at price levels</t>
+          <t>Momentum-divergence penalty for Technicals pillar (STAGED)</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>Wire t.l2_book from Schwab streaming API → render in renderRisk_LiquidityLadder. Today: ADV-derived size tiers shown as scaffold. Schwab streaming requires WebSocket session — see schwab_client.py.</t>
+          <t>Strong-RS/trend names whose fast momentum rolled over (MACD death cross + light volume) score too high on Technicals because RS/trend mask the weak momentum sub-score (CTS: 63% with a death cross). Staged penalty docks the pillar (-3) when mom&lt;=2/5 AND rvol&lt;1.0 AND death_cross. Default OFF.</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>Subscribe to Schwab Level-II quote stream; persist top-of-book snapshot into t.l2_book = {bid:[{px,size}], ask:[{px,size}]}. Frontend already reads these fields if present.</t>
+          <t>analysis.score_technicals + scoring.momentum_divergence_penalty config flag. ACTIVATION GATED on swing-WR/PF A/B backtest (principle 7) — do not flip _enabled without it. CTS 63%-&gt;55% when on.</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr"/>
@@ -3626,13 +3626,13 @@
       <c r="M63" s="3" t="inlineStr"/>
       <c r="N63" s="8" t="inlineStr"/>
     </row>
-    <row r="64" ht="75" customHeight="1">
+    <row r="64" ht="60" customHeight="1">
       <c r="A64" s="2" t="n">
         <v>63</v>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>TECH-MOM-DIVERGENCE-PENALTY</t>
+          <t>PARITY-AI-SIGNALS-V1</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
@@ -3642,22 +3642,22 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Scoring</t>
+          <t>Signals / Platform Parity</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>Momentum-divergence penalty for Technicals pillar (STAGED)</t>
+          <t>1st-Gen AI Signals</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>Strong-RS/trend names whose fast momentum rolled over (MACD death cross + light volume) score too high on Technicals because RS/trend mask the weak momentum sub-score (CTS: 63% with a death cross). Staged penalty docks the pillar (-3) when mom&lt;=2/5 AND rvol&lt;1.0 AND death_cross. Default OFF.</t>
+          <t>Surface a baseline AI BUY/SELL signal stream on the chart as quick-glance arrows/dots — the competitor-platform feature (TrendSpider, Trade Ideas) users expect to see at a glance, separate from the full ML Edge sub-tab.</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>analysis.score_technicals + scoring.momentum_divergence_penalty config flag. ACTIVATION GATED on swing-WR/PF A/B backtest (principle 7) — do not flip _enabled without it. CTS 63%-&gt;55% when on.</t>
+          <t>Reuse ML Edge dir-head + cone outputs but render as 1-bar arrows/markers on the new Chart sub-tab; isolate from the 10-section Technicals view; respect cache/ml_edge_predictions.json freshness.</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr"/>
@@ -3672,13 +3672,13 @@
       <c r="M64" s="3" t="inlineStr"/>
       <c r="N64" s="8" t="inlineStr"/>
     </row>
-    <row r="65" ht="60" customHeight="1">
+    <row r="65" ht="45" customHeight="1">
       <c r="A65" s="2" t="n">
         <v>64</v>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>PARITY-AI-SIGNALS-V1</t>
+          <t>TEST-AB-PAPER</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
@@ -3688,22 +3688,22 @@
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Signals / Platform Parity</t>
+          <t>Testing / Validation (Tier 2)</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>1st-Gen AI Signals</t>
+          <t>A/B Paper Split — live comparison</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>Surface a baseline AI BUY/SELL signal stream on the chart as quick-glance arrows/dots — the competitor-platform feature (TrendSpider, Trade Ideas) users expect to see at a glance, separate from the full ML Edge sub-tab.</t>
+          <t>Run config A on half the paper portfolio and config B on the other half; real-time comparison of WR / PF / equity divergence over 30-60d window.</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>Reuse ML Edge dir-head + cone outputs but render as 1-bar arrows/markers on the new Chart sub-tab; isolate from the 10-section Technicals view; respect cache/ml_edge_predictions.json freshness.</t>
+          <t>Extend executor.py to accept --variant flag; persist per-variant portfolio state; cross-section panel in System Status sub-tab. Effort 3-4hr.</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr"/>
@@ -3718,13 +3718,13 @@
       <c r="M65" s="3" t="inlineStr"/>
       <c r="N65" s="8" t="inlineStr"/>
     </row>
-    <row r="66" ht="45" customHeight="1">
+    <row r="66" ht="60" customHeight="1">
       <c r="A66" s="2" t="n">
         <v>65</v>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>TEST-AB-PAPER</t>
+          <t>TEST-BENCHMARK-SPY</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
@@ -3739,17 +3739,17 @@
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>A/B Paper Split — live comparison</t>
+          <t>Benchmark vs SPY — alpha / beta / IR</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>Run config A on half the paper portfolio and config B on the other half; real-time comparison of WR / PF / equity divergence over 30-60d window.</t>
+          <t>Compute strategy alpha, beta, information ratio vs SPY benchmark. Standard performance attribution; turns 'we made +X%' into 'we made +Y% over SPY at lower drawdown'.</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>Extend executor.py to accept --variant flag; persist per-variant portfolio state; cross-section panel in System Status sub-tab. Effort 3-4hr.</t>
+          <t>Daily portfolio_value series joined to SPY adjusted-close; regress daily returns -&gt; SPY returns for beta + alpha; IR = (mean excess return) / (std excess return); render in System Status. Effort ~1hr.</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr"/>
@@ -3770,7 +3770,7 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>TEST-BENCHMARK-SPY</t>
+          <t>TEST-DD-DIST</t>
         </is>
       </c>
       <c r="C67" s="10" t="inlineStr">
@@ -3785,17 +3785,17 @@
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>Benchmark vs SPY — alpha / beta / IR</t>
+          <t>Drawdown Distribution Simulator</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>Compute strategy alpha, beta, information ratio vs SPY benchmark. Standard performance attribution; turns 'we made +X%' into 'we made +Y% over SPY at lower drawdown'.</t>
+          <t>Bootstrap 1000 portfolio paths from closed-trade distribution; measure tail-drawdown probability at p95/p99; supports principle #9 (drawdown asymmetry — losing 50% requires +100% to recover).</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>Daily portfolio_value series joined to SPY adjusted-close; regress daily returns -&gt; SPY returns for beta + alpha; IR = (mean excess return) / (std excess return); render in System Status. Effort ~1hr.</t>
+          <t>Resample trade sequence with replacement; build equity curves; compute max-DD per path; histogram + tail percentiles; feed into position-sizing math. Effort 2-3hr.</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr"/>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>TEST-DD-DIST</t>
+          <t>TEST-SENSITIVITY</t>
         </is>
       </c>
       <c r="C68" s="10" t="inlineStr">
@@ -3831,17 +3831,17 @@
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>Drawdown Distribution Simulator</t>
+          <t>Sensitivity / Robustness Test</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>Bootstrap 1000 portfolio paths from closed-trade distribution; measure tail-drawdown probability at p95/p99; supports principle #9 (drawdown asymmetry — losing 50% requires +100% to recover).</t>
+          <t>Perturb each config parameter +/-20% (score floors, stop ATR mult, R:R floor, regime thresholds) and check whether the strategy still passes the gate. Finds overfit knobs that only work at one exact value.</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>Resample trade sequence with replacement; build equity curves; compute max-DD per path; histogram + tail percentiles; feed into position-sizing math. Effort 2-3hr.</t>
+          <t>Grid-walk key config thresholds; re-run backtest at each point; build sensitivity heatmap (param vs PF); flag any knob whose +/-20% perturbation collapses PF &gt;50%. Effort ~2hr.</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr"/>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>TEST-SENSITIVITY</t>
+          <t>TEST-SLIPPAGE-STRESS</t>
         </is>
       </c>
       <c r="C69" s="10" t="inlineStr">
@@ -3877,17 +3877,17 @@
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>Sensitivity / Robustness Test</t>
+          <t>Slippage Stress Test</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>Perturb each config parameter +/-20% (score floors, stop ATR mult, R:R floor, regime thresholds) and check whether the strategy still passes the gate. Finds overfit knobs that only work at one exact value.</t>
+          <t>Double the slippage assumption (ATR/ADV-scaled model from audit #5) and recompute backtest stats. Validates fragile execution dependence per principle #19 (slippage realism).</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>Grid-walk key config thresholds; re-run backtest at each point; build sensitivity heatmap (param vs PF); flag any knob whose +/-20% perturbation collapses PF &gt;50%. Effort ~2hr.</t>
+          <t>Re-run backtest with SLIPPAGE_MULT=2.0; compare WR/PF/Sharpe deltas; if a strategy collapses at 2x slippage it is execution-fragile and should be down-sized. Effort ~1hr.</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr"/>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>TEST-SLIPPAGE-STRESS</t>
+          <t>TEST-CORRELATED-FAILURE</t>
         </is>
       </c>
       <c r="C70" s="10" t="inlineStr">
@@ -3918,22 +3918,22 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Testing / Validation (Tier 2)</t>
+          <t>Testing / Validation (Tier 3)</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>Slippage Stress Test</t>
+          <t>Correlated-Failure — what if EODHD goes down 24h?</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>Double the slippage assumption (ATR/ADV-scaled model from audit #5) and recompute backtest stats. Validates fragile execution dependence per principle #19 (slippage realism).</t>
+          <t>Simulate the impact of the sole data provider (EODHD) being unavailable for 24-48h during market hours. What happens to (a) the scan, (b) live exec, (c) the dashboard?</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>Re-run backtest with SLIPPAGE_MULT=2.0; compare WR/PF/Sharpe deltas; if a strategy collapses at 2x slippage it is execution-fragile and should be down-sized. Effort ~1hr.</t>
+          <t>Inject EODHD error responses in a paper environment; observe failure modes (fallback to last-known cache vs hard error vs degraded scan); document recovery RTO; tighten any silent-fail paths discovered. Effort 2-3hr.</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr"/>
@@ -3948,13 +3948,13 @@
       <c r="M70" s="3" t="inlineStr"/>
       <c r="N70" s="8" t="inlineStr"/>
     </row>
-    <row r="71" ht="60" customHeight="1">
+    <row r="71" ht="45" customHeight="1">
       <c r="A71" s="2" t="n">
         <v>70</v>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>TEST-CORRELATED-FAILURE</t>
+          <t>TEST-CRASH-REPLAY</t>
         </is>
       </c>
       <c r="C71" s="10" t="inlineStr">
@@ -3969,17 +3969,17 @@
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>Correlated-Failure — what if EODHD goes down 24h?</t>
+          <t>Crash Replay — 2008/2020/2022 stress</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>Simulate the impact of the sole data provider (EODHD) being unavailable for 24-48h during market hours. What happens to (a) the scan, (b) live exec, (c) the dashboard?</t>
+          <t>Apply current portfolio composition to historical crash days (2008 GFC, 2020 COVID, 2022 rate-shock); measure realized drawdown + recovery time per scenario.</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>Inject EODHD error responses in a paper environment; observe failure modes (fallback to last-known cache vs hard error vs degraded scan); document recovery RTO; tighten any silent-fail paths discovered. Effort 2-3hr.</t>
+          <t>Snapshot today's positions; price-replay against historical daily OHLC from those windows; report per-crisis max-DD and time-to-recovery. Effort 2-3hr.</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr"/>
@@ -3994,13 +3994,13 @@
       <c r="M71" s="3" t="inlineStr"/>
       <c r="N71" s="8" t="inlineStr"/>
     </row>
-    <row r="72" ht="45" customHeight="1">
+    <row r="72" ht="60" customHeight="1">
       <c r="A72" s="2" t="n">
         <v>71</v>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>TEST-CRASH-REPLAY</t>
+          <t>TEST-KELLY-SIM</t>
         </is>
       </c>
       <c r="C72" s="10" t="inlineStr">
@@ -4015,17 +4015,17 @@
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>Crash Replay — 2008/2020/2022 stress</t>
+          <t>Half-Kelly vs Full-Kelly sizing simulation</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>Apply current portfolio composition to historical crash days (2008 GFC, 2020 COVID, 2022 rate-shock); measure realized drawdown + recovery time per scenario.</t>
+          <t>Visualize portfolio growth under Half-Kelly (current default) vs Full-Kelly vs Quarter-Kelly sizing rules; quantifies the volatility-vs-CAGR tradeoff that principle #9 codifies.</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>Snapshot today's positions; price-replay against historical daily OHLC from those windows; report per-crisis max-DD and time-to-recovery. Effort 2-3hr.</t>
+          <t>Bootstrap N portfolio paths under each Kelly fraction; chart median equity curve + percentile fans; surface terminal-wealth distribution. Effort ~2hr.</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr"/>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>TEST-KELLY-SIM</t>
+          <t>TEST-SLIPPAGE-ATTR</t>
         </is>
       </c>
       <c r="C73" s="10" t="inlineStr">
@@ -4061,17 +4061,17 @@
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>Half-Kelly vs Full-Kelly sizing simulation</t>
+          <t>Slippage Attribution — signal PnL vs realized PnL gap</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>Visualize portfolio growth under Half-Kelly (current default) vs Full-Kelly vs Quarter-Kelly sizing rules; quantifies the volatility-vs-CAGR tradeoff that principle #9 codifies.</t>
+          <t>For each closed trade, compute the gap between the model's predicted entry/exit and the actual fill price. Aggregate by setup/ticker/regime to find where slippage eats edge.</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>Bootstrap N portfolio paths under each Kelly fraction; chart median equity curve + percentile fans; surface terminal-wealth distribution. Effort ~2hr.</t>
+          <t>Read signal_log entries (which has the signal price) and join to paper_fills.json (which has the realized price); compute slippage_bp per trade; group + percentile. Effort ~2hr.</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr"/>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>TEST-SLIPPAGE-ATTR</t>
+          <t>TEST-TAX-AWARE</t>
         </is>
       </c>
       <c r="C74" s="10" t="inlineStr">
@@ -4107,17 +4107,17 @@
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>Slippage Attribution — signal PnL vs realized PnL gap</t>
+          <t>Tax-Aware Backtest — short-term cap-gains haircut</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>For each closed trade, compute the gap between the model's predicted entry/exit and the actual fill price. Aggregate by setup/ticker/regime to find where slippage eats edge.</t>
+          <t>Apply short-term capital-gains tax (35-40% on gains held &lt;1yr) to backtest PnL. Real after-tax return for a US retail account is materially lower than gross.</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>Read signal_log entries (which has the signal price) and join to paper_fills.json (which has the realized price); compute slippage_bp per trade; group + percentile. Effort ~2hr.</t>
+          <t>Add post_tax_pnl column to backtest output; apply 35% haircut to short-term gains (&gt;0 PnL, held &lt;365d) and 15% to long-term; report Sharpe / total-return pre vs post tax. Effort ~2hr.</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr"/>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>TEST-TAX-AWARE</t>
+          <t>WAIT-CALIB-DRIFT-SPARK</t>
         </is>
       </c>
       <c r="C75" s="10" t="inlineStr">
@@ -4148,22 +4148,22 @@
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>Testing / Validation (Tier 3)</t>
+          <t>Time-Dependent / Calibration</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>Tax-Aware Backtest — short-term cap-gains haircut</t>
+          <t>Calibration drift sparkline populates</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>Apply short-term capital-gains tax (35-40% on gains held &lt;1yr) to backtest PnL. Real after-tax return for a US retail account is materially lower than gross.</t>
+          <t>The calibration-drift sparkline in the ML Edge sub-tab needs multiple training cycles to populate (weeks). Each morning scan retrains and appends a calibration row; the sparkline reads from that history table.</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>Add post_tax_pnl column to backtest output; apply 35% haircut to short-term gains (&gt;0 PnL, held &lt;365d) and 15% to long-term; report Sharpe / total-return pre vs post tax. Effort ~2hr.</t>
+          <t>Passive wait. Re-check after 4-6 weekly retrain cycles. If still empty, verify ml.train_historical writes to cache/ml/calibration_history.jsonl on each run.</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr"/>
@@ -4178,13 +4178,13 @@
       <c r="M75" s="3" t="inlineStr"/>
       <c r="N75" s="8" t="inlineStr"/>
     </row>
-    <row r="76" ht="60" customHeight="1">
+    <row r="76" ht="45" customHeight="1">
       <c r="A76" s="2" t="n">
         <v>75</v>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>WAIT-CALIB-DRIFT-SPARK</t>
+          <t>WAIT-DRIFT-SNAPSHOTS</t>
         </is>
       </c>
       <c r="C76" s="10" t="inlineStr">
@@ -4194,22 +4194,22 @@
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Time-Dependent / Calibration</t>
+          <t>Time-Dependent / Drift Tracking</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>Calibration drift sparkline populates</t>
+          <t>Diff vs yesterday + 30-day drift populate</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>The calibration-drift sparkline in the ML Edge sub-tab needs multiple training cycles to populate (weeks). Each morning scan retrains and appends a calibration row; the sparkline reads from that history table.</t>
+          <t>The 'diff vs yesterday' + 30-day drift columns need 2+ daily snapshots stored. Starts populating tomorrow's scan.</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>Passive wait. Re-check after 4-6 weekly retrain cycles. If still empty, verify ml.train_historical writes to cache/ml/calibration_history.jsonl on each run.</t>
+          <t>Passive wait; first populated values appear in the next morning's scan output. Verify the snapshot persister wrote a row today.</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr"/>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>WAIT-DRIFT-SNAPSHOTS</t>
+          <t>WAIT-ML-PICKS-RESOLVE</t>
         </is>
       </c>
       <c r="C77" s="10" t="inlineStr">
@@ -4240,22 +4240,22 @@
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>Time-Dependent / Drift Tracking</t>
+          <t>Time-Dependent / Picks History</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>Diff vs yesterday + 30-day drift populate</t>
+          <t>Picks-history outcome resolution (resolve_ml_picks.py)</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>The 'diff vs yesterday' + 30-day drift columns need 2+ daily snapshots stored. Starts populating tomorrow's scan.</t>
+          <t>resolve_ml_picks.py needs 5 trading days from each pick to resolve outcomes. First AI Edge batch (picks from ~2026-05-18) resolves around 2026-05-23.</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>Passive wait; first populated values appear in the next morning's scan output. Verify the snapshot persister wrote a row today.</t>
+          <t>Passive wait. Re-check on 2026-05-23; verify resolve_ml_picks.py runs in run_daily_scan.sh and populates picks_history.json outcome columns.</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr"/>
@@ -4270,13 +4270,13 @@
       <c r="M77" s="3" t="inlineStr"/>
       <c r="N77" s="8" t="inlineStr"/>
     </row>
-    <row r="78" ht="45" customHeight="1">
+    <row r="78" ht="60" customHeight="1">
       <c r="A78" s="2" t="n">
         <v>77</v>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>WAIT-ML-PICKS-RESOLVE</t>
+          <t>WAIT-SURVIVORSHIP-DECAY</t>
         </is>
       </c>
       <c r="C78" s="10" t="inlineStr">
@@ -4286,22 +4286,22 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>Time-Dependent / Picks History</t>
+          <t>Time-Dependent / Survivorship Haircut</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>Picks-history outcome resolution (resolve_ml_picks.py)</t>
+          <t>Survivorship haircut shrinking 3pp -&gt; 0.5pp</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>resolve_ml_picks.py needs 5 trading days from each pick to resolve outcomes. First AI Edge batch (picks from ~2026-05-18) resolves around 2026-05-23.</t>
+          <t>The -3pp WR survivorship haircut should shrink as monthly S&amp;P 500 / R1000 membership snapshots accumulate (Wikipedia revision history). Once 24+ months of snapshots are stored, the haircut can fade toward 0.5pp.</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>Passive wait. Re-check on 2026-05-23; verify resolve_ml_picks.py runs in run_daily_scan.sh and populates picks_history.json outcome columns.</t>
+          <t>Passive wait — currently only current-membership data. Re-evaluate annually. Until then keep -3pp haircut per CLAUDE.md principle #6.</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr"/>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>WAIT-SURVIVORSHIP-DECAY</t>
+          <t>WAIT-WF-EQUITY-REAL</t>
         </is>
       </c>
       <c r="C79" s="10" t="inlineStr">
@@ -4332,22 +4332,22 @@
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>Time-Dependent / Survivorship Haircut</t>
+          <t>Time-Dependent / Walk-Forward</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>Survivorship haircut shrinking 3pp -&gt; 0.5pp</t>
+          <t>Walk-forward equity curve switches to REAL track</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>The -3pp WR survivorship haircut should shrink as monthly S&amp;P 500 / R1000 membership snapshots accumulate (Wikipedia revision history). Once 24+ months of snapshots are stored, the haircut can fade toward 0.5pp.</t>
+          <t>Currently the equity curve renders backtest-derived returns. Switches to REAL track once 5+ resolved AI Edge picks are available — first batch resolves ~2026-05-23, so REAL curve activates ~2026-05-24.</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Passive wait — currently only current-membership data. Re-evaluate annually. Until then keep -3pp haircut per CLAUDE.md principle #6.</t>
+          <t>Passive wait. Re-check on 2026-05-24; verify the equity curve flips from BACKTEST badge to REAL badge once n_resolved &gt;= 5.</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr"/>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>WAIT-WF-EQUITY-REAL</t>
+          <t>PARITY-10-CHARTS-GRID</t>
         </is>
       </c>
       <c r="C80" s="10" t="inlineStr">
@@ -4378,22 +4378,22 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>Time-Dependent / Walk-Forward</t>
+          <t>UI / Layout / Platform Parity</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>Walk-forward equity curve switches to REAL track</t>
+          <t>10-chart multi-pane grid</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>Currently the equity curve renders backtest-derived returns. Switches to REAL track once 5+ resolved AI Edge picks are available — first batch resolves ~2026-05-23, so REAL curve activates ~2026-05-24.</t>
+          <t>Display up to 10 ticker charts side-by-side in a configurable grid (2x5, 3x4, etc.) for at-a-glance correlation/leadership reads — what TrendSpider and Trade Ideas users default to.</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Passive wait. Re-check on 2026-05-24; verify the equity curve flips from BACKTEST badge to REAL badge once n_resolved &gt;= 5.</t>
+          <t>New 'Grid' workspace in kairos that renders N lightweight-chart canvases; ticker list drag-droppable; persists ticker set per layout.</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr"/>
@@ -4414,7 +4414,7 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>PARITY-10-CHARTS-GRID</t>
+          <t>PARITY-CUSTOM-LAYOUTS</t>
         </is>
       </c>
       <c r="C81" s="10" t="inlineStr">
@@ -4429,17 +4429,17 @@
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>10-chart multi-pane grid</t>
+          <t>Customizable Layouts (save/load workspace presets)</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>Display up to 10 ticker charts side-by-side in a configurable grid (2x5, 3x4, etc.) for at-a-glance correlation/leadership reads — what TrendSpider and Trade Ideas users default to.</t>
+          <t>User drags/resizes panels in the kairos workspace and saves the arrangement as a named preset (Day-Trade view / Swing view / Research view) and switches between them.</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>New 'Grid' workspace in kairos that renders N lightweight-chart canvases; ticker list drag-droppable; persists ticker set per layout.</t>
+          <t>Persist layout JSON in cache/user_layouts.json (per-user once auth lands); sidebar dropdown to switch; default presets shipped (Swing / Position / Research).</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr"/>
@@ -4454,13 +4454,13 @@
       <c r="M81" s="3" t="inlineStr"/>
       <c r="N81" s="8" t="inlineStr"/>
     </row>
-    <row r="82" ht="60" customHeight="1">
+    <row r="82" ht="75" customHeight="1">
       <c r="A82" s="2" t="n">
         <v>81</v>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>PARITY-CUSTOM-LAYOUTS</t>
+          <t>STRUCT-TARGETS-PHASE2</t>
         </is>
       </c>
       <c r="C82" s="10" t="inlineStr">
@@ -4470,35 +4470,51 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>UI / Layout / Platform Parity</t>
+          <t>Strategy / Targets</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>Customizable Layouts (save/load workspace presets)</t>
+          <t>Structural targets Phase 2 — engine uses them as T1/T2</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>User drags/resizes panels in the kairos workspace and saves the arrangement as a named preset (Day-Trade view / Swing view / Research view) and switches between them.</t>
+          <t>Phase 1 (shipped 2026-05-10): structural target sources (fractal, fib, EW Wave-3) display on Plan tab as informational. Phase 2: actually use these as T1/T2 instead of ATR-multiple targets. Needs per-source x regime evidence (&gt;=30 trades each).</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>Persist layout JSON in cache/user_layouts.json (per-user once auth lands); sidebar dropdown to switch; default presets shipped (Swing / Position / Research).</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr"/>
-      <c r="I82" s="5" t="inlineStr"/>
-      <c r="J82" s="5" t="inlineStr"/>
-      <c r="K82" s="7" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+          <t>Add config flag target_source = atr_multiple | structural. When structural, T1 = nearest_above with R:R&gt;=3 from {fractal_high, fib_127, EW_T1}. Fall back to ATR if R:R floor not met. Backtest side-by-side with current ATR-multiple.</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>1 day + backtest</t>
+        </is>
+      </c>
+      <c r="I82" s="5" t="inlineStr">
+        <is>
+          <t>High win potential, medium risk</t>
+        </is>
+      </c>
+      <c r="J82" s="5" t="inlineStr">
+        <is>
+          <t>Awaiting evidence. Phase 1 currently just populates display field; need 3-4 weeks of trade data with target_sources captured before Phase 2 is decidable.</t>
+        </is>
+      </c>
+      <c r="K82" s="11" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr"/>
       <c r="M82" s="3" t="inlineStr"/>
-      <c r="N82" s="8" t="inlineStr"/>
+      <c r="N82" s="8" t="inlineStr">
+        <is>
+          <t>Run backtest with target_source=structural and target_source=atr_multiple on same window. Compare PF/WR/avg_win.</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="75" customHeight="1">
       <c r="A83" s="2" t="n">
@@ -4506,69 +4522,77 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>STRUCT-TARGETS-PHASE2</t>
-        </is>
-      </c>
-      <c r="C83" s="10" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>K6</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Targets</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>Structural targets Phase 2 — engine uses them as T1/T2</t>
+          <t>Single canonical trade plan object — every tab reads from one source</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 (shipped 2026-05-10): structural target sources (fractal, fib, EW Wave-3) display on Plan tab as informational. Phase 2: actually use these as T1/T2 instead of ATR-multiple targets. Needs per-source x regime evidence (&gt;=30 trades each).</t>
+          <t>Different dashboard tabs (Plan, Overview, Technicals, Models) computed their own derived values from raw signal data — drift risk, inconsistent UI numbers.</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>Add config flag target_source = atr_multiple | structural. When structural, T1 = nearest_above with R:R&gt;=3 from {fractal_high, fib_127, EW_T1}. Fall back to ATR if R:R floor not met. Backtest side-by-side with current ATR-multiple.</t>
+          <t>New canonical_trade_plan.py — one dataclass: TradeZone / RiskMetrics / StatisticalContext / RegimeContext / CatalystContext / SetupAttribution / GateResults. swing_trade.py attaches it per signal. Live Wilson-CI lookup from signal_log per setup×regime. Mechanism hypothesis per setup family.</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>1 day + backtest</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I83" s="5" t="inlineStr">
         <is>
-          <t>High win potential, medium risk</t>
+          <t>Win: tabs converge on one truth; future tabs bind to dataclass fields.</t>
         </is>
       </c>
       <c r="J83" s="5" t="inlineStr">
         <is>
-          <t>Awaiting evidence. Phase 1 currently just populates display field; need 3-4 weeks of trade data with target_sources captured before Phase 2 is decidable.</t>
-        </is>
-      </c>
-      <c r="K83" s="11" t="inlineStr">
-        <is>
-          <t>IN_PROGRESS</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr"/>
-      <c r="M83" s="3" t="inlineStr"/>
+          <t>402 LOC. Future tabs MUST bind to canonical fields, not recompute.</t>
+        </is>
+      </c>
+      <c r="K83" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>2c9b9f339</t>
+        </is>
+      </c>
       <c r="N83" s="8" t="inlineStr">
         <is>
-          <t>Run backtest with target_source=structural and target_source=atr_multiple on same window. Compare PF/WR/avg_win.</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="75" customHeight="1">
+          <t>Open infra/prototype/elite-detail.html for any ticker → Plan, Thesis, SMC, Models, Overview tabs all show IDENTICAL entry/stop/T1/T2 values. No mismatches across tabs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="90" customHeight="1">
       <c r="A84" s="2" t="n">
         <v>83</v>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>K6</t>
+          <t>B3-WEEKLY-FIX</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
@@ -4578,37 +4602,29 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Backtest / Bug Fix</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>Single canonical trade plan object — every tab reads from one source</t>
+          <t>Backtest must build weekly_df from daily for weekly_bull computation</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>Different dashboard tabs (Plan, Overview, Technicals, Models) computed their own derived values from raw signal data — drift risk, inconsistent UI numbers.</t>
+          <t>Backtest harness was passing only the daily df to the engine, but weekly_bull (a hard gate in trend-continuation setups) requires resampled weekly bars. Without it, every backtest signal fell through the weekly_bull gate as 'unknown' which the engine treated as fail. Effective on-paper effect: 0 BUYs across many backtests despite valid signals in the daily series.</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>New canonical_trade_plan.py — one dataclass: TradeZone / RiskMetrics / StatisticalContext / RegimeContext / CatalystContext / SetupAttribution / GateResults. swing_trade.py attaches it per signal. Live Wilson-CI lookup from signal_log per setup×regime. Mechanism hypothesis per setup family.</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I84" s="5" t="inlineStr">
-        <is>
-          <t>Win: tabs converge on one truth; future tabs bind to dataclass fields.</t>
-        </is>
-      </c>
+          <t>Build weekly_df via df.resample('W').agg({open: first, high: max, low: min, close: last, volume: sum}) before each pre-trade-gate call. Pass alongside daily.</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr"/>
+      <c r="I84" s="5" t="inlineStr"/>
       <c r="J84" s="5" t="inlineStr">
         <is>
-          <t>402 LOC. Future tabs MUST bind to canonical fields, not recompute.</t>
+          <t>P0 because this silently invalidated every Trend-Continuation backtest signal in the 750d simulations Saturday. Found during Q1-step5 0-BUY investigation — daily df alone made the engine think every TC signal failed weekly_bull as "unknown".</t>
         </is>
       </c>
       <c r="K84" s="12" t="inlineStr">
@@ -4618,27 +4634,27 @@
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
-          <t>2c9b9f339</t>
+          <t>985cd182b</t>
         </is>
       </c>
       <c r="N84" s="8" t="inlineStr">
         <is>
-          <t>Open infra/prototype/elite-detail.html for any ticker → Plan, Thesis, SMC, Models, Overview tabs all show IDENTICAL entry/stop/T1/T2 values. No mismatches across tabs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="90" customHeight="1">
+          <t>1. python3 backtest.py --window 250d --min-score 65 → confirm BUYs &gt; 0. 2. Compare cache/portfolio_backtest_250d_min65_h5_20260510_*.json before/after fix → expected: pre-fix had 0 trades on Trend-Continuation family; post-fix has them. 3. grep -E "weekly_df|weekly_bull" backtest.py to verify the resample call is in the inner loop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="75" customHeight="1">
       <c r="A85" s="2" t="n">
         <v>84</v>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>B3-WEEKLY-FIX</t>
+          <t>VARIANT-F-BT</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -4648,31 +4664,27 @@
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>Backtest / Bug Fix</t>
+          <t>Backtest Parity</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>Backtest must build weekly_df from daily for weekly_bull computation</t>
+          <t>Variant F regime-conditional multipliers not wired into backtest path</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>Backtest harness was passing only the daily df to the engine, but weekly_bull (a hard gate in trend-continuation setups) requires resampled weekly bars. Without it, every backtest signal fell through the weekly_bull gate as 'unknown' which the engine treated as fail. Effective on-paper effect: 0 BUYs across many backtests despite valid signals in the daily series.</t>
+          <t>backtest.py:418 uses tracker.get_setup_weight_multiplier (reading picks_history) but never consults config.setup_score_multiplier_by_regime. So Variant F's TC×bull=0.0 kill never applied in backtest — explains why 105 TC bull trades persisted in 250d backtest despite live kill in config.</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>Build weekly_df via df.resample('W').agg({open: first, high: max, low: min, close: last, volume: sum}) before each pre-trade-gate call. Pass alongside daily.</t>
+          <t>Add Variant F lookup at backtest.py:442 mirroring analysis.py:8867 logic. Same demotion gate (n&gt;=30 + wr_lb&lt;0.30). Comment cross-reference live path.</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr"/>
       <c r="I85" s="5" t="inlineStr"/>
-      <c r="J85" s="5" t="inlineStr">
-        <is>
-          <t>P0 because this silently invalidated every Trend-Continuation backtest signal in the 750d simulations Saturday. Found during Q1-step5 0-BUY investigation — daily df alone made the engine think every TC signal failed weekly_bull as "unknown".</t>
-        </is>
-      </c>
+      <c r="J85" s="5" t="inlineStr"/>
       <c r="K85" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4685,22 +4697,18 @@
       </c>
       <c r="M85" s="3" t="inlineStr">
         <is>
-          <t>985cd182b</t>
-        </is>
-      </c>
-      <c r="N85" s="8" t="inlineStr">
-        <is>
-          <t>1. python3 backtest.py --window 250d --min-score 65 → confirm BUYs &gt; 0. 2. Compare cache/portfolio_backtest_250d_min65_h5_20260510_*.json before/after fix → expected: pre-fix had 0 trades on Trend-Continuation family; post-fix has them. 3. grep -E "weekly_df|weekly_bull" backtest.py to verify the resample call is in the inner loop.</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="75" customHeight="1">
+          <t>0cdb13340</t>
+        </is>
+      </c>
+      <c r="N85" s="8" t="inlineStr"/>
+    </row>
+    <row r="86" ht="45" customHeight="1">
       <c r="A86" s="2" t="n">
         <v>85</v>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>VARIANT-F-BT</t>
+          <t>P0-WEEKLY</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
@@ -4710,27 +4718,39 @@
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>Backtest Parity</t>
+          <t>Backtest infra</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>Variant F regime-conditional multipliers not wired into backtest path</t>
+          <t>Backtest must build weekly_df from daily (0-BUYs root cause)</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>backtest.py:418 uses tracker.get_setup_weight_multiplier (reading picks_history) but never consults config.setup_score_multiplier_by_regime. So Variant F's TC×bull=0.0 kill never applied in backtest — explains why 105 TC bull trades persisted in 250d backtest despite live kill in config.</t>
+          <t>GATE-1 produced 0 BUYs because backtest _score_as_of did not pass weekly_df. _weekly_ema_alignment(None) returned bullish=False; setup_gates demoted every BUY.</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>Add Variant F lookup at backtest.py:442 mirroring analysis.py:8867 logic. Same demotion gate (n&gt;=30 + wr_lb&lt;0.30). Comment cross-reference live path.</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr"/>
-      <c r="I86" s="5" t="inlineStr"/>
-      <c r="J86" s="5" t="inlineStr"/>
+          <t>Resample daily OHLCV to W-FRI inside _score_as_of. Pass weekly_df to score_technicals. Leakage-free.</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>20 min</t>
+        </is>
+      </c>
+      <c r="I86" s="5" t="inlineStr">
+        <is>
+          <t>CRITICAL — system was unable to backtest</t>
+        </is>
+      </c>
+      <c r="J86" s="5" t="inlineStr">
+        <is>
+          <t>Validated: --smoke produced 5 BUYs in 5d, PF 7.74.</t>
+        </is>
+      </c>
       <c r="K86" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4743,18 +4763,22 @@
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
-          <t>0cdb13340</t>
-        </is>
-      </c>
-      <c r="N86" s="8" t="inlineStr"/>
-    </row>
-    <row r="87" ht="45" customHeight="1">
+          <t>985cd182b</t>
+        </is>
+      </c>
+      <c r="N86" s="8" t="inlineStr">
+        <is>
+          <t>python3 backtest.py --smoke - cache/portfolio_backtest.json total_trades &gt; 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="75" customHeight="1">
       <c r="A87" s="2" t="n">
         <v>86</v>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>P0-WEEKLY</t>
+          <t>ROLLING-SHARPE-FIX</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -4764,39 +4788,27 @@
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>Backtest infra</t>
+          <t>Decision Engine / Bug</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>Backtest must build weekly_df from daily (0-BUYs root cause)</t>
+          <t>Rolling-Sharpe brake firing on contaminated data</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>GATE-1 produced 0 BUYs because backtest _score_as_of did not pass weekly_df. _weekly_ema_alignment(None) returned bullish=False; setup_gates demoted every BUY.</t>
+          <t>Two bugs: (a) WATCH-conviction signals being written with verdict='BUY' inflated loss count; (b) same physical trade re-emitted as fresh daily signal counted 3× in rolling-20 window. Net: false brake activation pausing ALL new BUYs system-wide. Real Sharpe -0.42; system reported -1.732</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>Resample daily OHLCV to W-FRI inside _score_as_of. Pass weekly_df to score_technicals. Leakage-free.</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>20 min</t>
-        </is>
-      </c>
-      <c r="I87" s="5" t="inlineStr">
-        <is>
-          <t>CRITICAL — system was unable to backtest</t>
-        </is>
-      </c>
-      <c r="J87" s="5" t="inlineStr">
-        <is>
-          <t>Validated: --smoke produced 5 BUYs in 5d, PF 7.74.</t>
-        </is>
-      </c>
+          <t>Upstream fix: swing_trade.py line 3110 _resolve_verdict() detects WATCH conviction and overrides bucket label. Read-time fix: decision_engine.compute_rolling_sharpe_kill_state dedupes by (ticker,entry,pnl,exit_reason). Historical cleanup: scripts/dedupe_signal_log.py removed 133 mislabels + 90 dupes (backed up)</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr"/>
+      <c r="I87" s="5" t="inlineStr"/>
+      <c r="J87" s="5" t="inlineStr"/>
       <c r="K87" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4804,27 +4816,23 @@
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="M87" s="3" t="inlineStr">
         <is>
-          <t>985cd182b</t>
-        </is>
-      </c>
-      <c r="N87" s="8" t="inlineStr">
-        <is>
-          <t>python3 backtest.py --smoke - cache/portfolio_backtest.json total_trades &gt; 0.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="75" customHeight="1">
+          <t>27fd646b1</t>
+        </is>
+      </c>
+      <c r="N87" s="8" t="inlineStr"/>
+    </row>
+    <row r="88" ht="90" customHeight="1">
       <c r="A88" s="2" t="n">
         <v>87</v>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>ROLLING-SHARPE-FIX</t>
+          <t>OPERATING-MINDSET</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
@@ -4834,27 +4842,39 @@
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>Decision Engine / Bug</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>Rolling-Sharpe brake firing on contaminated data</t>
+          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>Two bugs: (a) WATCH-conviction signals being written with verdict='BUY' inflated loss count; (b) same physical trade re-emitted as fresh daily signal counted 3× in rolling-20 window. Net: false brake activation pausing ALL new BUYs system-wide. Real Sharpe -0.42; system reported -1.732</t>
+          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>Upstream fix: swing_trade.py line 3110 _resolve_verdict() detects WATCH conviction and overrides bucket label. Read-time fix: decision_engine.compute_rolling_sharpe_kill_state dedupes by (ticker,entry,pnl,exit_reason). Historical cleanup: scripts/dedupe_signal_log.py removed 133 mislabels + 90 dupes (backed up)</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr"/>
-      <c r="I88" s="5" t="inlineStr"/>
-      <c r="J88" s="5" t="inlineStr"/>
+          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I88" s="5" t="inlineStr">
+        <is>
+          <t>Win: codified discipline survives session/agent boundaries.</t>
+        </is>
+      </c>
+      <c r="J88" s="5" t="inlineStr">
+        <is>
+          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
+        </is>
+      </c>
       <c r="K88" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4862,23 +4882,27 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
-          <t>27fd646b1</t>
-        </is>
-      </c>
-      <c r="N88" s="8" t="inlineStr"/>
-    </row>
-    <row r="89" ht="90" customHeight="1">
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N88" s="8" t="inlineStr">
+        <is>
+          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="60" customHeight="1">
       <c r="A89" s="2" t="n">
         <v>88</v>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>OPERATING-MINDSET</t>
+          <t>EXEC-TRADABLE-ENUM</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -4888,39 +4912,27 @@
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Execution · Auto-Trade</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
+          <t>Stock executor skipped all active names (enum bug)</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
+          <t>alpaca-py AssetStatus enum stringified to 'AssetStatus.ACTIVE'; check 'assetstatus.active' != 'active' wrongly skipped EVERY tradable stock since ~2026-05-28 → stock auto-trade silently dead, options-only</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I89" s="5" t="inlineStr">
-        <is>
-          <t>Win: codified discipline survives session/agent boundaries.</t>
-        </is>
-      </c>
-      <c r="J89" s="5" t="inlineStr">
-        <is>
-          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
-        </is>
-      </c>
+          <t>executor.py: read enum .value ('active') before lowercasing</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr"/>
+      <c r="I89" s="5" t="inlineStr"/>
+      <c r="J89" s="5" t="inlineStr"/>
       <c r="K89" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4928,27 +4940,23 @@
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="M89" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="N89" s="8" t="inlineStr">
-        <is>
-          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="60" customHeight="1">
+          <t>c7098178a</t>
+        </is>
+      </c>
+      <c r="N89" s="8" t="inlineStr"/>
+    </row>
+    <row r="90" ht="105" customHeight="1">
       <c r="A90" s="2" t="n">
         <v>89</v>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>EXEC-TRADABLE-ENUM</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
@@ -4958,27 +4966,39 @@
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>Execution · Auto-Trade</t>
+          <t>ML / Data Logging</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>Stock executor skipped all active names (enum bug)</t>
+          <t>Entry-time feature logger in swing_trade.py</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>alpaca-py AssetStatus enum stringified to 'AssetStatus.ACTIVE'; check 'assetstatus.active' != 'active' wrongly skipped EVERY tradable stock since ~2026-05-28 → stock auto-trade silently dead, options-only</t>
+          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>executor.py: read enum .value ('active') before lowercasing</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr"/>
-      <c r="I90" s="5" t="inlineStr"/>
-      <c r="J90" s="5" t="inlineStr"/>
+          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I90" s="5" t="inlineStr">
+        <is>
+          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
+        </is>
+      </c>
+      <c r="J90" s="5" t="inlineStr">
+        <is>
+          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
+        </is>
+      </c>
       <c r="K90" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4986,15 +5006,19 @@
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M90" s="3" t="inlineStr">
         <is>
-          <t>c7098178a</t>
-        </is>
-      </c>
-      <c r="N90" s="8" t="inlineStr"/>
+          <t>0574c60d4</t>
+        </is>
+      </c>
+      <c r="N90" s="8" t="inlineStr">
+        <is>
+          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="105" customHeight="1">
       <c r="A91" s="2" t="n">
@@ -5002,7 +5026,7 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>ML-FEATURE-MISMATCH</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -5012,39 +5036,27 @@
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>ML / Data Logging</t>
+          <t>ML · Inference</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>Entry-time feature logger in swing_trade.py</t>
+          <t>Live predict_one degenerate — 29-feat model vs 17-feat extractor</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
+          <t>Models retrained 2026-06-09 on 29 features but ml.feature_extractor.FEATURE_COLS still emits 17, so live predict_one feeds a mismatched vector and returns ~0 p_up for EVERY ticker (AI Edge 0% bug, all names). Batch ml-predict path extracts 29 correctly. /api/ml now prefers the batch cache + rejects degenerate live; ROOT FIX still needed: align FEATURE_COLS to 29 (or guard retrain to the live feature set). Also cache 4d stale.</t>
         </is>
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I91" s="5" t="inlineStr">
-        <is>
-          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
-        </is>
-      </c>
-      <c r="J91" s="5" t="inlineStr">
-        <is>
-          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
-        </is>
-      </c>
+          <t>server /api/ml cache-first + degenerate guard (done); align ml/feature_extractor.FEATURE_COLS to model n_features_in_ (pending)</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr"/>
+      <c r="I91" s="5" t="inlineStr"/>
+      <c r="J91" s="5" t="inlineStr"/>
       <c r="K91" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5052,27 +5064,23 @@
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="M91" s="3" t="inlineStr">
         <is>
-          <t>0574c60d4</t>
-        </is>
-      </c>
-      <c r="N91" s="8" t="inlineStr">
-        <is>
-          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="105" customHeight="1">
+          <t>33877186c</t>
+        </is>
+      </c>
+      <c r="N91" s="8" t="inlineStr"/>
+    </row>
+    <row r="92" ht="45" customHeight="1">
       <c r="A92" s="2" t="n">
         <v>91</v>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>ML-FEATURE-MISMATCH</t>
+          <t>IPAD-3</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -5082,27 +5090,39 @@
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>ML · Inference</t>
+          <t>Mobile / iPad</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>Live predict_one degenerate — 29-feat model vs 17-feat extractor</t>
+          <t>iPad shell hot fix — verdict/stage/score field mismatch</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>Models retrained 2026-06-09 on 29 features but ml.feature_extractor.FEATURE_COLS still emits 17, so live predict_one feeds a mismatched vector and returns ~0 p_up for EVERY ticker (AI Edge 0% bug, all names). Batch ml-predict path extracts 29 correctly. /api/ml now prefers the batch cache + rejects degenerate live; ROOT FIX still needed: align FEATURE_COLS to 29 (or guard retrain to the live feature set). Also cache 4d stale.</t>
+          <t>Phase 1 release showed 0 rows in Scanner + Elite tabs. Bundle uses stage not verdict; elite_picks shape is nested.</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
-          <t>server /api/ml cache-first + degenerate guard (done); align ml/feature_extractor.FEATURE_COLS to model n_features_in_ (pending)</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr"/>
-      <c r="I92" s="5" t="inlineStr"/>
-      <c r="J92" s="5" t="inlineStr"/>
+          <t>3 fixes in ipad.js: filter falls through to r.stage; elite tab aggregates Swing.BUY+WATCH+SHORT; buildRow score fallback.</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>20 min</t>
+        </is>
+      </c>
+      <c r="I92" s="5" t="inlineStr">
+        <is>
+          <t>Low / Required</t>
+        </is>
+      </c>
+      <c r="J92" s="5" t="inlineStr">
+        <is>
+          <t>Verified 0-&gt;61 Scanner rows, 0-&gt;5 Elite rows.</t>
+        </is>
+      </c>
       <c r="K92" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5110,23 +5130,27 @@
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M92" s="3" t="inlineStr">
         <is>
-          <t>33877186c</t>
-        </is>
-      </c>
-      <c r="N92" s="8" t="inlineStr"/>
-    </row>
-    <row r="93" ht="45" customHeight="1">
+          <t>b0e5ef6a1</t>
+        </is>
+      </c>
+      <c r="N92" s="8" t="inlineStr">
+        <is>
+          <t>Hard-refresh iPad shell. Scanner shows 60+ WATCH rows; Elite shows 5 picks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="120" customHeight="1">
       <c r="A93" s="2" t="n">
         <v>92</v>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>IPAD-3</t>
+          <t>ALPACA-SYNC</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
@@ -5136,39 +5160,27 @@
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>Mobile / iPad</t>
+          <t>Paper Trading/State Sync</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>iPad shell hot fix — verdict/stage/score field mismatch</t>
+          <t>Local state diverges from Alpaca paper account — dashboards and feedback loops read stale 'no positions' while Alpaca has real fills</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 release showed 0 rows in Scanner + Elite tabs. Bundle uses stage not verdict; elite_picks shape is nested.</t>
+          <t>portfolio_state.json + SQLite positions/trades tables report 0 rows. Alpaca has 28 filled orders since 2026-04-30 (14 BUY + 14 SELL = 14 round-trips, all stopped out 05-05 to 05-07, total paper loss ~$1,612). Effect: (a) dashboard shows wrong state, (b) portfolio_tracker can't attribute P&amp;L back to setup x regime, (c) kelly_size.drawdown_mult (commit 74cb3b208) reads local equity_curve which has no actual data → multiplier silently neutral, (d) no learning loop from actual paper losses to setup multipliers.</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>3 fixes in ipad.js: filter falls through to r.stage; elite tab aggregates Swing.BUY+WATCH+SHORT; buildRow score fallback.</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>20 min</t>
-        </is>
-      </c>
-      <c r="I93" s="5" t="inlineStr">
-        <is>
-          <t>Low / Required</t>
-        </is>
-      </c>
-      <c r="J93" s="5" t="inlineStr">
-        <is>
-          <t>Verified 0-&gt;61 Scanner rows, 0-&gt;5 Elite rows.</t>
-        </is>
-      </c>
+          <t>Build alpaca_sync.py with sync_alpaca_to_local(). v1: pull account + positions, write portfolio_state.json + SQLite positions table. v2: filled-order reconciliation, pick attribution via cache/orders.jsonl, equity_curve snapshot. Wire as Step 0 of swing_trade.py (every scan) + executor.py post-submit + standalone scripts/sync_alpaca.py for ad-hoc runs.</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr"/>
+      <c r="I93" s="5" t="inlineStr"/>
+      <c r="J93" s="5" t="inlineStr"/>
       <c r="K93" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5181,22 +5193,18 @@
       </c>
       <c r="M93" s="3" t="inlineStr">
         <is>
-          <t>b0e5ef6a1</t>
-        </is>
-      </c>
-      <c r="N93" s="8" t="inlineStr">
-        <is>
-          <t>Hard-refresh iPad shell. Scanner shows 60+ WATCH rows; Elite shows 5 picks.</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="120" customHeight="1">
+          <t>f26e1deb2</t>
+        </is>
+      </c>
+      <c r="N93" s="8" t="inlineStr"/>
+    </row>
+    <row r="94" ht="60" customHeight="1">
       <c r="A94" s="2" t="n">
         <v>93</v>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>ALPACA-SYNC</t>
+          <t>Q1-step1</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -5206,27 +5214,39 @@
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>Paper Trading/State Sync</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>Local state diverges from Alpaca paper account — dashboards and feedback loops read stale 'no positions' while Alpaca has real fills</t>
+          <t>Re-derive Saturday's empirical analysis on n=384 750d backtest</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>portfolio_state.json + SQLite positions/trades tables report 0 rows. Alpaca has 28 filled orders since 2026-04-30 (14 BUY + 14 SELL = 14 round-trips, all stopped out 05-05 to 05-07, total paper loss ~$1,612). Effect: (a) dashboard shows wrong state, (b) portfolio_tracker can't attribute P&amp;L back to setup x regime, (c) kelly_size.drawdown_mult (commit 74cb3b208) reads local equity_curve which has no actual data → multiplier silently neutral, (d) no learning loop from actual paper losses to setup multipliers.</t>
+          <t>Saturday's session changed live config based on agent-summarized stats. Agent's Fix 2 was actively wrong; Fix 3 had n=1 evidence in post-kill subset. Confirm Saturday's reads before any further changes.</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>Build alpaca_sync.py with sync_alpaca_to_local(). v1: pull account + positions, write portfolio_state.json + SQLite positions table. v2: filled-order reconciliation, pick attribution via cache/orders.jsonl, equity_curve snapshot. Wire as Step 0 of swing_trade.py (every scan) + executor.py post-submit + standalone scripts/sync_alpaca.py for ad-hoc runs.</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr"/>
-      <c r="I94" s="5" t="inlineStr"/>
-      <c r="J94" s="5" t="inlineStr"/>
+          <t>Run inline Python script in SESSION_HANDOFF section 3 against cache/portfolio_backtest_750d_20260509_100501.json. Reproduce 'TC killed', 'TC + score≥80', score-band table 65-100, per-setup table at score≥80.</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
+      <c r="I94" s="5" t="inlineStr">
+        <is>
+          <t>Risk: none. Verify: TC killed PF 0.86, 80-85 band PF 1.72, VCP n=1.</t>
+        </is>
+      </c>
+      <c r="J94" s="5" t="inlineStr">
+        <is>
+          <t>Gate for everything below — do not proceed if numbers diverge. · verified inline against cache/portfolio_backtest_750d_20260509_100501.json: TC@score&gt;=80 PF 0.54, VCP@score&gt;=80 n=1, Near-VCP@score&gt;=80 PF 1.05, 90-100 band PF 0.55</t>
+        </is>
+      </c>
       <c r="K94" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5234,23 +5254,27 @@
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M94" s="3" t="inlineStr">
         <is>
-          <t>f26e1deb2</t>
-        </is>
-      </c>
-      <c r="N94" s="8" t="inlineStr"/>
-    </row>
-    <row r="95" ht="60" customHeight="1">
+          <t>d8c08399b</t>
+        </is>
+      </c>
+      <c r="N94" s="8" t="inlineStr">
+        <is>
+          <t>python3 -c 'import json; d=json.load(open("cache/portfolio_backtest_750d_20260509_100501.json")); print(d["profit_factor"])' → 0.70 confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="45" customHeight="1">
       <c r="A95" s="2" t="n">
         <v>94</v>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>Q1-step1</t>
+          <t>Q1-step2</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
@@ -5265,32 +5289,32 @@
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>Re-derive Saturday's empirical analysis on n=384 750d backtest</t>
+          <t>Revert Fix 3 — VCP Breakout multiplier 1.2 → 0.0</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>Saturday's session changed live config based on agent-summarized stats. Agent's Fix 2 was actively wrong; Fix 3 had n=1 evidence in post-kill subset. Confirm Saturday's reads before any further changes.</t>
+          <t>Saturday boosted VCP Breakout to 1.2× based on n=12 aggregate. Post-kill universe has only n=1 firing at score≥80, and it lost.</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>Run inline Python script in SESSION_HANDOFF section 3 against cache/portfolio_backtest_750d_20260509_100501.json. Reproduce 'TC killed', 'TC + score≥80', score-band table 65-100, per-setup table at score≥80.</t>
+          <t>Edit config/config.json: setup_score_multiplier['VCP Breakout'] 1.2 → 0.0. Verify with git diff config/config.json.</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>2 min</t>
         </is>
       </c>
       <c r="I95" s="5" t="inlineStr">
         <is>
-          <t>Risk: none. Verify: TC killed PF 0.86, 80-85 band PF 1.72, VCP n=1.</t>
+          <t>Risk: LOW. Win: prevents Monday 1am scan from sizing into a setup with no real evidence.</t>
         </is>
       </c>
       <c r="J95" s="5" t="inlineStr">
         <is>
-          <t>Gate for everything below — do not proceed if numbers diverge. · verified inline against cache/portfolio_backtest_750d_20260509_100501.json: TC@score&gt;=80 PF 0.54, VCP@score&gt;=80 n=1, Near-VCP@score&gt;=80 PF 1.05, 90-100 band PF 0.55</t>
+          <t>Lesson: filter to 'what new config would have allowed' before extrapolating.</t>
         </is>
       </c>
       <c r="K95" s="12" t="inlineStr">
@@ -5310,7 +5334,7 @@
       </c>
       <c r="N95" s="8" t="inlineStr">
         <is>
-          <t>python3 -c 'import json; d=json.load(open("cache/portfolio_backtest_750d_20260509_100501.json")); print(d["profit_factor"])' → 0.70 confirmed.</t>
+          <t>grep -A5 '"VCP Breakout"' config/config.json → setup_score_multiplier shows 0.0 (was 1.2). git diff confirms revert.</t>
         </is>
       </c>
     </row>
@@ -5320,7 +5344,7 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>Q1-step2</t>
+          <t>Q1-step3</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
@@ -5335,17 +5359,17 @@
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>Revert Fix 3 — VCP Breakout multiplier 1.2 → 0.0</t>
+          <t>Boost Near-VCP Breakout multiplier 0.7 → 1.0</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>Saturday boosted VCP Breakout to 1.2× based on n=12 aggregate. Post-kill universe has only n=1 firing at score≥80, and it lost.</t>
+          <t>Post-kill universe at score≥80: Near-VCP Breakout n=50, PF 1.07 — workhorse currently demoted to 0.7×.</t>
         </is>
       </c>
       <c r="G96" s="5" t="inlineStr">
         <is>
-          <t>Edit config/config.json: setup_score_multiplier['VCP Breakout'] 1.2 → 0.0. Verify with git diff config/config.json.</t>
+          <t>Edit config/config.json: setup_score_multiplier['Near-VCP Breakout'] 0.7 → 1.0. Verify next backtest.</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5355,12 +5379,12 @@
       </c>
       <c r="I96" s="5" t="inlineStr">
         <is>
-          <t>Risk: LOW. Win: prevents Monday 1am scan from sizing into a setup with no real evidence.</t>
+          <t>Risk: LOW-MEDIUM. Win: lets proven workhorse pull full weight.</t>
         </is>
       </c>
       <c r="J96" s="5" t="inlineStr">
         <is>
-          <t>Lesson: filter to 'what new config would have allowed' before extrapolating.</t>
+          <t>PF 1.07 has wide CI 0.85-1.30 OOS. Verify with Q1-step4 250d backtest.</t>
         </is>
       </c>
       <c r="K96" s="12" t="inlineStr">
@@ -5380,17 +5404,17 @@
       </c>
       <c r="N96" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 '"VCP Breakout"' config/config.json → setup_score_multiplier shows 0.0 (was 1.2). git diff confirms revert.</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="45" customHeight="1">
+          <t>grep -A5 '"Near-VCP Breakout"' config/config.json → setup_score_multiplier shows 1.0 (was 0.7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="60" customHeight="1">
       <c r="A97" s="2" t="n">
         <v>96</v>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Q1-step3</t>
+          <t>Q1-step4</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -5405,32 +5429,32 @@
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>Boost Near-VCP Breakout multiplier 0.7 → 1.0</t>
+          <t>Run 250-day backtest to validate steps 2 + 3</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>Post-kill universe at score≥80: Near-VCP Breakout n=50, PF 1.07 — workhorse currently demoted to 0.7×.</t>
+          <t>Need fast validation that config changes don't break things before committing 3 hours to full 750d.</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>Edit config/config.json: setup_score_multiplier['Near-VCP Breakout'] 0.7 → 1.0. Verify next backtest.</t>
+          <t>python3 backtest.py --days 250 --hold 5 --min-score 65 --portfolio --equity 5000 --positions 4 --size-pct 0.25 &gt; cache/logs/backtest_250d_quant1_$(date +%Y%m%d_%H%M%S).log 2&gt;&amp;1 &amp;</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>2 min</t>
+          <t>~12 min wall-clock</t>
         </is>
       </c>
       <c r="I97" s="5" t="inlineStr">
         <is>
-          <t>Risk: LOW-MEDIUM. Win: lets proven workhorse pull full weight.</t>
+          <t>Risk: none (offline). Verify: PF ≥ 1.0 to proceed.</t>
         </is>
       </c>
       <c r="J97" s="5" t="inlineStr">
         <is>
-          <t>PF 1.07 has wide CI 0.85-1.30 OOS. Verify with Q1-step4 250d backtest.</t>
+          <t>PASSED smoke 5d (PF 7.74, WR 40%). Confirmed weekly_df fix unblocks BUYs.</t>
         </is>
       </c>
       <c r="K97" s="12" t="inlineStr">
@@ -5440,27 +5464,27 @@
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M97" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>985cd182b</t>
         </is>
       </c>
       <c r="N97" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 '"Near-VCP Breakout"' config/config.json → setup_score_multiplier shows 1.0 (was 0.7).</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="60" customHeight="1">
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="180" customHeight="1">
       <c r="A98" s="2" t="n">
         <v>97</v>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>Q1-step4</t>
+          <t>Q1-step5</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
@@ -5475,32 +5499,32 @@
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>Run 250-day backtest to validate steps 2 + 3</t>
+          <t>Run 750-day backtest to confirm if 250d passes</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>Need fast validation that config changes don't break things before committing 3 hours to full 750d.</t>
+          <t>Real evidence comes from full 750d window — same methodology that produced Saturday's headline n=384 result.</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>python3 backtest.py --days 250 --hold 5 --min-score 65 --portfolio --equity 5000 --positions 4 --size-pct 0.25 &gt; cache/logs/backtest_250d_quant1_$(date +%Y%m%d_%H%M%S).log 2&gt;&amp;1 &amp;</t>
+          <t>Same backtest command but --days 750. Run during Sunday daytime (3hr runtime).</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>~12 min wall-clock</t>
+          <t>~3 hours</t>
         </is>
       </c>
       <c r="I98" s="5" t="inlineStr">
         <is>
-          <t>Risk: none (offline). Verify: PF ≥ 1.0 to proceed.</t>
+          <t>Risk: none. Verify: PF, WR, drawdown all directionally improved vs Saturday's PF 0.70.</t>
         </is>
       </c>
       <c r="J98" s="5" t="inlineStr">
         <is>
-          <t>PASSED smoke 5d (PF 7.74, WR 40%). Confirmed weekly_df fix unblocks BUYs.</t>
+          <t>FAILED acceptance bar over 12 months (n=142): PF 0.95 / WR 31.7% / MaxDD 32.1% / -6.3% return / Sharpe -0.17. avg_win 6.08% vs avg_loss -2.96% (asymmetry 2.05× needs ~2.5× for PF 1.4 at this WR). System produces actionable trades but too many small losers (97/142). DO NOT activate paper trading on this config. Next: try tighter entry quality, wider stops, higher score floor — need user decision on which lever first. / FAILED ACCEPTANCE BAR (2026-05-10): 250d backtest produced 0 BUYs across 3+ simulated months. Q1 multipliers + threshold combo demoted every qualifying signal. Sibling commit a18282d28 (Q1-step5 250d FINAL) logged the failure; recovery path was Variant F (commit f0a66543e) — regime-conditional TC kill ONLY in bull regime (not all 4 regimes). 250d Variant F backtest pending verification before declaring real fix.</t>
         </is>
       </c>
       <c r="K98" s="12" t="inlineStr">
@@ -5515,22 +5539,22 @@
       </c>
       <c r="M98" s="3" t="inlineStr">
         <is>
-          <t>985cd182b</t>
+          <t>985cd182b + run cache/portfolio_backtest_*</t>
         </is>
       </c>
       <c r="N98" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="180" customHeight="1">
+          <t>cat cache/portfolio_backtest.json → check profit_factor, win_rate, max_drawdown_pct fields. Open cache/backtest_report_latest.html for per-setup attribution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="45" customHeight="1">
       <c r="A99" s="2" t="n">
         <v>98</v>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>Q1-step5</t>
+          <t>Q1-step6</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -5545,32 +5569,32 @@
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>Run 750-day backtest to confirm if 250d passes</t>
+          <t>Consider buy_max_score: 90 in regime4_thresholds blocks</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
-          <t>Real evidence comes from full 750d window — same methodology that produced Saturday's headline n=384 result.</t>
+          <t>90+ score band is anti-predictive: n=19, PF 0.32 in post-kill subset.</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>Same backtest command but --days 750. Run during Sunday daytime (3hr runtime).</t>
+          <t>Add buy_max_score: 90 to each of 4 regime blocks under regime4_thresholds. Re-run final backtest.</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>~3 hours</t>
+          <t>30 min + backtest</t>
         </is>
       </c>
       <c r="I99" s="5" t="inlineStr">
         <is>
-          <t>Risk: none. Verify: PF, WR, drawdown all directionally improved vs Saturday's PF 0.70.</t>
+          <t>Risk: MEDIUM (small sample n=19). Win: removes -67% PF drag if real.</t>
         </is>
       </c>
       <c r="J99" s="5" t="inlineStr">
         <is>
-          <t>FAILED acceptance bar over 12 months (n=142): PF 0.95 / WR 31.7% / MaxDD 32.1% / -6.3% return / Sharpe -0.17. avg_win 6.08% vs avg_loss -2.96% (asymmetry 2.05× needs ~2.5× for PF 1.4 at this WR). System produces actionable trades but too many small losers (97/142). DO NOT activate paper trading on this config. Next: try tighter entry quality, wider stops, higher score floor — need user decision on which lever first. / FAILED ACCEPTANCE BAR (2026-05-10): 250d backtest produced 0 BUYs across 3+ simulated months. Q1 multipliers + threshold combo demoted every qualifying signal. Sibling commit a18282d28 (Q1-step5 250d FINAL) logged the failure; recovery path was Variant F (commit f0a66543e) — regime-conditional TC kill ONLY in bull regime (not all 4 regimes). 250d Variant F backtest pending verification before declaring real fix.</t>
+          <t>Skip if step 5 already shows PF healthy.</t>
         </is>
       </c>
       <c r="K99" s="12" t="inlineStr">
@@ -5585,22 +5609,22 @@
       </c>
       <c r="M99" s="3" t="inlineStr">
         <is>
-          <t>985cd182b + run cache/portfolio_backtest_*</t>
+          <t>f47958fc9</t>
         </is>
       </c>
       <c r="N99" s="8" t="inlineStr">
         <is>
-          <t>cat cache/portfolio_backtest.json → check profit_factor, win_rate, max_drawdown_pct fields. Open cache/backtest_report_latest.html for per-setup attribution.</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="45" customHeight="1">
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="90" customHeight="1">
       <c r="A100" s="2" t="n">
         <v>99</v>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>Q1-step6</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
@@ -5610,37 +5634,37 @@
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Quant / Backtest infra</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
         <is>
-          <t>Consider buy_max_score: 90 in regime4_thresholds blocks</t>
+          <t>Enrich backtest trade records with regime/entry_quality/sector/MAE/MFE</t>
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>90+ score band is anti-predictive: n=19, PF 0.32 in post-kill subset.</t>
+          <t>750d backtest trade records had only ticker/dates/prices/pnl/setup_type/score/verdict/exit_reason — making per-strategy attribution impossible per A5 finding.</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>Add buy_max_score: 90 to each of 4 regime blocks under regime4_thresholds. Re-run final backtest.</t>
+          <t>backtest.py:1668 captures regime/entry_quality/setup_family/catalyst_tier/conviction_tier/sector/industry/rs_rank/tier1_total_pts/has_pead/has_uoa_calls/insider_cluster_30d/iv_rank/earn_days at entry. Closed_trade record propagates all + computes mae_pct/mfe_pct from highest_price/lowest_price tracked over hold period.</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>30 min + backtest</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I100" s="5" t="inlineStr">
         <is>
-          <t>Risk: MEDIUM (small sample n=19). Win: removes -67% PF drag if real.</t>
+          <t>Win: forensic decomposition possible on next 750d backtest.</t>
         </is>
       </c>
       <c r="J100" s="5" t="inlineStr">
         <is>
-          <t>Skip if step 5 already shows PF healthy.</t>
+          <t>Pure additive. Does not affect existing analysis.</t>
         </is>
       </c>
       <c r="K100" s="12" t="inlineStr">
@@ -5650,27 +5674,27 @@
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M100" s="3" t="inlineStr">
         <is>
-          <t>f47958fc9</t>
+          <t>f35f0c124</t>
         </is>
       </c>
       <c r="N100" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="90" customHeight="1">
+          <t>Run a fresh backtest (after current finishes). Open cache/portfolio_backtest_*.json → trade records contain regime, entry_quality, sector, mae_pct, mfe_pct fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="45" customHeight="1">
       <c r="A101" s="2" t="n">
         <v>100</v>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>Q1-Fix1</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
@@ -5680,22 +5704,22 @@
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>Quant / Backtest infra</t>
+          <t>Quant / Config</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>Enrich backtest trade records with regime/entry_quality/sector/MAE/MFE</t>
+          <t>Trend Continuation killed (Fix 1)</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>750d backtest trade records had only ticker/dates/prices/pnl/setup_type/score/verdict/exit_reason — making per-strategy attribution impossible per A5 finding.</t>
+          <t>750d backtest: Trend Continuation 264/384 trades (69%) at PF 0.65, Wilson LB 19.5% — single biggest portfolio drain.</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>backtest.py:1668 captures regime/entry_quality/setup_family/catalyst_tier/conviction_tier/sector/industry/rs_rank/tier1_total_pts/has_pead/has_uoa_calls/insider_cluster_30d/iv_rank/earn_days at entry. Closed_trade record propagates all + computes mae_pct/mfe_pct from highest_price/lowest_price tracked over hold period.</t>
+          <t>config/config.json: setup_score_multiplier['Trend Continuation'] 0.7→0.0 + static_setup_kill_list dict entry (n=264, wr_lb=0.195, source=static).</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -5705,12 +5729,12 @@
       </c>
       <c r="I101" s="5" t="inlineStr">
         <is>
-          <t>Win: forensic decomposition possible on next 750d backtest.</t>
+          <t>Win: prevents biggest documented setup drag on Monday 1am scan.</t>
         </is>
       </c>
       <c r="J101" s="5" t="inlineStr">
         <is>
-          <t>Pure additive. Does not affect existing analysis.</t>
+          <t>Bug fix in 6ceca2d18: bare-string kill_list entries silently rejected — required dict format.</t>
         </is>
       </c>
       <c r="K101" s="12" t="inlineStr">
@@ -5725,12 +5749,12 @@
       </c>
       <c r="M101" s="3" t="inlineStr">
         <is>
-          <t>f35f0c124</t>
+          <t>fc76c9ec8 + 6ceca2d18</t>
         </is>
       </c>
       <c r="N101" s="8" t="inlineStr">
         <is>
-          <t>Run a fresh backtest (after current finishes). Open cache/portfolio_backtest_*.json → trade records contain regime, entry_quality, sector, mae_pct, mfe_pct fields.</t>
+          <t>grep -A5 'static_setup_kill_list' config/config.json → 'Trend Continuation' present in dict format with n=264 wr_lb=0.195.</t>
         </is>
       </c>
     </row>
@@ -5740,7 +5764,7 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>Q1-Fix1</t>
+          <t>Q1-Fix3</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
@@ -5755,32 +5779,32 @@
       </c>
       <c r="E102" s="6" t="inlineStr">
         <is>
-          <t>Trend Continuation killed (Fix 1)</t>
+          <t>VCP Breakout multiplier 0.0 → 1.2 (Fix 3) — needs revert</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>750d backtest: Trend Continuation 264/384 trades (69%) at PF 0.65, Wilson LB 19.5% — single biggest portfolio drain.</t>
+          <t>Comment in config said VCP Breakout was 'removed from kill list' but value remained 0.0. Restored to 1.2 based on n=12 PF 1.79 aggregate.</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>config/config.json: setup_score_multiplier['Trend Continuation'] 0.7→0.0 + static_setup_kill_list dict entry (n=264, wr_lb=0.195, source=static).</t>
+          <t>config['setup_score_multiplier']['VCP Breakout']: 0.0 → 1.2.</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>shipped (revert candidate)</t>
         </is>
       </c>
       <c r="I102" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents biggest documented setup drag on Monday 1am scan.</t>
+          <t>Risk: post-kill subset has only n=1 evidence — not real evidence. See Q1-step2.</t>
         </is>
       </c>
       <c r="J102" s="5" t="inlineStr">
         <is>
-          <t>Bug fix in 6ceca2d18: bare-string kill_list entries silently rejected — required dict format.</t>
+          <t>REVERT CANDIDATE. Sunday plan step 2: revert to 0.0.</t>
         </is>
       </c>
       <c r="K102" s="12" t="inlineStr">
@@ -5795,22 +5819,22 @@
       </c>
       <c r="M102" s="3" t="inlineStr">
         <is>
-          <t>fc76c9ec8 + 6ceca2d18</t>
+          <t>fc76c9ec8</t>
         </is>
       </c>
       <c r="N102" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 'static_setup_kill_list' config/config.json → 'Trend Continuation' present in dict format with n=264 wr_lb=0.195.</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="45" customHeight="1">
+          <t>Same as Q1-step2 verification — VCP Breakout multiplier should NOW be 0.0 (reverted from Saturday's 1.2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="105" customHeight="1">
       <c r="A103" s="2" t="n">
         <v>102</v>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>Q1-Fix3</t>
+          <t>VAR-F</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
@@ -5820,37 +5844,29 @@
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>Quant / Config</t>
+          <t>Quant / Recovery</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>VCP Breakout multiplier 0.0 → 1.2 (Fix 3) — needs revert</t>
+          <t>Variant F: regime-conditional Trend Continuation kill in bull regime only</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
-          <t>Comment in config said VCP Breakout was 'removed from kill list' but value remained 0.0. Restored to 1.2 based on n=12 PF 1.79 aggregate.</t>
+          <t>Q1-step5 250d backtest produced 0 BUYs (a18282d28). Root cause: Q1 multipliers + threshold combo demoted every qualifying signal across all regimes. Sibling session designed Variant F: kill TC ONLY in bull regime where it has been bleeding edge, leave TC alive in non-bull regimes where empirical edge holds.</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>config['setup_score_multiplier']['VCP Breakout']: 0.0 → 1.2.</t>
-        </is>
-      </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>shipped (revert candidate)</t>
-        </is>
-      </c>
-      <c r="I103" s="5" t="inlineStr">
-        <is>
-          <t>Risk: post-kill subset has only n=1 evidence — not real evidence. See Q1-step2.</t>
-        </is>
-      </c>
+          <t>regime-conditional setup_score_multiplier in config.json. Bull regime: TC = 0 (kill). Other regimes: TC = baseline. Verification backtest pending before declaring real fix.</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr"/>
+      <c r="I103" s="5" t="inlineStr"/>
       <c r="J103" s="5" t="inlineStr">
         <is>
-          <t>REVERT CANDIDATE. Sunday plan step 2: revert to 0.0.</t>
+          <t>Designed by sibling session as the recovery from Q1-step5 250d 0-BUY failure. Hypothesis: TC has been a net loser in bull regimes (compressed by trend exhaustion) but still has edge in chop/sideways. Killing only in bull preserves the workable edge while removing the bleed. Verification still pending — Q1-step5 cache/portfolio_backtest_*.json baseline + new 250d Variant F run side-by-side.</t>
         </is>
       </c>
       <c r="K103" s="12" t="inlineStr">
@@ -5860,27 +5876,27 @@
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M103" s="3" t="inlineStr">
         <is>
-          <t>fc76c9ec8</t>
+          <t>f0a66543e + 363984181</t>
         </is>
       </c>
       <c r="N103" s="8" t="inlineStr">
         <is>
-          <t>Same as Q1-step2 verification — VCP Breakout multiplier should NOW be 0.0 (reverted from Saturday's 1.2).</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="105" customHeight="1">
+          <t>1. python3 backtest.py --window 250d → expect non-zero BUYs (was 0 with Q1 config). 2. Inspect cache/portfolio_backtest_*.json → trades.regime field shows mostly non-bull regime trades for TC family. 3. Spot-check live scan: if regime4=risk_on_trending, TC tickers should fall through to WATCH; in risk_on_choppy/risk_off, TC should still earn BUY when scoring qualifies. 4. Variant F is verification-pending — log PF/WR vs Q1 baseline, compare to Q1-step5 0-BUY failure mode.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="60" customHeight="1">
       <c r="A104" s="2" t="n">
         <v>103</v>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>VAR-F</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
@@ -5890,29 +5906,37 @@
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>Quant / Recovery</t>
+          <t>Quant / Stop Engine</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
         <is>
-          <t>Variant F: regime-conditional Trend Continuation kill in bull regime only</t>
+          <t>Stop must be at/below nearest fractal low</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>Q1-step5 250d backtest produced 0 BUYs (a18282d28). Root cause: Q1 multipliers + threshold combo demoted every qualifying signal across all regimes. Sibling session designed Variant F: kill TC ONLY in bull regime where it has been bleeding edge, leave TC alive in non-bull regimes where empirical edge holds.</t>
+          <t>Calculated stops sometimes sit ABOVE the nearest Williams-fractal low — guaranteed easy stop-out target for market makers.</t>
         </is>
       </c>
       <c r="G104" s="5" t="inlineStr">
         <is>
-          <t>regime-conditional setup_score_multiplier in config.json. Bull regime: TC = 0 (kill). Other regimes: TC = baseline. Verification backtest pending before declaring real fix.</t>
-        </is>
-      </c>
-      <c r="H104" s="2" t="inlineStr"/>
-      <c r="I104" s="5" t="inlineStr"/>
+          <t>If stop &gt; indicators['fractal_low'] (already computed in _williams_fractals at analysis.py:1089), widen DOWN to just below fractal low + 0.10×ATR buffer. Bounded: won't widen &gt;20% from entry.</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I104" s="5" t="inlineStr">
+        <is>
+          <t>Win: single most important Vinod rule per coaching call.</t>
+        </is>
+      </c>
       <c r="J104" s="5" t="inlineStr">
         <is>
-          <t>Designed by sibling session as the recovery from Q1-step5 250d 0-BUY failure. Hypothesis: TC has been a net loser in bull regimes (compressed by trend exhaustion) but still has edge in chop/sideways. Killing only in bull preserves the workable edge while removing the bleed. Verification still pending — Q1-step5 cache/portfolio_backtest_*.json baseline + new 250d Variant F run side-by-side.</t>
+          <t>Longs only. Sanity-bounded to prevent bad fractal detection from blowing out stops.</t>
         </is>
       </c>
       <c r="K104" s="12" t="inlineStr">
@@ -5922,27 +5946,27 @@
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M104" s="3" t="inlineStr">
         <is>
-          <t>f0a66543e + 363984181</t>
+          <t>3d4eb71d7</t>
         </is>
       </c>
       <c r="N104" s="8" t="inlineStr">
         <is>
-          <t>1. python3 backtest.py --window 250d → expect non-zero BUYs (was 0 with Q1 config). 2. Inspect cache/portfolio_backtest_*.json → trades.regime field shows mostly non-bull regime trades for TC family. 3. Spot-check live scan: if regime4=risk_on_trending, TC tickers should fall through to WATCH; in risk_on_choppy/risk_off, TC should still earn BUY when scoring qualifies. 4. Variant F is verification-pending — log PF/WR vs Q1 baseline, compare to Q1-step5 0-BUY failure mode.</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="60" customHeight="1">
+          <t>python3 swing_trade.py deep AAPL → check that stop value ≤ indicators.fractal_low (or within 0.10×ATR buffer below it). NEVER above fractal_low.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="90" customHeight="1">
       <c r="A105" s="2" t="n">
         <v>104</v>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>GATE-1</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
@@ -5952,37 +5976,37 @@
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>Quant / Stop Engine</t>
+          <t>Quant / Validation</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>Stop must be at/below nearest fractal low</t>
+          <t>Validation backtest restart + 0-BUYs investigation</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>Calculated stops sometimes sit ABOVE the nearest Williams-fractal low — guaranteed easy stop-out target for market makers.</t>
+          <t>First validation backtest (PID 25081) died at 2024-01-04 with 0 BUYs in 8 months. Restart (PID 29239) currently running showing same pattern — QUANT-1 config (Trend Continuation killed) appears to starve the system of trades.</t>
         </is>
       </c>
       <c r="G105" s="5" t="inlineStr">
         <is>
-          <t>If stop &gt; indicators['fractal_low'] (already computed in _williams_fractals at analysis.py:1089), widen DOWN to just below fractal low + 0.10×ATR buffer. Bounded: won't widen &gt;20% from entry.</t>
+          <t>Restarted backtest at 22:48 PT (PID 29239). When done: if PF &gt;= 1.0 → ship QUANT-1b (buy_max_score=80). If 0 BUYs persists → revert TC kill or apply soft demote (mult 0.5) instead of hard kill.</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>in flight</t>
         </is>
       </c>
       <c r="I105" s="5" t="inlineStr">
         <is>
-          <t>Win: single most important Vinod rule per coaching call.</t>
+          <t>Risk: confirmation that TC kill removed all profitable signals along with the bad ones.</t>
         </is>
       </c>
       <c r="J105" s="5" t="inlineStr">
         <is>
-          <t>Longs only. Sanity-bounded to prevent bad fractal detection from blowing out stops.</t>
+          <t>Validation backtest ran ~1.5h before being killed; conclusive evidence: 0 BUYs across 3+ simulated months Jan-Apr 2024 with QUANT-1 config. Confirms Trend Continuation full-kill is over-aggressive — A5-followup analysis of signal_log shows TC has WR 41.4% / avg +2.08% over n=140 closed signals (positive expectancy). Reverting in A5-followup commit.</t>
         </is>
       </c>
       <c r="K105" s="12" t="inlineStr">
@@ -5992,27 +6016,27 @@
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M105" s="3" t="inlineStr">
         <is>
-          <t>3d4eb71d7</t>
+          <t>logs/backtest_750d_quant1_validate2</t>
         </is>
       </c>
       <c r="N105" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep AAPL → check that stop value ≤ indicators.fractal_low (or within 0.10×ATR buffer below it). NEVER above fractal_low.</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="90" customHeight="1">
+          <t>ps -p 29239 → if alive backtest still running. When done: ls cache/portfolio_backtest_750d_*.json | head -1 → check PF, total_return_pct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="75" customHeight="1">
       <c r="A106" s="2" t="n">
         <v>105</v>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>GATE-1</t>
+          <t>KILL-MULT0</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
@@ -6022,39 +6046,27 @@
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>Quant / Validation</t>
+          <t>Scoring/Kill List</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
-          <t>Validation backtest restart + 0-BUYs investigation</t>
+          <t>Kill multiplier mult=0.0 silently dropped in live scoring</t>
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>First validation backtest (PID 25081) died at 2024-01-04 with 0 BUYs in 8 months. Restart (PID 29239) currently running showing same pattern — QUANT-1 config (Trend Continuation killed) appears to starve the system of trades.</t>
+          <t>analysis.py:9366 condition was 'mult &gt; 0' which excluded the kill value. Result: EMA21 Pullback / 52wk Breakout / Variant F TC×bull kills (all evidence-backed n&gt;=30 + wr_lb&lt;0.30) never fired. 53 supposedly-killed BUYs entered signal_log over 2 weeks.</t>
         </is>
       </c>
       <c r="G106" s="5" t="inlineStr">
         <is>
-          <t>Restarted backtest at 22:48 PT (PID 29239). When done: if PF &gt;= 1.0 → ship QUANT-1b (buy_max_score=80). If 0 BUYs persists → revert TC kill or apply soft demote (mult 0.5) instead of hard kill.</t>
-        </is>
-      </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>in flight</t>
-        </is>
-      </c>
-      <c r="I106" s="5" t="inlineStr">
-        <is>
-          <t>Risk: confirmation that TC kill removed all profitable signals along with the bad ones.</t>
-        </is>
-      </c>
-      <c r="J106" s="5" t="inlineStr">
-        <is>
-          <t>Validation backtest ran ~1.5h before being killed; conclusive evidence: 0 BUYs across 3+ simulated months Jan-Apr 2024 with QUANT-1 config. Confirms Trend Continuation full-kill is over-aggressive — A5-followup analysis of signal_log shows TC has WR 41.4% / avg +2.08% over n=140 closed signals (positive expectancy). Reverting in A5-followup commit.</t>
-        </is>
-      </c>
+          <t>Change condition to 'mult &gt;= 0' in analysis.py:9366. Add 'silent no-op' code comment with root-cause reference. Backtest path (backtest.py:418 via apply_setup_wr_multiplier) is separate — wire Variant F into backtest.py:442 as well.</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr"/>
+      <c r="I106" s="5" t="inlineStr"/>
+      <c r="J106" s="5" t="inlineStr"/>
       <c r="K106" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -6067,22 +6079,18 @@
       </c>
       <c r="M106" s="3" t="inlineStr">
         <is>
-          <t>logs/backtest_750d_quant1_validate2</t>
-        </is>
-      </c>
-      <c r="N106" s="8" t="inlineStr">
-        <is>
-          <t>ps -p 29239 → if alive backtest still running. When done: ls cache/portfolio_backtest_750d_*.json | head -1 → check PF, total_return_pct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="75" customHeight="1">
+          <t>0cdb13340</t>
+        </is>
+      </c>
+      <c r="N106" s="8" t="inlineStr"/>
+    </row>
+    <row r="107" ht="45" customHeight="1">
       <c r="A107" s="2" t="n">
         <v>106</v>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>KILL-MULT0</t>
+          <t>VARIANT-F</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
@@ -6092,27 +6100,39 @@
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>Scoring/Kill List</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>Kill multiplier mult=0.0 silently dropped in live scoring</t>
+          <t>Regime-conditional setup_score_multiplier (TC kill in bull only)</t>
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr">
         <is>
-          <t>analysis.py:9366 condition was 'mult &gt; 0' which excluded the kill value. Result: EMA21 Pullback / 52wk Breakout / Variant F TC×bull kills (all evidence-backed n&gt;=30 + wr_lb&lt;0.30) never fired. 53 supposedly-killed BUYs entered signal_log over 2 weeks.</t>
+          <t>250d backtest diagnosis: TC in bull regime n=85, PF 0.55 — 60% of total losses. TC neutral PF 1.75, bear PF 2.68. Global 1.0x averages out and bleeds in bull.</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>Change condition to 'mult &gt;= 0' in analysis.py:9366. Add 'silent no-op' code comment with root-cause reference. Backtest path (backtest.py:418 via apply_setup_wr_multiplier) is separate — wire Variant F into backtest.py:442 as well.</t>
-        </is>
-      </c>
-      <c r="H107" s="2" t="inlineStr"/>
-      <c r="I107" s="5" t="inlineStr"/>
-      <c r="J107" s="5" t="inlineStr"/>
+          <t>New setup_score_multiplier_by_regime config block + analysis.py:8790 lookup. TC: bull=0.0, neutral=1.0, bear=1.5.</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>45 min</t>
+        </is>
+      </c>
+      <c r="I107" s="5" t="inlineStr">
+        <is>
+          <t>High — addresses #1 PF drag</t>
+        </is>
+      </c>
+      <c r="J107" s="5" t="inlineStr">
+        <is>
+          <t>Distinct from QUANT-6. 250d validation backtest stopped by user.</t>
+        </is>
+      </c>
       <c r="K107" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -6125,18 +6145,22 @@
       </c>
       <c r="M107" s="3" t="inlineStr">
         <is>
-          <t>0cdb13340</t>
-        </is>
-      </c>
-      <c r="N107" s="8" t="inlineStr"/>
-    </row>
-    <row r="108" ht="45" customHeight="1">
+          <t>f0a66543e</t>
+        </is>
+      </c>
+      <c r="N107" s="8" t="inlineStr">
+        <is>
+          <t>Verify config has setup_score_multiplier_by_regime. TC ticker score in bull regime should be set to 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="60" customHeight="1">
       <c r="A108" s="2" t="n">
         <v>107</v>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>VARIANT-F</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
@@ -6146,37 +6170,37 @@
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Strategy / Filter Layer</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
         <is>
-          <t>Regime-conditional setup_score_multiplier (TC kill in bull only)</t>
+          <t>signal_filter.py — declarative whitelist gate</t>
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>250d backtest diagnosis: TC in bull regime n=85, PF 0.55 — 60% of total losses. TC neutral PF 1.75, bear PF 2.68. Global 1.0x averages out and bleeds in bull.</t>
+          <t>BUY decisions ran on raw 5-pillar score regardless of whether the (setup × regime × score_band × entry_quality) combo had backtest evidence behind it.</t>
         </is>
       </c>
       <c r="G108" s="5" t="inlineStr">
         <is>
-          <t>New setup_score_multiplier_by_regime config block + analysis.py:8790 lookup. TC: bull=0.0, neutral=1.0, bear=1.5.</t>
+          <t>New signal_filter.py — demotes BUY→WATCH for non-whitelisted combos. _validations gate enforces n&gt;=20 AND wr_lb&gt;=0.40 per rule. Wired at decision_engine.py:626 after BUY threshold passes. 5/5 unit tests pass.</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I108" s="5" t="inlineStr">
         <is>
-          <t>High — addresses #1 PF drag</t>
+          <t>Win: prevents BUY in unproven combos. OFF by default until A5 attribution complete.</t>
         </is>
       </c>
       <c r="J108" s="5" t="inlineStr">
         <is>
-          <t>Distinct from QUANT-6. 250d validation backtest stopped by user.</t>
+          <t>Flip config['signal_filter']['_enabled']=true after per-subtype A5 attribution review.</t>
         </is>
       </c>
       <c r="K108" s="12" t="inlineStr">
@@ -6186,17 +6210,17 @@
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M108" s="3" t="inlineStr">
         <is>
-          <t>f0a66543e</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N108" s="8" t="inlineStr">
         <is>
-          <t>Verify config has setup_score_multiplier_by_regime. TC ticker score in bull regime should be set to 0.</t>
+          <t>1) cat config/config.json | grep -A3 signal_filter → confirm _enabled=false. 2) Toggle to true via --config-override → run scan → BUY count drops. Toggle off → restored.</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6230,7 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
@@ -6221,17 +6245,17 @@
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>signal_filter.py — declarative whitelist gate</t>
+          <t>Regime gate in compute_final_verdict</t>
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
-          <t>BUY decisions ran on raw 5-pillar score regardless of whether the (setup × regime × score_band × entry_quality) combo had backtest evidence behind it.</t>
+          <t>750d evidence: strategy is bull-only. risk_off_trending and panic regimes returned negative expectancy.</t>
         </is>
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
-          <t>New signal_filter.py — demotes BUY→WATCH for non-whitelisted combos. _validations gate enforces n&gt;=20 AND wr_lb&gt;=0.40 per rule. Wired at decision_engine.py:626 after BUY threshold passes. 5/5 unit tests pass.</t>
+          <t>compute_final_verdict refuses new BUY in regime ∈ {risk_off_trending, panic}. Returns verdict=WATCH with audit gate 'regime_gate' failed. Sits BEFORE _eval_hard_gates so it's the first decision after circuit-breakers.</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6241,12 +6265,12 @@
       </c>
       <c r="I109" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents BUY in unproven combos. OFF by default until A5 attribution complete.</t>
+          <t>Win: bull-only strategy, period.</t>
         </is>
       </c>
       <c r="J109" s="5" t="inlineStr">
         <is>
-          <t>Flip config['signal_filter']['_enabled']=true after per-subtype A5 attribution review.</t>
+          <t>Existing positions unaffected (exits run via separate paths).</t>
         </is>
       </c>
       <c r="K109" s="12" t="inlineStr">
@@ -6261,12 +6285,12 @@
       </c>
       <c r="M109" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N109" s="8" t="inlineStr">
         <is>
-          <t>1) cat config/config.json | grep -A3 signal_filter → confirm _enabled=false. 2) Toggle to true via --config-override → run scan → BUY count drops. Toggle off → restored.</t>
+          <t>Run scan during simulated risk_off regime (set regime via --config-override) → confirm zero BUY verdicts emitted. Audit gate 'regime_gate' marked failed.</t>
         </is>
       </c>
     </row>
@@ -6276,7 +6300,7 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>STRATEGY-TUNE-20260519</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
@@ -6286,39 +6310,27 @@
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Filter Layer</t>
+          <t>Strategy Tuning</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
         <is>
-          <t>Regime gate in compute_final_verdict</t>
+          <t>5 data-backed fixes from 986-trade backtest analysis</t>
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>750d evidence: strategy is bull-only. risk_off_trending and panic regimes returned negative expectancy.</t>
+          <t>Sector blocklist (Energy/BasicMat/ConsumerCyclical/CommServices), FRESH entry block, Impulse Catalyst kill in choppy, score floor 65, MISSED relaxed in trending</t>
         </is>
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>compute_final_verdict refuses new BUY in regime ∈ {risk_off_trending, panic}. Returns verdict=WATCH with audit gate 'regime_gate' failed. Sits BEFORE _eval_hard_gates so it's the first decision after circuit-breakers.</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I110" s="5" t="inlineStr">
-        <is>
-          <t>Win: bull-only strategy, period.</t>
-        </is>
-      </c>
-      <c r="J110" s="5" t="inlineStr">
-        <is>
-          <t>Existing positions unaffected (exits run via separate paths).</t>
-        </is>
-      </c>
+          <t>decision_engine.py + config.json</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr"/>
+      <c r="I110" s="5" t="inlineStr"/>
+      <c r="J110" s="5" t="inlineStr"/>
       <c r="K110" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -6326,27 +6338,23 @@
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M110" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
-        </is>
-      </c>
-      <c r="N110" s="8" t="inlineStr">
-        <is>
-          <t>Run scan during simulated risk_off regime (set regime via --config-override) → confirm zero BUY verdicts emitted. Audit gate 'regime_gate' marked failed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="60" customHeight="1">
+          <t>29578a5fb</t>
+        </is>
+      </c>
+      <c r="N110" s="8" t="inlineStr"/>
+    </row>
+    <row r="111" ht="75" customHeight="1">
       <c r="A111" s="2" t="n">
         <v>110</v>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>STRATEGY-TUNE-20260519</t>
+          <t>TARGET-CAP-10WK</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
@@ -6356,22 +6364,22 @@
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>Strategy Tuning</t>
+          <t>Strategy/Target Sanity</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>5 data-backed fixes from 986-trade backtest analysis</t>
+          <t>weekly_pullback target1 uncapped — anomalous spikes poison trade plan</t>
         </is>
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
-          <t>Sector blocklist (Energy/BasicMat/ConsumerCyclical/CommServices), FRESH entry block, Impulse Catalyst kill in choppy, score floor 65, MISSED relaxed in trending</t>
+          <t>weekly_pullback.py:226 set target1 = float(high.iloc[-20:].max()) with NO entry-relative cap. CAR (Avis) intraday spike to $847.70 on 04-22 entered the 20-bar window on 04-28, producing 9 straight losing entries with target1=$847.70 (RR 10+, stop hit, -10% loss each). Root cause of 12.7% BUY WR collapse in signal_log.</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
-          <t>decision_engine.py + config.json</t>
+          <t>Cap target1 at entry * 1.15 (aligns with 7-14d hold horizon). Validated against 9 historical CAR entries: 6 of 9 would have failed buy_min_rr=3.0 gate → not entered.</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr"/>
@@ -6384,23 +6392,23 @@
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M111" s="3" t="inlineStr">
         <is>
-          <t>29578a5fb</t>
+          <t>87336f2de</t>
         </is>
       </c>
       <c r="N111" s="8" t="inlineStr"/>
     </row>
-    <row r="112" ht="75" customHeight="1">
+    <row r="112" ht="45" customHeight="1">
       <c r="A112" s="2" t="n">
         <v>111</v>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>TARGET-CAP-10WK</t>
+          <t>STOCKSMITH-MODE-CASCADE</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
@@ -6410,22 +6418,22 @@
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>Strategy/Target Sanity</t>
+          <t>V2 Dashboard / Detail</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
         <is>
-          <t>weekly_pullback target1 uncapped — anomalous spikes poison trade plan</t>
+          <t>Global SWING/POSITION/INVESTMENT mode cascade (§5,A,B)</t>
         </is>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>weekly_pullback.py:226 set target1 = float(high.iloc[-20:].max()) with NO entry-relative cap. CAR (Avis) intraday spike to $847.70 on 04-22 entered the 20-bar window on 04-28, producing 9 straight losing entries with target1=$847.70 (RR 10+, stop hit, -10% loss each). Root cause of 12.7% BUY WR collapse in signal_log.</t>
+          <t>mode drives Overview/Plan/Risk-cones/AI-Edge/Chart-TF/Options-DTE + cross-mode + defensive tape + projection; window.__tmode</t>
         </is>
       </c>
       <c r="G112" s="5" t="inlineStr">
         <is>
-          <t>Cap target1 at entry * 1.15 (aligns with 7-14d hold horizon). Validated against 9 historical CAR entries: 6 of 9 would have failed buy_min_rr=3.0 gate → not entered.</t>
+          <t>Stocksmith.html AICrossMode + MODE_TF/MODE_DTE + SmrRiskCones</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr"/>
@@ -6438,12 +6446,12 @@
       </c>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="M112" s="3" t="inlineStr">
         <is>
-          <t>87336f2de</t>
+          <t>eb83a151d</t>
         </is>
       </c>
       <c r="N112" s="8" t="inlineStr"/>
@@ -6454,7 +6462,7 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>STOCKSMITH-MODE-CASCADE</t>
+          <t>STOCKSMITH-AI-CHART</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
@@ -6464,22 +6472,22 @@
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>V2 Dashboard / Detail</t>
+          <t>V2 Dashboard / ML Predictions</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>Global SWING/POSITION/INVESTMENT mode cascade (§5,A,B)</t>
+          <t>AI Price-Projection Chart (§1)</t>
         </is>
       </c>
       <c r="F113" s="5" t="inlineStr">
         <is>
-          <t>mode drives Overview/Plan/Risk-cones/AI-Edge/Chart-TF/Options-DTE + cross-mode + defensive tape + projection; window.__tmode</t>
+          <t>candlestick chart MA20/50/200 + swing dots + breakout box + mode-aware forward AI zone/target; real OHLCV + /api/ml quantiles; AI Edge + Patterns</t>
         </is>
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
-          <t>Stocksmith.html AICrossMode + MODE_TF/MODE_DTE + SmrRiskCones</t>
+          <t>Stocksmith.html AIProjectionChart</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr"/>
@@ -6497,7 +6505,7 @@
       </c>
       <c r="M113" s="3" t="inlineStr">
         <is>
-          <t>eb83a151d</t>
+          <t>a5dcb06c9</t>
         </is>
       </c>
       <c r="N113" s="8" t="inlineStr"/>
@@ -6508,7 +6516,7 @@
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>STOCKSMITH-AI-CHART</t>
+          <t>STOCKSMITH-OPTIONS-CALC</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
@@ -6518,22 +6526,22 @@
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>V2 Dashboard / ML Predictions</t>
+          <t>V2 Dashboard / Options</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
         <is>
-          <t>AI Price-Projection Chart (§1)</t>
+          <t>Options Profit Calculator grid + manual mode/presets (§2+§8)</t>
         </is>
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>candlestick chart MA20/50/200 + swing dots + breakout box + mode-aware forward AI zone/target; real OHLCV + /api/ml quantiles; AI Edge + Patterns</t>
+          <t>%-return-on-premium heatmap, IV-shift + ER crush, 6 strategy presets, BS pricer; real Schwab spot/IV/DTE</t>
         </is>
       </c>
       <c r="G114" s="5" t="inlineStr">
         <is>
-          <t>Stocksmith.html AIProjectionChart</t>
+          <t>Stocksmith.html OtkProfitGrid + eoBuildOptTicket</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr"/>
@@ -6551,7 +6559,7 @@
       </c>
       <c r="M114" s="3" t="inlineStr">
         <is>
-          <t>a5dcb06c9</t>
+          <t>932cef7fe</t>
         </is>
       </c>
       <c r="N114" s="8" t="inlineStr"/>
@@ -6562,32 +6570,32 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>STOCKSMITH-OPTIONS-CALC</t>
-        </is>
-      </c>
-      <c r="C115" s="4" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>PICK-FORENSICS</t>
+        </is>
+      </c>
+      <c r="C115" s="9" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>V2 Dashboard / Options</t>
+          <t>Audit / Attribution</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
-          <t>Options Profit Calculator grid + manual mode/presets (§2+§8)</t>
+          <t>Why did BUY lose / AVOID win — per-pick post-mortem</t>
         </is>
       </c>
       <c r="F115" s="5" t="inlineStr">
         <is>
-          <t>%-return-on-premium heatmap, IV-shift + ER crush, 6 strategy presets, BS pricer; real Schwab spot/IV/DTE</t>
+          <t>join decision verdict+gates x realized outcome x setup-regime stats; aggregate where calls fail</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>Stocksmith.html OtkProfitGrid + eoBuildOptTicket</t>
+          <t>scripts/pick_forensics.py + dashboard tab</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr"/>
@@ -6600,23 +6608,23 @@
       </c>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="M115" s="3" t="inlineStr">
         <is>
-          <t>932cef7fe</t>
+          <t>5e6375889</t>
         </is>
       </c>
       <c r="N115" s="8" t="inlineStr"/>
     </row>
-    <row r="116" ht="45" customHeight="1">
+    <row r="116" ht="75" customHeight="1">
       <c r="A116" s="2" t="n">
         <v>115</v>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>PICK-FORENSICS</t>
+          <t>AUDIT-PENDING-UX</t>
         </is>
       </c>
       <c r="C116" s="9" t="inlineStr">
@@ -6626,22 +6634,22 @@
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>Audit / Attribution</t>
+          <t>Audit Trail / Maturation UX</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
         <is>
-          <t>Why did BUY lose / AVOID win — per-pick post-mortem</t>
+          <t>Pending rows handled cleanly · maturation chip · refresh button · TTL cache</t>
         </is>
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>join decision verdict+gates x realized outcome x setup-regime stats; aggregate where calls fail</t>
+          <t>Records with no matured horizon get faded 50% opacity + 🕓 prefix. Default 'Hide Pending' filter ON so user opens to actionable data. Manual ↻ Refresh button busts cache. 5-min TTL on _ledgerCache so backend rebuilds become visible without page reload. Toolbar shows N matured · K pending · generated Nm ago</t>
         </is>
       </c>
       <c r="G116" s="5" t="inlineStr">
         <is>
-          <t>scripts/pick_forensics.py + dashboard tab</t>
+          <t>kairos.html QuantHistoryLedger _filters.hidePending + _qauditTogglePending + _qauditForceRefresh + qhist-pending CSS class</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr"/>
@@ -6654,12 +6662,12 @@
       </c>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="M116" s="3" t="inlineStr">
         <is>
-          <t>5e6375889</t>
+          <t>dfbe955fe</t>
         </is>
       </c>
       <c r="N116" s="8" t="inlineStr"/>
@@ -6670,7 +6678,7 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>AUDIT-PENDING-UX</t>
+          <t>AUDIT-D0-INTRADAY</t>
         </is>
       </c>
       <c r="C117" s="9" t="inlineStr">
@@ -6680,22 +6688,22 @@
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>Audit Trail / Maturation UX</t>
+          <t>Audit Trail / Same-Day Returns</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>Pending rows handled cleanly · maturation chip · refresh button · TTL cache</t>
+          <t>D0 column · same-day entry→close return</t>
         </is>
       </c>
       <c r="F117" s="5" t="inlineStr">
         <is>
-          <t>Records with no matured horizon get faded 50% opacity + 🕓 prefix. Default 'Hide Pending' filter ON so user opens to actionable data. Manual ↻ Refresh button busts cache. 5-min TTL on _ledgerCache so backend rebuilds become visible without page reload. Toolbar shows N matured · K pending · generated Nm ago</t>
+          <t>Today's picks now show real return on same day instead of waiting until tomorrow's close. Computed in build_audit_ledger.py for any pick where price_at_pick differs from anchor close by ≥0.05%. Today: 112/117 May 18 picks show D0 (ZS +8.47%, VRT -8.41%)</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>kairos.html QuantHistoryLedger _filters.hidePending + _qauditTogglePending + _qauditForceRefresh + qhist-pending CSS class</t>
+          <t>infra/prototype/build_audit_ledger.py d0 computation + kairos.html D0 column + DAILY group colspan 7→8</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr"/>
@@ -6718,13 +6726,13 @@
       </c>
       <c r="N117" s="8" t="inlineStr"/>
     </row>
-    <row r="118" ht="75" customHeight="1">
+    <row r="118" ht="60" customHeight="1">
       <c r="A118" s="2" t="n">
         <v>117</v>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>AUDIT-D0-INTRADAY</t>
+          <t>AUDIT-LEDGER-CADENCE</t>
         </is>
       </c>
       <c r="C118" s="9" t="inlineStr">
@@ -6734,22 +6742,22 @@
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>Audit Trail / Same-Day Returns</t>
+          <t>Audit Trail / Scheduled Rebuilds</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
         <is>
-          <t>D0 column · same-day entry→close return</t>
+          <t>Multi-time-of-day ledger rebuild</t>
         </is>
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>Today's picks now show real return on same day instead of waiting until tomorrow's close. Computed in build_audit_ledger.py for any pick where price_at_pick differs from anchor close by ≥0.05%. Today: 112/117 May 18 picks show D0 (ZS +8.47%, VRT -8.41%)</t>
+          <t>Three new launchd jobs · 9/11/3 PM PT intraday · 1:30 PM PT post-close · combined with the existing 6:30 AM morning briefing's audit rebuild. Yesterday's D1 fills 30 min after today's close. Today's D0 updates every 2hrs intraday</t>
         </is>
       </c>
       <c r="G118" s="5" t="inlineStr">
         <is>
-          <t>infra/prototype/build_audit_ledger.py d0 computation + kairos.html D0 column + DAILY group colspan 7→8</t>
+          <t>infra/launchd/com.swingtrade.audit-ledger-eod.plist + .audit-ledger-intraday.plist</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr"/>
@@ -6772,13 +6780,13 @@
       </c>
       <c r="N118" s="8" t="inlineStr"/>
     </row>
-    <row r="119" ht="60" customHeight="1">
+    <row r="119" ht="75" customHeight="1">
       <c r="A119" s="2" t="n">
         <v>118</v>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>AUDIT-LEDGER-CADENCE</t>
+          <t>AUTO-STOP-FLATTEN</t>
         </is>
       </c>
       <c r="C119" s="9" t="inlineStr">
@@ -6788,22 +6796,22 @@
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>Audit Trail / Scheduled Rebuilds</t>
+          <t>Automation</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
         <is>
-          <t>Multi-time-of-day ledger rebuild</t>
+          <t>Auto-engine past-stop flatten</t>
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
-          <t>Three new launchd jobs · 9/11/3 PM PT intraday · 1:30 PM PT post-close · combined with the existing 6:30 AM morning briefing's audit rebuild. Yesterday's D1 fills 30 min after today's close. Today's D0 updates every 2hrs intraday</t>
+          <t>Protective-stop placement emitted structurally-invalid StopOrderRequest when price had already breached the stop (long last&lt;=stop / short last&gt;=stop); Alpaca rejected it and the position was left naked (NEM short Jun-2/Jun-4, AFRM/RVTY Jun-2).</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
-          <t>infra/launchd/com.swingtrade.audit-ledger-eod.plist + .audit-ledger-intraday.plist</t>
+          <t>Added PAST-STOP GUARD in auto_engine.py exit loop block 5a: if price past stop, market-close (flatten) via close_position instead of submitting invalid stop; Slack AUTO-STOP-HIT alert; logged as CLOSE. Validated against 5 historical cases.</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr"/>
@@ -6816,23 +6824,23 @@
       </c>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="M119" s="3" t="inlineStr">
         <is>
-          <t>dfbe955fe</t>
+          <t>033e2b1a8</t>
         </is>
       </c>
       <c r="N119" s="8" t="inlineStr"/>
     </row>
-    <row r="120" ht="75" customHeight="1">
+    <row r="120" ht="60" customHeight="1">
       <c r="A120" s="2" t="n">
         <v>119</v>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>AUTO-STOP-FLATTEN</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="C120" s="9" t="inlineStr">
@@ -6842,27 +6850,39 @@
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>Automation</t>
+          <t>Backtest / Diagnosis</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr">
         <is>
-          <t>Auto-engine past-stop flatten</t>
+          <t>Diagnose --as-of-membership n_trades=0 bug</t>
         </is>
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>Protective-stop placement emitted structurally-invalid StopOrderRequest when price had already breached the stop (long last&lt;=stop / short last&gt;=stop); Alpaca rejected it and the position was left naked (NEM short Jun-2/Jun-4, AFRM/RVTY Jun-2).</t>
+          <t>Walk-forward runs with --as-of-membership universe (~1000 tickers) returned n_trades=0 even though universe loader works correctly.</t>
         </is>
       </c>
       <c r="G120" s="5" t="inlineStr">
         <is>
-          <t>Added PAST-STOP GUARD in auto_engine.py exit loop block 5a: if price past stop, market-close (flatten) via close_position instead of submitting invalid stop; Slack AUTO-STOP-HIT alert; logged as CLOSE. Validated against 5 historical cases.</t>
-        </is>
-      </c>
-      <c r="H120" s="2" t="inlineStr"/>
-      <c r="I120" s="5" t="inlineStr"/>
-      <c r="J120" s="5" t="inlineStr"/>
+          <t>diagnose_as_of_membership.py — script captures findings. Root cause documented in SESSION_HANDOFF section 9. Downstream pipeline bug — universe loaded fine but analysis filtered everything out.</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>shipped (diagnosis); pending (fix)</t>
+        </is>
+      </c>
+      <c r="I120" s="5" t="inlineStr">
+        <is>
+          <t>Win: known root cause; fix will unblock historical backtesting at scale.</t>
+        </is>
+      </c>
+      <c r="J120" s="5" t="inlineStr">
+        <is>
+          <t>Fix deferred until standalone 750d backtest finishes.</t>
+        </is>
+      </c>
       <c r="K120" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -6870,23 +6890,27 @@
       </c>
       <c r="L120" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M120" s="3" t="inlineStr">
         <is>
-          <t>033e2b1a8</t>
-        </is>
-      </c>
-      <c r="N120" s="8" t="inlineStr"/>
-    </row>
-    <row r="121" ht="60" customHeight="1">
+          <t>9bc015562</t>
+        </is>
+      </c>
+      <c r="N120" s="8" t="inlineStr">
+        <is>
+          <t>cat diagnose_as_of_membership.py output OR re-run: python3 diagnose_as_of_membership.py → '88.3% OHLCV coverage' confirmed; bug elsewhere in pipeline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="105" customHeight="1">
       <c r="A121" s="2" t="n">
         <v>120</v>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>BACKTEST-MTM-CLOSE</t>
         </is>
       </c>
       <c r="C121" s="9" t="inlineStr">
@@ -6896,37 +6920,37 @@
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>Backtest / Diagnosis</t>
+          <t>Backtest infra</t>
         </is>
       </c>
       <c r="E121" s="6" t="inlineStr">
         <is>
-          <t>Diagnose --as-of-membership n_trades=0 bug</t>
+          <t>Backtest closes unexited positions at 0% pnl instead of MTM</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
-          <t>Walk-forward runs with --as-of-membership universe (~1000 tickers) returned n_trades=0 even though universe loader works correctly.</t>
+          <t>When a backtest window ends with positions still open (no stop/target hit), those trades are recorded with pnl_pct=0.0 instead of actual mark-to-market. Discovered 2026-05-11 via WF: F3 (Oct-Dec 2025) and F4 (Jul-Oct 2025) each had only 4 'trades' — all entered day 1, exited window end, pnl=0%. They were positions held throughout the window that never hit exit conditions; the backtest closed them at 0% instead of realizing MTM.</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
-          <t>diagnose_as_of_membership.py — script captures findings. Root cause documented in SESSION_HANDOFF section 9. Downstream pipeline bug — universe loaded fine but analysis filtered everything out.</t>
+          <t>In run_portfolio_backtest end-of-window cleanup: compute exit_price as the window's last close for each ticker, then compute pnl_pct properly. Add exit_reason='end_of_backtest_mtm' for traceability. Don't drop these trades from stats.</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>shipped (diagnosis); pending (fix)</t>
+          <t>1-2 hrs</t>
         </is>
       </c>
       <c r="I121" s="5" t="inlineStr">
         <is>
-          <t>Win: known root cause; fix will unblock historical backtesting at scale.</t>
+          <t>Medium / Medium — exposes hidden long-hold edge that current logic masks</t>
         </is>
       </c>
       <c r="J121" s="5" t="inlineStr">
         <is>
-          <t>Fix deferred until standalone 750d backtest finishes.</t>
+          <t>Root cause: backtest.py:1603 day_bars.empty path skipped past the current_price update. Positions held through data gaps had current_price stuck at entry_price forever, so end-of-backtest MTM reported pnl=0.0%. Fix: when day_bars empty, look up last available close from df[df.index &lt;= date_ts] and update current_price. End-of-backtest exit_reason still 'end_of_backtest' but pnl is now actual MTM not 0%.</t>
         </is>
       </c>
       <c r="K121" s="12" t="inlineStr">
@@ -6936,27 +6960,27 @@
       </c>
       <c r="L121" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M121" s="3" t="inlineStr">
         <is>
-          <t>9bc015562</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N121" s="8" t="inlineStr">
         <is>
-          <t>cat diagnose_as_of_membership.py output OR re-run: python3 diagnose_as_of_membership.py → '88.3% OHLCV coverage' confirmed; bug elsewhere in pipeline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="105" customHeight="1">
+          <t>Re-run F3 or F4 window (e.g. --days 50 --end-date 2025-12-31). Phantom trades should now show real pnl_pct based on entry vs window-end close, not 0.0%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="45" customHeight="1">
       <c r="A122" s="2" t="n">
         <v>121</v>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>BACKTEST-MTM-CLOSE</t>
+          <t>PERF-OPT-1</t>
         </is>
       </c>
       <c r="C122" s="9" t="inlineStr">
@@ -6966,37 +6990,37 @@
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>Backtest infra</t>
+          <t>Backtest performance</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
-          <t>Backtest closes unexited positions at 0% pnl instead of MTM</t>
+          <t>backtest.py --smoke (5d quick-validate mode)</t>
         </is>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>When a backtest window ends with positions still open (no stop/target hit), those trades are recorded with pnl_pct=0.0 instead of actual mark-to-market. Discovered 2026-05-11 via WF: F3 (Oct-Dec 2025) and F4 (Jul-Oct 2025) each had only 4 'trades' — all entered day 1, exited window end, pnl=0%. They were positions held throughout the window that never hit exit conditions; the backtest closed them at 0% instead of realizing MTM.</t>
+          <t>Validating config changes required full 60d run (~12 min). Bad iteration loop.</t>
         </is>
       </c>
       <c r="G122" s="5" t="inlineStr">
         <is>
-          <t>In run_portfolio_backtest end-of-window cleanup: compute exit_price as the window's last close for each ticker, then compute pnl_pct properly. Add exit_reason='end_of_backtest_mtm' for traceability. Don't drop these trades from stats.</t>
+          <t>Added --smoke flag: 5d window, top-100 universe by avg dollar vol, auto-portfolio. Runs in &lt;60s. Use to catch config bugs BEFORE long runs.</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>1-2 hrs</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="I122" s="5" t="inlineStr">
         <is>
-          <t>Medium / Medium — exposes hidden long-hold edge that current logic masks</t>
+          <t>Low risk / High win</t>
         </is>
       </c>
       <c r="J122" s="5" t="inlineStr">
         <is>
-          <t>Root cause: backtest.py:1603 day_bars.empty path skipped past the current_price update. Positions held through data gaps had current_price stuck at entry_price forever, so end-of-backtest MTM reported pnl=0.0%. Fix: when day_bars empty, look up last available close from df[df.index &lt;= date_ts] and update current_price. End-of-backtest exit_reason still 'end_of_backtest' but pnl is now actual MTM not 0%.</t>
+          <t>Shipped 2026-05-10.</t>
         </is>
       </c>
       <c r="K122" s="12" t="inlineStr">
@@ -7006,7 +7030,7 @@
       </c>
       <c r="L122" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M122" s="3" t="inlineStr">
@@ -7016,7 +7040,7 @@
       </c>
       <c r="N122" s="8" t="inlineStr">
         <is>
-          <t>Re-run F3 or F4 window (e.g. --days 50 --end-date 2025-12-31). Phantom trades should now show real pnl_pct based on entry vs window-end close, not 0.0%.</t>
+          <t>python3 backtest.py --smoke → completes &lt;60s, prints summary, no errors. Tweak setup_score_multiplier in config.json, re-run, observe BUY count change.</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7050,7 @@
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-1</t>
+          <t>PERF-OPT-2</t>
         </is>
       </c>
       <c r="C123" s="9" t="inlineStr">
@@ -7041,22 +7065,22 @@
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
-          <t>backtest.py --smoke (5d quick-validate mode)</t>
+          <t>yfinance info disk cache (24h TTL)</t>
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>Validating config changes required full 60d run (~12 min). Bad iteration loop.</t>
+          <t>Re-running backtest re-fetched 711 ticker info dicts from yfinance every time. ~30-60s wasted per run.</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>Added --smoke flag: 5d window, top-100 universe by avg dollar vol, auto-portfolio. Runs in &lt;60s. Use to catch config bugs BEFORE long runs.</t>
+          <t>_load_or_fetch_infos_cached() wraps get_stock_info_batch with disk cache keyed by sorted-universe SHA1 hash. 24h TTL. Switching universes auto-invalidates.</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="I123" s="5" t="inlineStr">
@@ -7066,7 +7090,7 @@
       </c>
       <c r="J123" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10.</t>
+          <t>Shipped 2026-05-10. Cache files: cache/infos_&lt;sha&gt;.json</t>
         </is>
       </c>
       <c r="K123" s="12" t="inlineStr">
@@ -7086,7 +7110,7 @@
       </c>
       <c r="N123" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --smoke → completes &lt;60s, prints summary, no errors. Tweak setup_score_multiplier in config.json, re-run, observe BUY count change.</t>
+          <t>Run backtest twice in a row; second run logs "Cached yfinance info hit" and skips fetch.</t>
         </is>
       </c>
     </row>
@@ -7096,7 +7120,7 @@
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-2</t>
+          <t>PERF-OPT-3</t>
         </is>
       </c>
       <c r="C124" s="9" t="inlineStr">
@@ -7111,32 +7135,32 @@
       </c>
       <c r="E124" s="6" t="inlineStr">
         <is>
-          <t>yfinance info disk cache (24h TTL)</t>
+          <t>backtest.py --profile-cprof (cProfile hotspot audit)</t>
         </is>
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>Re-running backtest re-fetched 711 ticker info dicts from yfinance every time. ~30-60s wasted per run.</t>
+          <t>No data on actual backtest hot paths — all optimization was guesswork.</t>
         </is>
       </c>
       <c r="G124" s="5" t="inlineStr">
         <is>
-          <t>_load_or_fetch_infos_cached() wraps get_stock_info_batch with disk cache keyed by sorted-universe SHA1 hash. 24h TTL. Switching universes auto-invalidates.</t>
+          <t>Added --profile-cprof flag. Wraps main() in cProfile.Profile(); writes top-50 cumulative-time entries to cache/logs/backtest_cprofile_&lt;ts&gt;.txt.</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="I124" s="5" t="inlineStr">
         <is>
-          <t>Low risk / High win</t>
+          <t>Low risk / High win (evidence-based opt)</t>
         </is>
       </c>
       <c r="J124" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10. Cache files: cache/infos_&lt;sha&gt;.json</t>
+          <t>Shipped 2026-05-10.</t>
         </is>
       </c>
       <c r="K124" s="12" t="inlineStr">
@@ -7156,17 +7180,17 @@
       </c>
       <c r="N124" s="8" t="inlineStr">
         <is>
-          <t>Run backtest twice in a row; second run logs "Cached yfinance info hit" and skips fetch.</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="45" customHeight="1">
+          <t>python3 backtest.py --smoke --profile-cprof → check cache/logs/backtest_cprofile_*.txt; should list top 50 functions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="60" customHeight="1">
       <c r="A125" s="2" t="n">
         <v>124</v>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-3</t>
+          <t>PERF-OPT-4</t>
         </is>
       </c>
       <c r="C125" s="9" t="inlineStr">
@@ -7181,32 +7205,32 @@
       </c>
       <c r="E125" s="6" t="inlineStr">
         <is>
-          <t>backtest.py --profile-cprof (cProfile hotspot audit)</t>
+          <t>walk_forward_v2 fold parallelization (--parallel)</t>
         </is>
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>No data on actual backtest hot paths — all optimization was guesswork.</t>
+          <t>4-fold walk-forward ran sequentially: ~8-12h wall-clock. Bottleneck was wall-clock waiting, not CPU.</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>Added --profile-cprof flag. Wraps main() in cProfile.Profile(); writes top-50 cumulative-time entries to cache/logs/backtest_cprofile_&lt;ts&gt;.txt.</t>
+          <t>Added --parallel + --workers flags. multiprocessing.Pool with spawn-mode (macOS-safe). Each fold runs as separate process. Cuts 4-fold WF from 8-12h to 2-3h.</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I125" s="5" t="inlineStr">
         <is>
-          <t>Low risk / High win (evidence-based opt)</t>
+          <t>Low risk / Massive time savings</t>
         </is>
       </c>
       <c r="J125" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10.</t>
+          <t>Shipped 2026-05-10. EODHD rate-limit (~14/sec burst) caps useful parallelism at ~4 workers; explicitly capped via --workers default.</t>
         </is>
       </c>
       <c r="K125" s="12" t="inlineStr">
@@ -7226,17 +7250,17 @@
       </c>
       <c r="N125" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --smoke --profile-cprof → check cache/logs/backtest_cprofile_*.txt; should list top 50 functions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="60" customHeight="1">
+          <t>python3 backtest/walk_forward_v2.py --folds 4 --train-days 250 --test-days 50 --parallel → log shows "Parallel walk-forward ON" and folds run concurrently. Compare wall-clock vs sequential.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="105" customHeight="1">
       <c r="A126" s="2" t="n">
         <v>125</v>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-4</t>
+          <t>BULLVEDA-FUNNEL-MARKETGATE</t>
         </is>
       </c>
       <c r="C126" s="9" t="inlineStr">
@@ -7246,39 +7270,27 @@
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>Backtest performance</t>
+          <t>BullVeda / Home</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
         <is>
-          <t>walk_forward_v2 fold parallelization (--parallel)</t>
+          <t>Scan funnel paints whole universe bearish on market-gate days</t>
         </is>
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>4-fold walk-forward ran sequentially: ~8-12h wall-clock. Bottleneck was wall-clock waiting, not CPU.</t>
+          <t>On a market-wide entry-gate day (SPY -2.6% + 7 distribution days, 2026-06-08) the Home scan funnel showed 0 bullish / 0 neutral / 1000 avoid: realFunnel read decisions_by_mode (stamped AVOID on every gate-blocked name) and the universe tile read scan_count from the empty all_scored list. Engine was correct (no new longs on a crash day); the dashboard misrepresented it as universe-wide bearishness.</t>
         </is>
       </c>
       <c r="G126" s="5" t="inlineStr">
         <is>
-          <t>Added --parallel + --workers flags. multiprocessing.Pool with spawn-mode (macOS-safe). Each fold runs as separate process. Cuts 4-fold WF from 8-12h to 2-3h.</t>
-        </is>
-      </c>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>1 hr</t>
-        </is>
-      </c>
-      <c r="I126" s="5" t="inlineStr">
-        <is>
-          <t>Low risk / Massive time savings</t>
-        </is>
-      </c>
-      <c r="J126" s="5" t="inlineStr">
-        <is>
-          <t>Shipped 2026-05-10. EODHD rate-limit (~14/sec burst) caps useful parallelism at ~4 workers; explicitly capped via --workers default.</t>
-        </is>
-      </c>
+          <t>realFunnel un-collapses entry-gate AVOIDs to the composite verdict + adds a 'no new longs today' banner (committed 57df99939/eb960bde8); build_data.py scan_count = len(all_scored)+len(killed); served data.critical.json scan_count patched 0-&gt;1000.</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr"/>
+      <c r="I126" s="5" t="inlineStr"/>
+      <c r="J126" s="5" t="inlineStr"/>
       <c r="K126" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -7286,27 +7298,23 @@
       </c>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="M126" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N126" s="8" t="inlineStr">
-        <is>
-          <t>python3 backtest/walk_forward_v2.py --folds 4 --train-days 250 --test-days 50 --parallel → log shows "Parallel walk-forward ON" and folds run concurrently. Compare wall-clock vs sequential.</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="105" customHeight="1">
+          <t>eb960bde8</t>
+        </is>
+      </c>
+      <c r="N126" s="8" t="inlineStr"/>
+    </row>
+    <row r="127" ht="45" customHeight="1">
       <c r="A127" s="2" t="n">
         <v>126</v>
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>BULLVEDA-FUNNEL-MARKETGATE</t>
+          <t>PEAD-7</t>
         </is>
       </c>
       <c r="C127" s="9" t="inlineStr">
@@ -7316,22 +7324,22 @@
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>BullVeda / Home</t>
+          <t>Choice C Strategy</t>
         </is>
       </c>
       <c r="E127" s="6" t="inlineStr">
         <is>
-          <t>Scan funnel paints whole universe bearish on market-gate days</t>
+          <t>PEAD data pipeline</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>On a market-wide entry-gate day (SPY -2.6% + 7 distribution days, 2026-06-08) the Home scan funnel showed 0 bullish / 0 neutral / 1000 avoid: realFunnel read decisions_by_mode (stamped AVOID on every gate-blocked name) and the universe tile read scan_count from the empty all_scored list. Engine was correct (no new longs on a crash day); the dashboard misrepresented it as universe-wide bearishness.</t>
+          <t>Wire EODHD past-earnings surprise + post-report gap</t>
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>realFunnel un-collapses entry-gate AVOIDs to the composite verdict + adds a 'no new longs today' banner (committed 57df99939/eb960bde8); build_data.py scan_count = len(all_scored)+len(killed); served data.critical.json scan_count patched 0-&gt;1000.</t>
+          <t>data_fetcher._load_recent_earnings_surprises_global + _compute_post_report_gap_pct; revenue + analyst-revision gates relaxed (data not plumbed yet)</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr"/>
@@ -7344,23 +7352,23 @@
       </c>
       <c r="L127" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="M127" s="3" t="inlineStr">
         <is>
-          <t>eb960bde8</t>
+          <t>f089b48ef</t>
         </is>
       </c>
       <c r="N127" s="8" t="inlineStr"/>
     </row>
-    <row r="128" ht="45" customHeight="1">
+    <row r="128" ht="60" customHeight="1">
       <c r="A128" s="2" t="n">
         <v>127</v>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>PEAD-7</t>
+          <t>CLEAN-1</t>
         </is>
       </c>
       <c r="C128" s="9" t="inlineStr">
@@ -7370,27 +7378,39 @@
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>Choice C Strategy</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
         <is>
-          <t>PEAD data pipeline</t>
+          <t>backtest_v2.py — keep or delete?</t>
         </is>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>Wire EODHD past-earnings surprise + post-report gap</t>
+          <t>158-line file. docs/architecture.md:191 references as entrypoint but file is abandoned snapshot — likely never run.</t>
         </is>
       </c>
       <c r="G128" s="5" t="inlineStr">
         <is>
-          <t>data_fetcher._load_recent_earnings_surprises_global + _compute_post_report_gap_pct; revenue + analyst-revision gates relaxed (data not plumbed yet)</t>
-        </is>
-      </c>
-      <c r="H128" s="2" t="inlineStr"/>
-      <c r="I128" s="5" t="inlineStr"/>
-      <c r="J128" s="5" t="inlineStr"/>
+          <t>ASK USER: 'Do you ever run backtest_v2.py?' If no → delete + update docs/architecture.md.</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>10 min after answer</t>
+        </is>
+      </c>
+      <c r="I128" s="5" t="inlineStr">
+        <is>
+          <t>Win: -158 lines + clearer docs.</t>
+        </is>
+      </c>
+      <c r="J128" s="5" t="inlineStr">
+        <is>
+          <t>Phase 2 agent flagged but held back without user judgment. · DELETED — was 158-line abandoned snapshot, has_main=0 (not even runnable). Updated docs/architecture.md + morning_briefing.py to remove references.</t>
+        </is>
+      </c>
       <c r="K128" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -7398,23 +7418,27 @@
       </c>
       <c r="L128" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M128" s="3" t="inlineStr">
         <is>
-          <t>f089b48ef</t>
-        </is>
-      </c>
-      <c r="N128" s="8" t="inlineStr"/>
-    </row>
-    <row r="129" ht="60" customHeight="1">
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N128" s="8" t="inlineStr">
+        <is>
+          <t>ls backtest_v2.py → no such file (deleted). docs/architecture.md no longer references it. morning_briefing.py uses cache/logs/backtest_*.log glob.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="90" customHeight="1">
       <c r="A129" s="2" t="n">
         <v>128</v>
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-1</t>
+          <t>CLEAN-3</t>
         </is>
       </c>
       <c r="C129" s="9" t="inlineStr">
@@ -7429,32 +7453,32 @@
       </c>
       <c r="E129" s="6" t="inlineStr">
         <is>
-          <t>backtest_v2.py — keep or delete?</t>
+          <t>8 standalone analysis scripts — ask user which still in use</t>
         </is>
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>158-line file. docs/architecture.md:191 references as entrypoint but file is abandoned snapshot — likely never run.</t>
+          <t>Manual research scripts: audit_360.py (1320 lines!), analyze_backtest.py, analyze_signals.py, false_negatives.py, feature_importance.py, score_distribution_check.py, sensitivity.py, stop_width_sensitivity.py.</t>
         </is>
       </c>
       <c r="G129" s="5" t="inlineStr">
         <is>
-          <t>ASK USER: 'Do you ever run backtest_v2.py?' If no → delete + update docs/architecture.md.</t>
+          <t>ASK USER per file: 'Do you ever run X?' For each 'no' → archive to _legacy/ or delete. ~3-5K lines win.</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>10 min after answer</t>
+          <t>30 min after answers</t>
         </is>
       </c>
       <c r="I129" s="5" t="inlineStr">
         <is>
-          <t>Win: -158 lines + clearer docs.</t>
+          <t>Win: ~3-5K lines if mostly stale.</t>
         </is>
       </c>
       <c r="J129" s="5" t="inlineStr">
         <is>
-          <t>Phase 2 agent flagged but held back without user judgment. · DELETED — was 158-line abandoned snapshot, has_main=0 (not even runnable). Updated docs/architecture.md + morning_briefing.py to remove references.</t>
+          <t>audit_360.py is the biggest single file — start there. · Archived 3 to _legacy/ (analyze_backtest 194 lines, false_negatives 309, stop_width_sensitivity 144 — all 0 active py_refs). KEPT 5 with active references: audit_360 (3 refs, 1320 lines), analyze_signals (2 refs), sensitivity (5 refs), feature_importance (1 ref ML), score_distribution_check (1 ref).</t>
         </is>
       </c>
       <c r="K129" s="12" t="inlineStr">
@@ -7474,17 +7498,17 @@
       </c>
       <c r="N129" s="8" t="inlineStr">
         <is>
-          <t>ls backtest_v2.py → no such file (deleted). docs/architecture.md no longer references it. morning_briefing.py uses cache/logs/backtest_*.log glob.</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="90" customHeight="1">
+          <t>ls _legacy/{analyze_backtest,false_negatives,stop_width_sensitivity}.py → 3 files moved. Verify audit_360.py / analyze_signals.py / sensitivity.py / feature_importance.py / score_distribution_check.py still in root (kept).</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="60" customHeight="1">
       <c r="A130" s="2" t="n">
         <v>129</v>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-3</t>
+          <t>EODHD-RATE-FIX</t>
         </is>
       </c>
       <c r="C130" s="9" t="inlineStr">
@@ -7494,39 +7518,27 @@
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Data / EODHD (rate-limit)</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
         <is>
-          <t>8 standalone analysis scripts — ask user which still in use</t>
+          <t>Per-minute rate-limit fix — enrichment burst</t>
         </is>
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>Manual research scripts: audit_360.py (1320 lines!), analyze_backtest.py, analyze_signals.py, false_negatives.py, feature_importance.py, score_distribution_check.py, sensitivity.py, stop_width_sensitivity.py.</t>
+          <t>max_enrichment_tickers regressed 3000 (was 300/700); deep-enriched ~2500 tickers x ~14 endpoints, bursting EODHD 950/min. Reverted to validated 700. Bulk endpoint + dedup were ALREADY done (brief diagnosis was wrong).</t>
         </is>
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>ASK USER per file: 'Do you ever run X?' For each 'no' → archive to _legacy/ or delete. ~3-5K lines win.</t>
-        </is>
-      </c>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>30 min after answers</t>
-        </is>
-      </c>
-      <c r="I130" s="5" t="inlineStr">
-        <is>
-          <t>Win: ~3-5K lines if mostly stale.</t>
-        </is>
-      </c>
-      <c r="J130" s="5" t="inlineStr">
-        <is>
-          <t>audit_360.py is the biggest single file — start there. · Archived 3 to _legacy/ (analyze_backtest 194 lines, false_negatives 309, stop_width_sensitivity 144 — all 0 active py_refs). KEPT 5 with active references: audit_360 (3 refs, 1320 lines), analyze_signals (2 refs), sensitivity (5 refs), feature_importance (1 ref ML), score_distribution_check (1 ref).</t>
-        </is>
-      </c>
+          <t>config max_enrichment_tickers + job-restructure (cross-process limiter)</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr"/>
+      <c r="I130" s="5" t="inlineStr"/>
+      <c r="J130" s="5" t="inlineStr"/>
       <c r="K130" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -7534,19 +7546,15 @@
       </c>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="M130" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="N130" s="8" t="inlineStr">
-        <is>
-          <t>ls _legacy/{analyze_backtest,false_negatives,stop_width_sensitivity}.py → 3 files moved. Verify audit_360.py / analyze_signals.py / sensitivity.py / feature_importance.py / score_distribution_check.py still in root (kept).</t>
-        </is>
-      </c>
+          <t>0a346032b</t>
+        </is>
+      </c>
+      <c r="N130" s="8" t="inlineStr"/>
     </row>
     <row r="131" ht="60" customHeight="1">
       <c r="A131" s="2" t="n">
@@ -7554,7 +7562,7 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>EODHD-RATE-FIX</t>
+          <t>DATA-WIRE-NO-DEMO</t>
         </is>
       </c>
       <c r="C131" s="9" t="inlineStr">
@@ -7564,22 +7572,22 @@
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>Data / EODHD (rate-limit)</t>
+          <t>Data Wiring</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr">
         <is>
-          <t>Per-minute rate-limit fix — enrichment burst</t>
+          <t>Kill fabrications + wire real fields (no demo data)</t>
         </is>
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>max_enrichment_tickers regressed 3000 (was 300/700); deep-enriched ~2500 tickers x ~14 endpoints, bursting EODHD 950/min. Reverted to validated 700. Bulk endpoint + dedup were ALREADY done (brief diagnosis was wrong).</t>
+          <t>removed AI-chart synthetic candles + DCF synthetic base; wired p_up (ml_edge), revision breadth (earnings_beat), Schwab option Greeks, DCF net-debt, beta, crowding — fallback-safe</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>config max_enrichment_tickers + job-restructure (cross-process limiter)</t>
+          <t>Stocksmith.html + server.py /api/ticker,/api/universe,/api/options</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr"/>
@@ -7597,18 +7605,18 @@
       </c>
       <c r="M131" s="3" t="inlineStr">
         <is>
-          <t>0a346032b</t>
+          <t>1a9103f67</t>
         </is>
       </c>
       <c r="N131" s="8" t="inlineStr"/>
     </row>
-    <row r="132" ht="60" customHeight="1">
+    <row r="132" ht="75" customHeight="1">
       <c r="A132" s="2" t="n">
         <v>131</v>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>DATA-WIRE-NO-DEMO</t>
+          <t>CONGRESS-FLOW-1</t>
         </is>
       </c>
       <c r="C132" s="9" t="inlineStr">
@@ -7618,22 +7626,22 @@
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>Data Wiring</t>
+          <t>Data · Smart Money</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr">
         <is>
-          <t>Kill fabrications + wire real fields (no demo data)</t>
+          <t>Congressional / political-flow tracker</t>
         </is>
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>removed AI-chart synthetic candles + DCF synthetic base; wired p_up (ml_edge), revision breadth (earnings_beat), Schwab option Greeks, DCF net-debt, beta, crowding — fallback-safe</t>
+          <t>Reconnect dead congress feeds (Senate/House Stock Watcher 403, Capitol Trades 429) via multi-source cascade; surface as Congress board + per-ticker Intel tile + Home strip, joined to our verdict</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr">
         <is>
-          <t>Stocksmith.html + server.py /api/ticker,/api/universe,/api/options</t>
+          <t>congress_trades.py (Quiver beta + Capitol + House Clerk + Senate eFD, preserve-on-degrade) -&gt; cache/congressional_picks.json -&gt; /api/congress[/{ticker}] -&gt; SurfaceCongress + surface-signal Sec10 + CongressBuyingStrip; nightly scripts/refresh_congress.py + launchd congress-refresh.plist</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr"/>
@@ -7646,23 +7654,23 @@
       </c>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="M132" s="3" t="inlineStr">
         <is>
-          <t>1a9103f67</t>
+          <t>1bc69ae57</t>
         </is>
       </c>
       <c r="N132" s="8" t="inlineStr"/>
     </row>
-    <row r="133" ht="75" customHeight="1">
+    <row r="133" ht="90" customHeight="1">
       <c r="A133" s="2" t="n">
         <v>132</v>
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>CONGRESS-FLOW-1</t>
+          <t>EODHD-SHARED-LIMITER</t>
         </is>
       </c>
       <c r="C133" s="9" t="inlineStr">
@@ -7672,22 +7680,22 @@
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>Data · Smart Money</t>
+          <t>Data/EODHD</t>
         </is>
       </c>
       <c r="E133" s="6" t="inlineStr">
         <is>
-          <t>Congressional / political-flow tracker</t>
+          <t>Scale daily scan to top 1500 + NASDAQ without aborts</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
-          <t>Reconnect dead congress feeds (Senate/House Stock Watcher 403, Capitol Trades 429) via multi-source cascade; surface as Congress board + per-ticker Intel tile + Home strip, joined to our verdict</t>
+          <t>Per-process EODHD limiter let concurrent jobs burst past 1000/min -&gt; 429s -&gt; 31% fill -&gt; 30% abort guard, silently capping the scan at ~744. Also deep_enrichment_top_n==max_enrichment so deep runs scraped WSB/StockTwits/congressional on all names and stalled.</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>congress_trades.py (Quiver beta + Capitol + House Clerk + Senate eFD, preserve-on-degrade) -&gt; cache/congressional_picks.json -&gt; /api/congress[/{ticker}] -&gt; SurfaceCongress + surface-signal Sec10 + CongressBuyingStrip; nightly scripts/refresh_congress.py + launchd congress-refresh.plist</t>
+          <t>Added cross-process _SharedRateLimiter (flock-backed, one 950/min budget for the whole key, fail-open); raised max_enrichment_tickers 1000-&gt;1500; decoupled deep_enrichment_top_n 1500-&gt;500 so only top 500 get heavy scrapes while 1500 still score. include_nasdaq_all + full-mode already on. Validated: universe 3622 incl NDXall=1000, 91% fill no abort, 1500 scored (1004 passed + 496 killed).</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr"/>
@@ -7700,23 +7708,23 @@
       </c>
       <c r="L133" s="2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="M133" s="3" t="inlineStr">
         <is>
-          <t>1bc69ae57</t>
+          <t>fabb3562f</t>
         </is>
       </c>
       <c r="N133" s="8" t="inlineStr"/>
     </row>
-    <row r="134" ht="90" customHeight="1">
+    <row r="134" ht="75" customHeight="1">
       <c r="A134" s="2" t="n">
         <v>133</v>
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>EODHD-SHARED-LIMITER</t>
+          <t>MODE-1</t>
         </is>
       </c>
       <c r="C134" s="9" t="inlineStr">
@@ -7726,22 +7734,22 @@
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>Data/EODHD</t>
+          <t>Decision Engine</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
         <is>
-          <t>Scale daily scan to top 1500 + NASDAQ without aborts</t>
+          <t>Per-mode SWING/POSITION/INVEST decisions (Option A · Phase 1)</t>
         </is>
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>Per-process EODHD limiter let concurrent jobs burst past 1000/min -&gt; 429s -&gt; 31% fill -&gt; 30% abort guard, silently capping the scan at ~744. Also deep_enrichment_top_n==max_enrichment so deep runs scraped WSB/StockTwits/congressional on all names and stalled.</t>
+          <t>UI mode toggle was cosmetic — t.decision and t.canonical_trade_plan were strategy-agnostic single fields. Toggling SWING/POS/INV in detail header did not change verdict, stop, T1/T2, or R:R. Users with informed conviction couldn't get a mode-specific read.</t>
         </is>
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>Added cross-process _SharedRateLimiter (flock-backed, one 950/min budget for the whole key, fail-open); raised max_enrichment_tickers 1000-&gt;1500; decoupled deep_enrichment_top_n 1500-&gt;500 so only top 500 get heavy scrapes while 1500 still score. include_nasdaq_all + full-mode already on. Validated: universe 3622 incl NDXall=1000, 91% fill no abort, 1500 scored (1004 passed + 496 killed).</t>
+          <t>New _MODE_RULEBOOK + compute_decisions_by_mode() in analysis.py. Each mode applies own stop (1.25/1.75x ATR or -15% DD), R:R floor (3.0/2.5/2.0), entry-quality gate, earnings blackout. Output as t.decisions_by_mode={swing,position,investment}. Frontend reads via _qdStrategyCurrent().</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr"/>
@@ -7754,12 +7762,12 @@
       </c>
       <c r="L134" s="2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M134" s="3" t="inlineStr">
         <is>
-          <t>fabb3562f</t>
+          <t>3e812743</t>
         </is>
       </c>
       <c r="N134" s="8" t="inlineStr"/>
@@ -7770,7 +7778,7 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>MODE-1</t>
+          <t>MODE-2</t>
         </is>
       </c>
       <c r="C135" s="9" t="inlineStr">
@@ -7785,17 +7793,17 @@
       </c>
       <c r="E135" s="6" t="inlineStr">
         <is>
-          <t>Per-mode SWING/POSITION/INVEST decisions (Option A · Phase 1)</t>
+          <t>Per-mode sizing + verdict-divergence explanation (Phase 2)</t>
         </is>
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
-          <t>UI mode toggle was cosmetic — t.decision and t.canonical_trade_plan were strategy-agnostic single fields. Toggling SWING/POS/INV in detail header did not change verdict, stop, T1/T2, or R:R. Users with informed conviction couldn't get a mode-specific read.</t>
+          <t>Per-mode decisions shipped in MODE-1 didn't apply mode-specific size_mult or explain WHY a mode's verdict differed from the legacy single-decision.</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
         <is>
-          <t>New _MODE_RULEBOOK + compute_decisions_by_mode() in analysis.py. Each mode applies own stop (1.25/1.75x ATR or -15% DD), R:R floor (3.0/2.5/2.0), entry-quality gate, earnings blackout. Output as t.decisions_by_mode={swing,position,investment}. Frontend reads via _qdStrategyCurrent().</t>
+          <t>compute_decisions_by_mode() now accepts base_alloc_pct + legacy_decision. Per-mode final_alloc_pct = base × size_mult, capped 5% NAV. New diverge_note field surfaces the exact rule that caused divergence (R:R floor, entry-quality gate, ER blackout). Frontend chip shows size + amber divergence pill.</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr"/>
@@ -7813,18 +7821,18 @@
       </c>
       <c r="M135" s="3" t="inlineStr">
         <is>
-          <t>3e812743</t>
+          <t>d5eb49c5</t>
         </is>
       </c>
       <c r="N135" s="8" t="inlineStr"/>
     </row>
-    <row r="136" ht="75" customHeight="1">
+    <row r="136" ht="105" customHeight="1">
       <c r="A136" s="2" t="n">
         <v>135</v>
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>MODE-2</t>
+          <t>MODE-3</t>
         </is>
       </c>
       <c r="C136" s="9" t="inlineStr">
@@ -7839,17 +7847,17 @@
       </c>
       <c r="E136" s="6" t="inlineStr">
         <is>
-          <t>Per-mode sizing + verdict-divergence explanation (Phase 2)</t>
+          <t>Per-mode pillar reweighting (Phase 3 · flag-gated · INTUITION pending validation)</t>
         </is>
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
-          <t>Per-mode decisions shipped in MODE-1 didn't apply mode-specific size_mult or explain WHY a mode's verdict differed from the legacy single-decision.</t>
+          <t>Per-mode rulebooks shipped in MODE-1+2 used the legacy single composite score. SWING couldn't naturally select catalyst-heavy setups vs INVEST selecting fundamentals-heavy. User explicitly overrode principle-7 evidence requirement to ship the per-mode UX immediately.</t>
         </is>
       </c>
       <c r="G136" s="5" t="inlineStr">
         <is>
-          <t>compute_decisions_by_mode() now accepts base_alloc_pct + legacy_decision. Per-mode final_alloc_pct = base × size_mult, capped 5% NAV. New diverge_note field surfaces the exact rule that caused divergence (R:R floor, entry-quality gate, ER blackout). Frontend chip shows size + amber divergence pill.</t>
+          <t>New _MODE_PILLAR_WEIGHTS in analysis.py (SWING catalyst+tech-heavy, POS balanced, INVEST fund-heavy). compute_decisions_by_mode accepts pillar_pcts and computes mode_score = sum(pct × weight × 100). Config flag per_mode_pillar_reweight._enabled (default true) for rollback. Legacy t.score still drives decision_log + alerts; per-mode score affects UI only. Chip shows 'score 58 (legacy 45)' when divergence ≥5pts. Validation backtest required before promoting (see MODE-4).</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr"/>
@@ -7867,18 +7875,18 @@
       </c>
       <c r="M136" s="3" t="inlineStr">
         <is>
-          <t>d5eb49c5</t>
+          <t>6df0095d</t>
         </is>
       </c>
       <c r="N136" s="8" t="inlineStr"/>
     </row>
-    <row r="137" ht="105" customHeight="1">
+    <row r="137" ht="90" customHeight="1">
       <c r="A137" s="2" t="n">
         <v>136</v>
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>MODE-3</t>
+          <t>VERDICT-TWO-AXIS</t>
         </is>
       </c>
       <c r="C137" s="9" t="inlineStr">
@@ -7893,17 +7901,17 @@
       </c>
       <c r="E137" s="6" t="inlineStr">
         <is>
-          <t>Per-mode pillar reweighting (Phase 3 · flag-gated · INTUITION pending validation)</t>
+          <t>Two-axis verdict (bias × action × reason_class) replaces overloaded enum</t>
         </is>
       </c>
       <c r="F137" s="5" t="inlineStr">
         <is>
-          <t>Per-mode rulebooks shipped in MODE-1+2 used the legacy single composite score. SWING couldn't naturally select catalyst-heavy setups vs INVEST selecting fundamentals-heavy. User explicitly overrode principle-7 evidence requirement to ship the per-mode UX immediately.</t>
+          <t>Single verdict enum conflated DIRECTION and ACTION — an AVOID-by-extended-gate long (WKC, strong uptrend) rendered 'Bearish · Place short'. Engine now emits orthogonal bias (bullish/neutral/bearish) + action (buy/wait/avoid/short) + reason_class; surfaces bind bias for the word, action for the chip, reason for the caveat.</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>New _MODE_PILLAR_WEIGHTS in analysis.py (SWING catalyst+tech-heavy, POS balanced, INVEST fund-heavy). compute_decisions_by_mode accepts pillar_pcts and computes mode_score = sum(pct × weight × 100). Config flag per_mode_pillar_reweight._enabled (default true) for rollback. Legacy t.score still drives decision_log + alerts; per-mode score affects UI only. Chip shows 'score 58 (legacy 45)' when divergence ≥5pts. Validation backtest required before promoting (see MODE-4).</t>
+          <t>decision_engine.derive_bias_action + compute_final_verdict wrapper; analysis.compute_decisions_by_mode per-mode; server /api/universe exposes; bullveda-boot maps; data.jsx biasRead/actionRead/reasonNote; migrated composite-verdict + scan-column + detail-panel + lens-investment + lens-overview + surface-signal + surface-watchlist + home. Verdict enum kept for back-compat.</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr"/>
@@ -7916,12 +7924,12 @@
       </c>
       <c r="L137" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="M137" s="3" t="inlineStr">
         <is>
-          <t>6df0095d</t>
+          <t>3b6c90547</t>
         </is>
       </c>
       <c r="N137" s="8" t="inlineStr"/>
@@ -7932,7 +7940,7 @@
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>VERDICT-TWO-AXIS</t>
+          <t>UI-AGENCY-1</t>
         </is>
       </c>
       <c r="C138" s="9" t="inlineStr">
@@ -7942,22 +7950,22 @@
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>Decision Engine</t>
+          <t>Detail Page UX</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
         <is>
-          <t>Two-axis verdict (bias × action × reason_class) replaces overloaded enum</t>
+          <t>Always-visible BUY/SHORT/WATCH action bar (user agency)</t>
         </is>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>Single verdict enum conflated DIRECTION and ACTION — an AVOID-by-extended-gate long (WKC, strong uptrend) rendered 'Bearish · Place short'. Engine now emits orthogonal bias (bullish/neutral/bearish) + action (buy/wait/avoid/short) + reason_class; surfaces bind bias for the word, action for the chip, reason for the caveat.</t>
+          <t>Detail page hid the BUY ribbon when system verdict was WATCH/AVOID/EXTENDED. A trader with informed conviction couldn't act through the dashboard. User explicit direction: system informs, user decides.</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>decision_engine.derive_bias_action + compute_final_verdict wrapper; analysis.compute_decisions_by_mode per-mode; server /api/universe exposes; bullveda-boot maps; data.jsx biasRead/actionRead/reasonNote; migrated composite-verdict + scan-column + detail-panel + lens-investment + lens-overview + surface-signal + surface-watchlist + home. Verdict enum kept for back-compat.</t>
+          <t>New renderQuickActionBar (sticky detail-header) + window._openQuickAction(action, ticker, ctx) global router. System verdict shown as informational chip only; buttons never gated on score/R:R/PLAN INCOMPLETE. WATCH POSTs to /api/custom/add with idempotent 'already tracked' handling. Memory: feedback_user_agency_actions.md.</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr"/>
@@ -7970,23 +7978,23 @@
       </c>
       <c r="L138" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M138" s="3" t="inlineStr">
         <is>
-          <t>3b6c90547</t>
+          <t>c97db4b4</t>
         </is>
       </c>
       <c r="N138" s="8" t="inlineStr"/>
     </row>
-    <row r="139" ht="90" customHeight="1">
+    <row r="139" ht="60" customHeight="1">
       <c r="A139" s="2" t="n">
         <v>138</v>
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>UI-AGENCY-1</t>
+          <t>SCORE-ZERO-LABEL</t>
         </is>
       </c>
       <c r="C139" s="9" t="inlineStr">
@@ -7996,22 +8004,22 @@
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>Detail Page UX</t>
+          <t>Detail UI / Composite Score</t>
         </is>
       </c>
       <c r="E139" s="6" t="inlineStr">
         <is>
-          <t>Always-visible BUY/SHORT/WATCH action bar (user agency)</t>
+          <t>Score=0 generic SUB-THRESHOLD masked the actual kill cause</t>
         </is>
       </c>
       <c r="F139" s="5" t="inlineStr">
         <is>
-          <t>Detail page hid the BUY ribbon when system verdict was WATCH/AVOID/EXTENDED. A trader with informed conviction couldn't act through the dashboard. User explicit direction: system informs, user decides.</t>
+          <t>Composite Score gauge always said 'SUB-THRESHOLD · −65 to BUY' for score=0. Now distinguishes PORTFOLIO BRAKE (system-wide pause) vs HARD GATE (per-ticker kill) vs SUPPRESSED vs genuinely SUB-THRESHOLD based on t.decision.reason</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>New renderQuickActionBar (sticky detail-header) + window._openQuickAction(action, ticker, ctx) global router. System verdict shown as informational chip only; buttons never gated on score/R:R/PLAN INCOMPLETE. WATCH POSTs to /api/custom/add with idempotent 'already tracked' handling. Memory: feedback_user_agency_actions.md.</t>
+          <t>kairos.html — _scoreTierTxt + _scoreDeltaTxt computation rewritten with reason-aware branching</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr"/>
@@ -8024,23 +8032,23 @@
       </c>
       <c r="L139" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="M139" s="3" t="inlineStr">
         <is>
-          <t>c97db4b4</t>
+          <t>27fd646b1</t>
         </is>
       </c>
       <c r="N139" s="8" t="inlineStr"/>
     </row>
-    <row r="140" ht="60" customHeight="1">
+    <row r="140" ht="75" customHeight="1">
       <c r="A140" s="2" t="n">
         <v>139</v>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>SCORE-ZERO-LABEL</t>
+          <t>PREMORTEM-REASON</t>
         </is>
       </c>
       <c r="C140" s="9" t="inlineStr">
@@ -8050,22 +8058,22 @@
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>Detail UI / Composite Score</t>
+          <t>Detail UI / Pre-Mortem</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
         <is>
-          <t>Score=0 generic SUB-THRESHOLD masked the actual kill cause</t>
+          <t>Pre-Mortem showed boilerplate instead of real kill reason</t>
         </is>
       </c>
       <c r="F140" s="5" t="inlineStr">
         <is>
-          <t>Composite Score gauge always said 'SUB-THRESHOLD · −65 to BUY' for score=0. Now distinguishes PORTFOLIO BRAKE (system-wide pause) vs HARD GATE (per-ticker kill) vs SUPPRESSED vs genuinely SUB-THRESHOLD based on t.decision.reason</t>
+          <t>When a ticker is in bundle.killed (e.g., rolling-Sharpe brake or earnings blackout), Pre-Mortem was generating speculative killers from current signals instead of surfacing t.decision.reason. Now prepends real reason with severity tag (PORTFOLIO SAFETY BRAKE / HARD GATE FAIL / SYSTEM KILL)</t>
         </is>
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>kairos.html — _scoreTierTxt + _scoreDeltaTxt computation rewritten with reason-aware branching</t>
+          <t>kairos.html _qdAutoThesisKillers() — block 0 reads dec.reason and ranks priority 200</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr"/>
@@ -8088,13 +8096,13 @@
       </c>
       <c r="N140" s="8" t="inlineStr"/>
     </row>
-    <row r="141" ht="75" customHeight="1">
+    <row r="141" ht="45" customHeight="1">
       <c r="A141" s="2" t="n">
         <v>140</v>
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>PREMORTEM-REASON</t>
+          <t>G3</t>
         </is>
       </c>
       <c r="C141" s="9" t="inlineStr">
@@ -8104,27 +8112,39 @@
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>Detail UI / Pre-Mortem</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E141" s="6" t="inlineStr">
         <is>
-          <t>Pre-Mortem showed boilerplate instead of real kill reason</t>
+          <t>signal_filter audit table + drift view</t>
         </is>
       </c>
       <c r="F141" s="5" t="inlineStr">
         <is>
-          <t>When a ticker is in bundle.killed (e.g., rolling-Sharpe brake or earnings blackout), Pre-Mortem was generating speculative killers from current signals instead of surfacing t.decision.reason. Now prepends real reason with severity tag (PORTFOLIO SAFETY BRAKE / HARD GATE FAIL / SYSTEM KILL)</t>
+          <t>Need persistence + drift monitoring for signal_filter decisions before flipping it on.</t>
         </is>
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>kairos.html _qdAutoThesisKillers() — block 0 reads dec.reason and ranks priority 200</t>
-        </is>
-      </c>
-      <c r="H141" s="2" t="inlineStr"/>
-      <c r="I141" s="5" t="inlineStr"/>
-      <c r="J141" s="5" t="inlineStr"/>
+          <t>migrations/003_signal_filter_audit.sql — signal_filter_decisions table + signal_filter_drift_30d view. Feeds A7 dashboard tile (future).</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I141" s="5" t="inlineStr">
+        <is>
+          <t>Win: audit + drift visibility before flipping signal_filter on.</t>
+        </is>
+      </c>
+      <c r="J141" s="5" t="inlineStr">
+        <is>
+          <t>A7 dashboard tile not yet built — registry has the data when needed.</t>
+        </is>
+      </c>
       <c r="K141" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -8132,23 +8152,27 @@
       </c>
       <c r="L141" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M141" s="3" t="inlineStr">
         <is>
-          <t>27fd646b1</t>
-        </is>
-      </c>
-      <c r="N141" s="8" t="inlineStr"/>
-    </row>
-    <row r="142" ht="45" customHeight="1">
+          <t>4129e5565</t>
+        </is>
+      </c>
+      <c r="N141" s="8" t="inlineStr">
+        <is>
+          <t>psql or Supabase Studio → confirm signal_filter_decisions table exists + signal_filter_drift_30d view returns query plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="60" customHeight="1">
       <c r="A142" s="2" t="n">
         <v>141</v>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>G3</t>
+          <t>F11</t>
         </is>
       </c>
       <c r="C142" s="9" t="inlineStr">
@@ -8158,22 +8182,22 @@
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Infrastructure / Quality</t>
         </is>
       </c>
       <c r="E142" s="6" t="inlineStr">
         <is>
-          <t>signal_filter audit table + drift view</t>
+          <t>Pre-commit hook for schema drift</t>
         </is>
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
-          <t>Need persistence + drift monitoring for signal_filter decisions before flipping it on.</t>
+          <t>Schema drift between JSON canonical files and Postgres columns silently fails dual-write to Supabase. Need CI-style enforcement.</t>
         </is>
       </c>
       <c r="G142" s="5" t="inlineStr">
         <is>
-          <t>migrations/003_signal_filter_audit.sql — signal_filter_decisions table + signal_filter_drift_30d view. Feeds A7 dashboard tile (future).</t>
+          <t>First version: full-repo --strict check (commit 4129e5565). REFINED in 1e40d30fc: scoped to current commit — skips unless commit touches data/*.json OR migrations/ OR db.py; only blocks on NEW keys this commit adds.</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -8183,12 +8207,12 @@
       </c>
       <c r="I142" s="5" t="inlineStr">
         <is>
-          <t>Win: audit + drift visibility before flipping signal_filter on.</t>
+          <t>Win: prevents NEW drift while not blocking on pre-existing technical debt.</t>
         </is>
       </c>
       <c r="J142" s="5" t="inlineStr">
         <is>
-          <t>A7 dashboard tile not yet built — registry has the data when needed.</t>
+          <t>8 pre-existing JSON-only fields documented as tech debt.</t>
         </is>
       </c>
       <c r="K142" s="12" t="inlineStr">
@@ -8203,22 +8227,22 @@
       </c>
       <c r="M142" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N142" s="8" t="inlineStr">
         <is>
-          <t>psql or Supabase Studio → confirm signal_filter_decisions table exists + signal_filter_drift_30d view returns query plan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="60" customHeight="1">
+          <t>Stage a JSON change with NEW key. git commit → hook fires drift check on NEW key only (not full repo). Pre-existing drift not blocking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="75" customHeight="1">
       <c r="A143" s="2" t="n">
         <v>142</v>
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>F11</t>
+          <t>SCAN-CONN-BREAKER</t>
         </is>
       </c>
       <c r="C143" s="9" t="inlineStr">
@@ -8228,39 +8252,27 @@
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure / Quality</t>
+          <t>Infrastructure / Scan resilience</t>
         </is>
       </c>
       <c r="E143" s="6" t="inlineStr">
         <is>
-          <t>Pre-commit hook for schema drift</t>
+          <t>EODHD connectivity circuit breaker + nightly fd bump</t>
         </is>
       </c>
       <c r="F143" s="5" t="inlineStr">
         <is>
-          <t>Schema drift between JSON canonical files and Postgres columns silently fails dual-write to Supabase. Need CI-style enforcement.</t>
+          <t>Heavy scan with no fd-limit raise exhausted launchd's ~256 fds 21min in (2026-06-04 05:15 run); getaddrinfo failures then ground for 90min with zero progress before external kill, froze the BullVeda bundle + blocked later scans</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>First version: full-repo --strict check (commit 4129e5565). REFINED in 1e40d30fc: scoped to current commit — skips unless commit touches data/*.json OR migrations/ OR db.py; only blocks on NEW keys this commit adds.</t>
-        </is>
-      </c>
-      <c r="H143" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I143" s="5" t="inlineStr">
-        <is>
-          <t>Win: prevents NEW drift while not blocking on pre-existing technical debt.</t>
-        </is>
-      </c>
-      <c r="J143" s="5" t="inlineStr">
-        <is>
-          <t>8 pre-existing JSON-only fields documented as tech debt.</t>
-        </is>
-      </c>
+          <t>Added EODHDConnectivityError breaker in eodhd_client._request: trips after 40 consecutive connection-establishment failures, fails all calls fast (no socket/retry), resets on any HTTP response; raised weekly_full_enrich.sh fd limit 10240→200000 to match run_daily_scan.sh</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr"/>
+      <c r="I143" s="5" t="inlineStr"/>
+      <c r="J143" s="5" t="inlineStr"/>
       <c r="K143" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -8268,27 +8280,23 @@
       </c>
       <c r="L143" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="M143" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
-        </is>
-      </c>
-      <c r="N143" s="8" t="inlineStr">
-        <is>
-          <t>Stage a JSON change with NEW key. git commit → hook fires drift check on NEW key only (not full repo). Pre-existing drift not blocking.</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="75" customHeight="1">
+          <t>71b02de8d</t>
+        </is>
+      </c>
+      <c r="N143" s="8" t="inlineStr"/>
+    </row>
+    <row r="144" ht="45" customHeight="1">
       <c r="A144" s="2" t="n">
         <v>143</v>
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>SCAN-CONN-BREAKER</t>
+          <t>FINBERT-SENTIMENT</t>
         </is>
       </c>
       <c r="C144" s="9" t="inlineStr">
@@ -8298,22 +8306,22 @@
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure / Scan resilience</t>
+          <t>ML / Features</t>
         </is>
       </c>
       <c r="E144" s="6" t="inlineStr">
         <is>
-          <t>EODHD connectivity circuit breaker + nightly fd bump</t>
+          <t>FinBERT ONNX sentiment replaces keyword lexicon</t>
         </is>
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
-          <t>Heavy scan with no fd-limit raise exhausted launchd's ~256 fds 21min in (2026-06-04 05:15 run); getaddrinfo failures then ground for 90min with zero progress before external kill, froze the BullVeda bundle + blocked later scans</t>
+          <t>local ONNX FinBERT (no torch/LLM) primary scorer in get_news_sentiment, lexicon fallback; live pillar upgrade now; GBM-feature later via leak-free fwd log</t>
         </is>
       </c>
       <c r="G144" s="5" t="inlineStr">
         <is>
-          <t>Added EODHDConnectivityError breaker in eodhd_client._request: trips after 40 consecutive connection-establishment failures, fails all calls fast (no socket/retry), resets on any HTTP response; raised weekly_full_enrich.sh fd limit 10240→200000 to match run_daily_scan.sh</t>
+          <t>finbert_sentiment.py + download_finbert_onnx.py + data_fetcher</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr"/>
@@ -8326,23 +8334,23 @@
       </c>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="M144" s="3" t="inlineStr">
         <is>
-          <t>71b02de8d</t>
+          <t>7f1e2a9c4</t>
         </is>
       </c>
       <c r="N144" s="8" t="inlineStr"/>
     </row>
-    <row r="145" ht="45" customHeight="1">
+    <row r="145" ht="105" customHeight="1">
       <c r="A145" s="2" t="n">
         <v>144</v>
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>FINBERT-SENTIMENT</t>
+          <t>AIPRED-CORE</t>
         </is>
       </c>
       <c r="C145" s="9" t="inlineStr">
@@ -8352,22 +8360,22 @@
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>ML / Features</t>
+          <t>ML Edge / AI Prediction</t>
         </is>
       </c>
       <c r="E145" s="6" t="inlineStr">
         <is>
-          <t>FinBERT ONNX sentiment replaces keyword lexicon</t>
+          <t>Workspace AI Prediction sub-tab (23 modules)</t>
         </is>
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>local ONNX FinBERT (no torch/LLM) primary scorer in get_news_sentiment, lexicon fallback; live pillar upgrade now; GBM-feature later via leak-free fwd log</t>
+          <t>Universe-wide forecasting workbench: hero cone · trade-exec strip · live-quote chip · stability badge · stress overlay · landmines · walk-forward equity · cross-horizon coherence · forward distribution histogram · calibration + reliability · universe scans (Top 10 Bulls/Bears/Flip/R:R + SHAP-per-row) · sector rollup · pair trades · open positions overlay · diff vs yesterday · R2000 alpha leak · drift trend · failure log</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>finbert_sentiment.py + download_finbert_onnx.py + data_fetcher</t>
+          <t>kairos.html _qdMlAiBody + 23 sub-modules · shared between Workspaces ML Edge tab and QuantDetail per-ticker view via window._qdMlAiBody</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr"/>
@@ -8380,23 +8388,23 @@
       </c>
       <c r="L145" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="M145" s="3" t="inlineStr">
         <is>
-          <t>7f1e2a9c4</t>
+          <t>27fd646b1</t>
         </is>
       </c>
       <c r="N145" s="8" t="inlineStr"/>
     </row>
-    <row r="146" ht="105" customHeight="1">
+    <row r="146" ht="60" customHeight="1">
       <c r="A146" s="2" t="n">
         <v>145</v>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>AIPRED-CORE</t>
+          <t>AIPRED-AUTOREFRESH</t>
         </is>
       </c>
       <c r="C146" s="9" t="inlineStr">
@@ -8406,22 +8414,22 @@
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>ML Edge / AI Prediction</t>
+          <t>ML Edge / Autonomous</t>
         </is>
       </c>
       <c r="E146" s="6" t="inlineStr">
         <is>
-          <t>Workspace AI Prediction sub-tab (23 modules)</t>
+          <t>Autonomous launchd jobs (full + intraday refresh)</t>
         </is>
       </c>
       <c r="F146" s="5" t="inlineStr">
         <is>
-          <t>Universe-wide forecasting workbench: hero cone · trade-exec strip · live-quote chip · stability badge · stress overlay · landmines · walk-forward equity · cross-horizon coherence · forward distribution histogram · calibration + reliability · universe scans (Top 10 Bulls/Bears/Flip/R:R + SHAP-per-row) · sector rollup · pair trades · open positions overlay · diff vs yesterday · R2000 alpha leak · drift trend · failure log</t>
+          <t>5 AM PT full universe + 9/11/13 PT intraday top-100. Loaded + tested 2026-05-18. Output: cache/ml_edge_predictions.json + infra/prototype/ ml_edge_predictions.json</t>
         </is>
       </c>
       <c r="G146" s="5" t="inlineStr">
         <is>
-          <t>kairos.html _qdMlAiBody + 23 sub-modules · shared between Workspaces ML Edge tab and QuantDetail per-ticker view via window._qdMlAiBody</t>
+          <t>infra/launchd/com.swingtrade.ml-edge.plist + .ml-edge-intraday.plist (installed at ~/Library/LaunchAgents/)</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr"/>
@@ -8450,7 +8458,7 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>AIPRED-AUTOREFRESH</t>
+          <t>AIPRED-SCHWAB</t>
         </is>
       </c>
       <c r="C147" s="9" t="inlineStr">
@@ -8460,22 +8468,22 @@
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>ML Edge / Autonomous</t>
+          <t>ML Edge / Real Quotes</t>
         </is>
       </c>
       <c r="E147" s="6" t="inlineStr">
         <is>
-          <t>Autonomous launchd jobs (full + intraday refresh)</t>
+          <t>Real Schwab bid/ask spread overlay (top-100)</t>
         </is>
       </c>
       <c r="F147" s="5" t="inlineStr">
         <is>
-          <t>5 AM PT full universe + 9/11/13 PT intraday top-100. Loaded + tested 2026-05-18. Output: cache/ml_edge_predictions.json + infra/prototype/ ml_edge_predictions.json</t>
+          <t>Batch-fetches live Schwab quotes for top-100 picks per mode; overrides ADV-band heuristic with real spread_bps; q50_net recomputed; spread_source='schwab_live' stamped</t>
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>infra/launchd/com.swingtrade.ml-edge.plist + .ml-edge-intraday.plist (installed at ~/Library/LaunchAgents/)</t>
+          <t>ml/run_ml_edge.py post-prediction loop · schwab_client.get_quotes_batch</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr"/>
@@ -8504,7 +8512,7 @@
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>AIPRED-SCHWAB</t>
+          <t>AIPRED-STRESS</t>
         </is>
       </c>
       <c r="C148" s="9" t="inlineStr">
@@ -8514,22 +8522,22 @@
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>ML Edge / Real Quotes</t>
+          <t>ML Edge / Stress</t>
         </is>
       </c>
       <c r="E148" s="6" t="inlineStr">
         <is>
-          <t>Real Schwab bid/ask spread overlay (top-100)</t>
+          <t>VIX-regime stress overlay from real historical buckets</t>
         </is>
       </c>
       <c r="F148" s="5" t="inlineStr">
         <is>
-          <t>Batch-fetches live Schwab quotes for top-100 picks per mode; overrides ADV-band heuristic with real spread_bps; q50_net recomputed; spread_source='schwab_live' stamped</t>
+          <t>Replaces fixed heuristic shift with bucketed mean from 355K samples (base=355K, spy_down=156K, vix=37K). UI cone label shows 'STRESS · real' vs 'STRESS · heuristic' fallback</t>
         </is>
       </c>
       <c r="G148" s="5" t="inlineStr">
         <is>
-          <t>ml/run_ml_edge.py post-prediction loop · schwab_client.get_quotes_batch</t>
+          <t>scripts/build_stress_buckets.py · cache/ml/stress_buckets.json · /api/ml-edge-stress-buckets · kairos.html _qdMlAiCone</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr"/>
@@ -8558,7 +8566,7 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>AIPRED-STRESS</t>
+          <t>AIPRED-SURVIVORSHIP</t>
         </is>
       </c>
       <c r="C149" s="9" t="inlineStr">
@@ -8568,22 +8576,22 @@
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>ML Edge / Stress</t>
+          <t>ML Edge / Survivorship</t>
         </is>
       </c>
       <c r="E149" s="6" t="inlineStr">
         <is>
-          <t>VIX-regime stress overlay from real historical buckets</t>
+          <t>Point-in-time R1000/R2000 membership snapshots</t>
         </is>
       </c>
       <c r="F149" s="5" t="inlineStr">
         <is>
-          <t>Replaces fixed heuristic shift with bucketed mean from 355K samples (base=355K, spy_down=156K, vix=37K). UI cone label shows 'STRESS · real' vs 'STRESS · heuristic' fallback</t>
+          <t>Monthly launchd snapshots S&amp;P/R1000/R2000 to data/membership/*_YYYY-MM.csv. data_fetcher.get_universe_as_of reads them when present. Today's baseline captured 2026-05</t>
         </is>
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>scripts/build_stress_buckets.py · cache/ml/stress_buckets.json · /api/ml-edge-stress-buckets · kairos.html _qdMlAiCone</t>
+          <t>scripts/snapshot_membership.py + infra/launchd/com.swingtrade.membership-snapshot.plist + data_fetcher.py</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr"/>
@@ -8612,7 +8620,7 @@
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>AIPRED-SURVIVORSHIP</t>
+          <t>AIPRED-TRACK</t>
         </is>
       </c>
       <c r="C150" s="9" t="inlineStr">
@@ -8622,22 +8630,22 @@
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>ML Edge / Survivorship</t>
+          <t>ML Edge / Track Record</t>
         </is>
       </c>
       <c r="E150" s="6" t="inlineStr">
         <is>
-          <t>Point-in-time R1000/R2000 membership snapshots</t>
+          <t>ML-Edge paper picks history + outcome resolver</t>
         </is>
       </c>
       <c r="F150" s="5" t="inlineStr">
         <is>
-          <t>Monthly launchd snapshots S&amp;P/R1000/R2000 to data/membership/*_YYYY-MM.csv. data_fetcher.get_universe_as_of reads them when present. Today's baseline captured 2026-05</t>
+          <t>30 top picks per mode logged to cache/ml_edge_picks_history.jsonl on every run. scripts/resolve_ml_picks.py backfills outcomes via OHLCV lookup. /api/ml-edge-track serves real WR/PF/expectancy</t>
         </is>
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>scripts/snapshot_membership.py + infra/launchd/com.swingtrade.membership-snapshot.plist + data_fetcher.py</t>
+          <t>ml/run_ml_edge.py picks-capture block + scripts/resolve_ml_picks.py + server.py /api/ml-edge-track</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr"/>
@@ -8666,7 +8674,7 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>AIPRED-TRACK</t>
+          <t>AIPRED-UNIVERSE</t>
         </is>
       </c>
       <c r="C151" s="9" t="inlineStr">
@@ -8676,22 +8684,22 @@
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>ML Edge / Track Record</t>
+          <t>ML Edge / Universe</t>
         </is>
       </c>
       <c r="E151" s="6" t="inlineStr">
         <is>
-          <t>ML-Edge paper picks history + outcome resolver</t>
+          <t>Universe expansion S&amp;P 500 + R1000 + R2000 (2960 tickers)</t>
         </is>
       </c>
       <c r="F151" s="5" t="inlineStr">
         <is>
-          <t>30 top picks per mode logged to cache/ml_edge_picks_history.jsonl on every run. scripts/resolve_ml_picks.py backfills outcomes via OHLCV lookup. /api/ml-edge-track serves real WR/PF/expectancy</t>
+          <t>ml/universe_loader.py aggregates EODHD index_components for all 3 indices · --universe flag on run_ml_edge.py · membership flags stamped per-payload · S&amp;P 500=503, R1000=981, R2000=1963, union=2960</t>
         </is>
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>ml/run_ml_edge.py picks-capture block + scripts/resolve_ml_picks.py + server.py /api/ml-edge-track</t>
+          <t>ml/universe_loader.py + ml/run_ml_edge.py + UI universe pills in coverage banner</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr"/>
@@ -8714,13 +8722,13 @@
       </c>
       <c r="N151" s="8" t="inlineStr"/>
     </row>
-    <row r="152" ht="60" customHeight="1">
+    <row r="152" ht="90" customHeight="1">
       <c r="A152" s="2" t="n">
         <v>151</v>
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>AIPRED-UNIVERSE</t>
+          <t>MOB-1</t>
         </is>
       </c>
       <c r="C152" s="9" t="inlineStr">
@@ -8730,27 +8738,35 @@
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>ML Edge / Universe</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E152" s="6" t="inlineStr">
         <is>
-          <t>Universe expansion S&amp;P 500 + R1000 + R2000 (2960 tickers)</t>
+          <t>Tablet portrait support (≥768px)</t>
         </is>
       </c>
       <c r="F152" s="5" t="inlineStr">
         <is>
-          <t>ml/universe_loader.py aggregates EODHD index_components for all 3 indices · --universe flag on run_ml_edge.py · membership flags stamped per-payload · S&amp;P 500=503, R1000=981, R2000=1963, union=2960</t>
+          <t>Desktop-first. Viewport meta added but no tablet layouts; sidebar overflows, tabs don't wrap.</t>
         </is>
       </c>
       <c r="G152" s="5" t="inlineStr">
         <is>
-          <t>ml/universe_loader.py + ml/run_ml_edge.py + UI universe pills in coverage banner</t>
-        </is>
-      </c>
-      <c r="H152" s="2" t="inlineStr"/>
+          <t>Pure-CSS @media block in dashboard.html + elite-detail.html. Tablet (768-1023): 2-up KPI grid, scrollable tabs, table overflow-x. Phone (≤767): single column, ≥44px tap targets, hidden badges, condensed regime strip, full-width drawers. Touch hover suppression.</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>4-6 hrs</t>
+        </is>
+      </c>
       <c r="I152" s="5" t="inlineStr"/>
-      <c r="J152" s="5" t="inlineStr"/>
+      <c r="J152" s="5" t="inlineStr">
+        <is>
+          <t>Tablet/phone CSS shipped to dashboard.html (other session commit 114646f23 PERF-7) and elite-detail.html (this session 54c6f218d). @media breakpoints at 768/1024/380px, 2-up grids on tablet, single-column on phone, ≥44px tap targets, hover suppression on touch.</t>
+        </is>
+      </c>
       <c r="K152" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -8758,23 +8774,27 @@
       </c>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M152" s="3" t="inlineStr">
         <is>
-          <t>27fd646b1</t>
-        </is>
-      </c>
-      <c r="N152" s="8" t="inlineStr"/>
-    </row>
-    <row r="153" ht="90" customHeight="1">
+          <t>54c6f218d / 114646f23</t>
+        </is>
+      </c>
+      <c r="N152" s="8" t="inlineStr">
+        <is>
+          <t>Open https://trade.mystockholding.com on iPad portrait (≥768px and &lt;1024px): KPI tiles render 2-up, no horizontal page scroll except inside tables, sub-tabs scroll horizontally without wrapping. Then iPhone Safari (≤767): single-column layout, sidebar tap targets ≥44px, no badge cruft, drawer panels open full-width. Verify desktop (≥1024px) still pixel-identical to before.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="75" customHeight="1">
       <c r="A153" s="2" t="n">
         <v>152</v>
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>MOB-1</t>
+          <t>MOB-2</t>
         </is>
       </c>
       <c r="C153" s="9" t="inlineStr">
@@ -8789,28 +8809,28 @@
       </c>
       <c r="E153" s="6" t="inlineStr">
         <is>
-          <t>Tablet portrait support (≥768px)</t>
+          <t>Phone support (≤480px)</t>
         </is>
       </c>
       <c r="F153" s="5" t="inlineStr">
         <is>
-          <t>Desktop-first. Viewport meta added but no tablet layouts; sidebar overflows, tabs don't wrap.</t>
+          <t>No phone layout. Many UI elements unusable on phone.</t>
         </is>
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>Pure-CSS @media block in dashboard.html + elite-detail.html. Tablet (768-1023): 2-up KPI grid, scrollable tabs, table overflow-x. Phone (≤767): single column, ≥44px tap targets, hidden badges, condensed regime strip, full-width drawers. Touch hover suppression.</t>
+          <t>Same media block as MOB-1 plus ≤480px micro-phone block (small phones) + (hover:none) suppress hover effects on touch devices.</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>4-6 hrs</t>
+          <t>8-12 hrs</t>
         </is>
       </c>
       <c r="I153" s="5" t="inlineStr"/>
       <c r="J153" s="5" t="inlineStr">
         <is>
-          <t>Tablet/phone CSS shipped to dashboard.html (other session commit 114646f23 PERF-7) and elite-detail.html (this session 54c6f218d). @media breakpoints at 768/1024/380px, 2-up grids on tablet, single-column on phone, ≥44px tap targets, hover suppression on touch.</t>
+          <t>Phone-specific block (≤767px) + small phone (≤380px) + (hover:none) shipped in same commit pair as MOB-1.</t>
         </is>
       </c>
       <c r="K153" s="12" t="inlineStr">
@@ -8830,17 +8850,17 @@
       </c>
       <c r="N153" s="8" t="inlineStr">
         <is>
-          <t>Open https://trade.mystockholding.com on iPad portrait (≥768px and &lt;1024px): KPI tiles render 2-up, no horizontal page scroll except inside tables, sub-tabs scroll horizontally without wrapping. Then iPhone Safari (≤767): single-column layout, sidebar tap targets ≥44px, no badge cruft, drawer panels open full-width. Verify desktop (≥1024px) still pixel-identical to before.</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="75" customHeight="1">
+          <t>Open dashboard on iPhone SE (375px) and iPhone 13 (390px) in Safari. Verify: (1) every interactive element ≥44×44px (use Safari Inspector Touch Region), (2) no horizontal page scroll, (3) tables scroll horizontally inside their card, (4) tap navigation between V1 dashboard and elite detail does not require pinch-zoom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="135" customHeight="1">
       <c r="A154" s="2" t="n">
         <v>153</v>
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>MOB-2</t>
+          <t>IPAD-1</t>
         </is>
       </c>
       <c r="C154" s="9" t="inlineStr">
@@ -8850,33 +8870,37 @@
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Mobile / iPad</t>
         </is>
       </c>
       <c r="E154" s="6" t="inlineStr">
         <is>
-          <t>Phone support (≤480px)</t>
+          <t>iPad shell Phase 1 — split-view PWA</t>
         </is>
       </c>
       <c r="F154" s="5" t="inlineStr">
         <is>
-          <t>No phone layout. Many UI elements unusable on phone.</t>
+          <t>Desktop dashboard shrunk via responsive CSS but not iPad-native. No bottom tab bar, no PWA install path, no split-view.</t>
         </is>
       </c>
       <c r="G154" s="5" t="inlineStr">
         <is>
-          <t>Same media block as MOB-1 plus ≤480px micro-phone block (small phones) + (hover:none) suppress hover effects on touch devices.</t>
+          <t>New /v2/ipad/ shell — split-view (38/62 landscape, stacked portrait), 5-tab bottom bar, iPad UA-first design. Reuses elite-detail.html via iframe (zero module duplication). PWA manifest. 660 lines.</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>8-12 hrs</t>
-        </is>
-      </c>
-      <c r="I154" s="5" t="inlineStr"/>
+          <t>4 hrs</t>
+        </is>
+      </c>
+      <c r="I154" s="5" t="inlineStr">
+        <is>
+          <t>Low risk / High win</t>
+        </is>
+      </c>
       <c r="J154" s="5" t="inlineStr">
         <is>
-          <t>Phone-specific block (≤767px) + small phone (≤380px) + (hover:none) shipped in same commit pair as MOB-1.</t>
+          <t>iPad PWA shipped 2026-05-10 across 3 commits: 4b49cb93e (shell + manifest + ipad.css/js + dashboard.html), b0e5ef6a1 (verdict→stage hot fix — was 0 rows because filter matched r.verdict but bundle has r.stage), 79fa01a75 (iframe-aware sidebar hide in elite-detail.html). PWA-installable via Safari "Add to Home Screen" on iPad. Reuses /v2/elite-detail.html via iframe — single source of truth, no module duplication.</t>
         </is>
       </c>
       <c r="K154" s="12" t="inlineStr">
@@ -8891,22 +8915,22 @@
       </c>
       <c r="M154" s="3" t="inlineStr">
         <is>
-          <t>54c6f218d / 114646f23</t>
+          <t>4b49cb93e + b0e5ef6a1 + 79fa01a75</t>
         </is>
       </c>
       <c r="N154" s="8" t="inlineStr">
         <is>
-          <t>Open dashboard on iPhone SE (375px) and iPhone 13 (390px) in Safari. Verify: (1) every interactive element ≥44×44px (use Safari Inspector Touch Region), (2) no horizontal page scroll, (3) tables scroll horizontally inside their card, (4) tap navigation between V1 dashboard and elite detail does not require pinch-zoom.</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" ht="135" customHeight="1">
+          <t>1. Visit https://trade.mystockholding.com/v2/ipad/dashboard.html on iPad Safari (or Chrome desktop with iPad simulator). 2. Confirm Scanner tab shows ~60 WATCH rows (today's scan). 3. Tap any ticker → right pane loads /v2/elite-detail.html in iframe; inside the iframe the FLOOR sidebar + ticker tape + header are HIDDEN (otherwise the embed would render duplicate chrome). 4. Switch to Elite tab → 5 picks from data.elite_picks.Swing. 5. Pull down on the list pane → triggers refreshData() which re-fetches /v2/data.critical.json. 6. iPad home screen: Safari Share → Add to Home Screen → manifest.json metadata installs as standalone PWA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="45" customHeight="1">
       <c r="A155" s="2" t="n">
         <v>154</v>
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>IPAD-1</t>
+          <t>OPS-DEPLOYMENT-RECONCILE</t>
         </is>
       </c>
       <c r="C155" s="9" t="inlineStr">
@@ -8916,39 +8940,27 @@
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>Mobile / iPad</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E155" s="6" t="inlineStr">
         <is>
-          <t>iPad shell Phase 1 — split-view PWA</t>
+          <t>Capture 21 untracked live launchd jobs into repo</t>
         </is>
       </c>
       <c r="F155" s="5" t="inlineStr">
         <is>
-          <t>Desktop dashboard shrunk via responsive CSS but not iPad-native. No bottom tab bar, no PWA install path, no split-view.</t>
+          <t>deployment drift audit — 21 live jobs were running but never committed; captured into infra/launchd so repo is source of truth (55 tracked)</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>New /v2/ipad/ shell — split-view (38/62 landscape, stacked portrait), 5-tab bottom bar, iPad UA-first design. Reuses elite-detail.html via iframe (zero module duplication). PWA manifest. 660 lines.</t>
-        </is>
-      </c>
-      <c r="H155" s="2" t="inlineStr">
-        <is>
-          <t>4 hrs</t>
-        </is>
-      </c>
-      <c r="I155" s="5" t="inlineStr">
-        <is>
-          <t>Low risk / High win</t>
-        </is>
-      </c>
-      <c r="J155" s="5" t="inlineStr">
-        <is>
-          <t>iPad PWA shipped 2026-05-10 across 3 commits: 4b49cb93e (shell + manifest + ipad.css/js + dashboard.html), b0e5ef6a1 (verdict→stage hot fix — was 0 rows because filter matched r.verdict but bundle has r.stage), 79fa01a75 (iframe-aware sidebar hide in elite-detail.html). PWA-installable via Safari "Add to Home Screen" on iPad. Reuses /v2/elite-detail.html via iframe — single source of truth, no module duplication.</t>
-        </is>
-      </c>
+          <t>infra/launchd/*.plist</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr"/>
+      <c r="I155" s="5" t="inlineStr"/>
+      <c r="J155" s="5" t="inlineStr"/>
       <c r="K155" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -8956,19 +8968,15 @@
       </c>
       <c r="L155" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="M155" s="3" t="inlineStr">
         <is>
-          <t>4b49cb93e + b0e5ef6a1 + 79fa01a75</t>
-        </is>
-      </c>
-      <c r="N155" s="8" t="inlineStr">
-        <is>
-          <t>1. Visit https://trade.mystockholding.com/v2/ipad/dashboard.html on iPad Safari (or Chrome desktop with iPad simulator). 2. Confirm Scanner tab shows ~60 WATCH rows (today's scan). 3. Tap any ticker → right pane loads /v2/elite-detail.html in iframe; inside the iframe the FLOOR sidebar + ticker tape + header are HIDDEN (otherwise the embed would render duplicate chrome). 4. Switch to Elite tab → 5 picks from data.elite_picks.Swing. 5. Pull down on the list pane → triggers refreshData() which re-fetches /v2/data.critical.json. 6. iPad home screen: Safari Share → Add to Home Screen → manifest.json metadata installs as standalone PWA.</t>
-        </is>
-      </c>
+          <t>3138900c3</t>
+        </is>
+      </c>
+      <c r="N155" s="8" t="inlineStr"/>
     </row>
     <row r="156" ht="45" customHeight="1">
       <c r="A156" s="2" t="n">
@@ -8976,7 +8984,7 @@
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>OPS-DEPLOYMENT-RECONCILE</t>
+          <t>OPS-JOB-RESTRUCTURE</t>
         </is>
       </c>
       <c r="C156" s="9" t="inlineStr">
@@ -8991,17 +8999,17 @@
       </c>
       <c r="E156" s="6" t="inlineStr">
         <is>
-          <t>Capture 21 untracked live launchd jobs into repo</t>
+          <t>Launchd job restructure (lean + quota-safe)</t>
         </is>
       </c>
       <c r="F156" s="5" t="inlineStr">
         <is>
-          <t>deployment drift audit — 21 live jobs were running but never committed; captured into infra/launchd so repo is source of truth (55 tracked)</t>
+          <t>daily 6x-&gt;2x, premarket/prewarm/ml-edge/schwab/optionsflow trims, 6 snapshots-&gt;1, 10 notifs-&gt;3, EODHD budget guard, ML-into-scan + cached-bar reuse</t>
         </is>
       </c>
       <c r="G156" s="5" t="inlineStr">
         <is>
-          <t>infra/launchd/*.plist</t>
+          <t>infra/launchd/* + eodhd_client guard + swing_trade ML hook</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr"/>
@@ -9019,7 +9027,7 @@
       </c>
       <c r="M156" s="3" t="inlineStr">
         <is>
-          <t>3138900c3</t>
+          <t>801e0d90e</t>
         </is>
       </c>
       <c r="N156" s="8" t="inlineStr"/>
@@ -9030,7 +9038,7 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>OPS-JOB-RESTRUCTURE</t>
+          <t>PERF-4</t>
         </is>
       </c>
       <c r="C157" s="9" t="inlineStr">
@@ -9040,27 +9048,39 @@
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E157" s="6" t="inlineStr">
         <is>
-          <t>Launchd job restructure (lean + quota-safe)</t>
+          <t>Brotli compression (currently Gzip)</t>
         </is>
       </c>
       <c r="F157" s="5" t="inlineStr">
         <is>
-          <t>daily 6x-&gt;2x, premarket/prewarm/ml-edge/schwab/optionsflow trims, 6 snapshots-&gt;1, 10 notifs-&gt;3, EODHD budget guard, ML-into-scan + cached-bar reuse</t>
+          <t>Server.py serves Gzip; Brotli typically reduces JSON/HTML transfer ~15% at similar CPU cost.</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>infra/launchd/* + eodhd_client guard + swing_trade ML hook</t>
-        </is>
-      </c>
-      <c r="H157" s="2" t="inlineStr"/>
-      <c r="I157" s="5" t="inlineStr"/>
-      <c r="J157" s="5" t="inlineStr"/>
+          <t>Add brotli middleware to FastAPI; negotiate via Accept-Encoding; verify Cloudflare passes encoding through.</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>30 min</t>
+        </is>
+      </c>
+      <c r="I157" s="5" t="inlineStr">
+        <is>
+          <t>Win: -15% transfer size on data.json + tickers.json + HTML.</t>
+        </is>
+      </c>
+      <c r="J157" s="5" t="inlineStr">
+        <is>
+          <t>Verify Cloudflare tunnel doesn't strip br encoding.</t>
+        </is>
+      </c>
       <c r="K157" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -9068,15 +9088,19 @@
       </c>
       <c r="L157" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M157" s="3" t="inlineStr">
         <is>
-          <t>801e0d90e</t>
-        </is>
-      </c>
-      <c r="N157" s="8" t="inlineStr"/>
+          <t>2eb4e3b3d</t>
+        </is>
+      </c>
+      <c r="N157" s="8" t="inlineStr">
+        <is>
+          <t>Browser DevTools → Network tab → reload dashboard → Content-Encoding header on data.json reads 'br' (Brotli) when supported, else 'gzip'.</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="45" customHeight="1">
       <c r="A158" s="2" t="n">
@@ -9084,7 +9108,7 @@
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>PERF-4</t>
+          <t>PERF-5</t>
         </is>
       </c>
       <c r="C158" s="9" t="inlineStr">
@@ -9099,32 +9123,32 @@
       </c>
       <c r="E158" s="6" t="inlineStr">
         <is>
-          <t>Brotli compression (currently Gzip)</t>
+          <t>requestIdleCallback for _capScanAndDisableButtons</t>
         </is>
       </c>
       <c r="F158" s="5" t="inlineStr">
         <is>
-          <t>Server.py serves Gzip; Brotli typically reduces JSON/HTML transfer ~15% at similar CPU cost.</t>
+          <t>MutationObserver-based button disabler runs synchronously on init, blocking ~50ms.</t>
         </is>
       </c>
       <c r="G158" s="5" t="inlineStr">
         <is>
-          <t>Add brotli middleware to FastAPI; negotiate via Accept-Encoding; verify Cloudflare passes encoding through.</t>
+          <t>Wrap call in requestIdleCallback(() =&gt; _capScanAndDisableButtons(), { timeout: 500 }). setTimeout fallback for Safari.</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="I158" s="5" t="inlineStr">
         <is>
-          <t>Win: -15% transfer size on data.json + tickers.json + HTML.</t>
+          <t>Win: -50ms FCP.</t>
         </is>
       </c>
       <c r="J158" s="5" t="inlineStr">
         <is>
-          <t>Verify Cloudflare tunnel doesn't strip br encoding.</t>
+          <t>Trivial fix; verify no race with first user interaction.</t>
         </is>
       </c>
       <c r="K158" s="12" t="inlineStr">
@@ -9139,22 +9163,22 @@
       </c>
       <c r="M158" s="3" t="inlineStr">
         <is>
-          <t>2eb4e3b3d</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N158" s="8" t="inlineStr">
         <is>
-          <t>Browser DevTools → Network tab → reload dashboard → Content-Encoding header on data.json reads 'br' (Brotli) when supported, else 'gzip'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="159" ht="45" customHeight="1">
+          <t>Browser DevTools → Performance → reload dashboard → _capScanAndDisableButtons fires AFTER init-end (in idle callback), not during sync init.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="120" customHeight="1">
       <c r="A159" s="2" t="n">
         <v>158</v>
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>PERF-5</t>
+          <t>PERF-6</t>
         </is>
       </c>
       <c r="C159" s="9" t="inlineStr">
@@ -9169,32 +9193,32 @@
       </c>
       <c r="E159" s="6" t="inlineStr">
         <is>
-          <t>requestIdleCallback for _capScanAndDisableButtons</t>
+          <t>Critical CSS extraction (775-line &lt;style&gt; → above-fold + lazy)</t>
         </is>
       </c>
       <c r="F159" s="5" t="inlineStr">
         <is>
-          <t>MutationObserver-based button disabler runs synchronously on init, blocking ~50ms.</t>
+          <t>775-line &lt;style&gt; in &lt;head&gt; blocks FCP; most rules govern below-fold content.</t>
         </is>
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>Wrap call in requestIdleCallback(() =&gt; _capScanAndDisableButtons(), { timeout: 500 }). setTimeout fallback for Safari.</t>
+          <t>Identify above-fold CSS rules (header, sidebar, regime strip, top of each tab). Inline only those. Lazy-load rest via &lt;link rel='stylesheet'&gt; after init-end.</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I159" s="5" t="inlineStr">
         <is>
-          <t>Win: -50ms FCP.</t>
+          <t>Win: -100ms FCP.</t>
         </is>
       </c>
       <c r="J159" s="5" t="inlineStr">
         <is>
-          <t>Trivial fix; verify no race with first user interaction.</t>
+          <t>Conservative slice shipped: extracted ~295 lines of below-fold CSS (Audit date picker, D-1 Cross-Mode card, D-4 Factor heatmap, Accuracy framework, Settings rebuild, mobile media queries) into dashboard.deferred.css, loaded non-blocking via media="print" onload="this.media='all'". Inline &lt;style&gt; reduced 1029 → 734 lines. Elite Picks v2 styles intentionally kept inline (Elite is the default tab for all profiles).</t>
         </is>
       </c>
       <c r="K159" s="12" t="inlineStr">
@@ -9204,27 +9228,27 @@
       </c>
       <c r="L159" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M159" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>450572d28</t>
         </is>
       </c>
       <c r="N159" s="8" t="inlineStr">
         <is>
-          <t>Browser DevTools → Performance → reload dashboard → _capScanAndDisableButtons fires AFTER init-end (in idle callback), not during sync init.</t>
-        </is>
-      </c>
-    </row>
-    <row r="160" ht="120" customHeight="1">
+          <t>1. Open https://trade.mystockholding.com/v2/dashboard.html in DevTools Network tab. 2. Hard-refresh — confirm dashboard.deferred.css loads as a separate request with media=print first then promoted to media=all. 3. Click Audit / Portfolio / Accuracy / Settings tabs — all styled correctly (no FOUC). 4. Resize viewport to &lt;1024px — tablet/phone media queries fire correctly. 5. View source — inline &lt;style&gt; ends around line 749 (vs 1044 before). 6. Lighthouse FCP should improve ~50-150ms vs PERF-7-only baseline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="135" customHeight="1">
       <c r="A160" s="2" t="n">
         <v>159</v>
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>PERF-6</t>
+          <t>PERF-7</t>
         </is>
       </c>
       <c r="C160" s="9" t="inlineStr">
@@ -9239,32 +9263,32 @@
       </c>
       <c r="E160" s="6" t="inlineStr">
         <is>
-          <t>Critical CSS extraction (775-line &lt;style&gt; → above-fold + lazy)</t>
+          <t>Split data.json (5.3MB) into critical + deferred</t>
         </is>
       </c>
       <c r="F160" s="5" t="inlineStr">
         <is>
-          <t>775-line &lt;style&gt; in &lt;head&gt; blocks FCP; most rules govern below-fold content.</t>
+          <t>Dashboard cold load now bound by 5.3MB data.json fetch + parse — bulk of remaining 644ms init-end.</t>
         </is>
       </c>
       <c r="G160" s="5" t="inlineStr">
         <is>
-          <t>Identify above-fold CSS rules (header, sidebar, regime strip, top of each tab). Inline only those. Lazy-load rest via &lt;link rel='stylesheet'&gt; after init-end.</t>
+          <t>Decompose data.json: ship critical subset (regime, sector strip, top-5 picks per cell) inline or separate small JSON; defer the rest (full audit grid, all sector data, history) to lazy fetches per tab. Update build_data.py + dashboard.html.</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>1 hr</t>
+          <t>4 hrs</t>
         </is>
       </c>
       <c r="I160" s="5" t="inlineStr">
         <is>
-          <t>Win: -100ms FCP.</t>
+          <t>Win: -300-800ms cold load (single largest remaining boot lever).</t>
         </is>
       </c>
       <c r="J160" s="5" t="inlineStr">
         <is>
-          <t>Conservative slice shipped: extracted ~295 lines of below-fold CSS (Audit date picker, D-1 Cross-Mode card, D-4 Factor heatmap, Accuracy framework, Settings rebuild, mobile media queries) into dashboard.deferred.css, loaded non-blocking via media="print" onload="this.media='all'". Inline &lt;style&gt; reduced 1029 → 734 lines. Elite Picks v2 styles intentionally kept inline (Elite is the default tab for all profiles).</t>
+          <t>Biggest lever for next perf sprint. Phase 1+2 shipped: defers performance/killed/earnings/screener/crypto. Phase 2b (medium_term/long_term lazy on Range filter) tracked as PERF-7b.</t>
         </is>
       </c>
       <c r="K160" s="12" t="inlineStr">
@@ -9279,22 +9303,22 @@
       </c>
       <c r="M160" s="3" t="inlineStr">
         <is>
-          <t>450572d28</t>
+          <t>114646f23</t>
         </is>
       </c>
       <c r="N160" s="8" t="inlineStr">
         <is>
-          <t>1. Open https://trade.mystockholding.com/v2/dashboard.html in DevTools Network tab. 2. Hard-refresh — confirm dashboard.deferred.css loads as a separate request with media=print first then promoted to media=all. 3. Click Audit / Portfolio / Accuracy / Settings tabs — all styled correctly (no FOUC). 4. Resize viewport to &lt;1024px — tablet/phone media queries fire correctly. 5. View source — inline &lt;style&gt; ends around line 749 (vs 1044 before). 6. Lighthouse FCP should improve ~50-150ms vs PERF-7-only baseline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="161" ht="135" customHeight="1">
+          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~1.5MB) + data_perf.json + data_killed.json + data_earnings.json + data_screener.json + data_crypto.json (and the legacy data.json for backward compat). 2. Open /v2/dashboard.html in DevTools Network — boot fetches data.critical.json (~1.5MB), not data.json (5.3MB). 3. Click Performance / Killed / Earnings / Screener / Crypto tabs — each fetches its data_&lt;name&gt;.json once (memoized). 4. Default short_term tab + Range filters (mt/lt) + sidebar counts (Screener N) render correctly at boot from the critical bundle's _chunk_counts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="75" customHeight="1">
       <c r="A161" s="2" t="n">
         <v>160</v>
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>PERF-7</t>
+          <t>PERF-OPT</t>
         </is>
       </c>
       <c r="C161" s="9" t="inlineStr">
@@ -9304,37 +9328,29 @@
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Performance / Backtest</t>
         </is>
       </c>
       <c r="E161" s="6" t="inlineStr">
         <is>
-          <t>Split data.json (5.3MB) into critical + deferred</t>
+          <t>Backtest resource optimizations (PERF-OPT-1..4)</t>
         </is>
       </c>
       <c r="F161" s="5" t="inlineStr">
         <is>
-          <t>Dashboard cold load now bound by 5.3MB data.json fetch + parse — bulk of remaining 644ms init-end.</t>
+          <t>Backtest harness was IO-bound and CPU-bound when running 750d windows: serial OHLCV reads, redundant fundamental fetches inside the per-day loop, full-array recompute on every signal evaluation. 750d run was taking 4-8h.</t>
         </is>
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
-          <t>Decompose data.json: ship critical subset (regime, sector strip, top-5 picks per cell) inline or separate small JSON; defer the rest (full audit grid, all sector data, history) to lazy fetches per tab. Update build_data.py + dashboard.html.</t>
-        </is>
-      </c>
-      <c r="H161" s="2" t="inlineStr">
-        <is>
-          <t>4 hrs</t>
-        </is>
-      </c>
-      <c r="I161" s="5" t="inlineStr">
-        <is>
-          <t>Win: -300-800ms cold load (single largest remaining boot lever).</t>
-        </is>
-      </c>
+          <t>Four optimizations: (1) batch OHLCV reads parallel via thread pool; (2) memoize fundamentals lookup per ticker; (3) precompute regime classifications once per simulated day rather than per signal; (4) skip redundant point-in-time membership checks when universe is static.</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr"/>
+      <c r="I161" s="5" t="inlineStr"/>
       <c r="J161" s="5" t="inlineStr">
         <is>
-          <t>Biggest lever for next perf sprint. Phase 1+2 shipped: defers performance/killed/earnings/screener/crypto. Phase 2b (medium_term/long_term lazy on Range filter) tracked as PERF-7b.</t>
+          <t>4-fold speedup on 250d backtests (~6h → ~1.5h). Critical for the WF auto-validation loop closure (running 4 folds × grid search becomes feasible overnight).</t>
         </is>
       </c>
       <c r="K161" s="12" t="inlineStr">
@@ -9349,22 +9365,22 @@
       </c>
       <c r="M161" s="3" t="inlineStr">
         <is>
-          <t>114646f23</t>
+          <t>94c0c5a01</t>
         </is>
       </c>
       <c r="N161" s="8" t="inlineStr">
         <is>
-          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~1.5MB) + data_perf.json + data_killed.json + data_earnings.json + data_screener.json + data_crypto.json (and the legacy data.json for backward compat). 2. Open /v2/dashboard.html in DevTools Network — boot fetches data.critical.json (~1.5MB), not data.json (5.3MB). 3. Click Performance / Killed / Earnings / Screener / Crypto tabs — each fetches its data_&lt;name&gt;.json once (memoized). 4. Default short_term tab + Range filters (mt/lt) + sidebar counts (Screener N) render correctly at boot from the critical bundle's _chunk_counts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="162" ht="75" customHeight="1">
+          <t>1. time python3 backtest.py --window 250d → expect &lt;1.5h on M1/M2 (was 4-8h). 2. Memory peak &lt;4GB (was OOM-ing on 750d runs). 3. PF/WR/total_return must MATCH the pre-optimization run within rounding (no behavior change, just speed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="105" customHeight="1">
       <c r="A162" s="2" t="n">
         <v>161</v>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT</t>
+          <t>QUANT-3</t>
         </is>
       </c>
       <c r="C162" s="9" t="inlineStr">
@@ -9374,29 +9390,37 @@
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>Performance / Backtest</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E162" s="6" t="inlineStr">
         <is>
-          <t>Backtest resource optimizations (PERF-OPT-1..4)</t>
+          <t>Score-band filters per regime (e.g., min 70 in choppy)</t>
         </is>
       </c>
       <c r="F162" s="5" t="inlineStr">
         <is>
-          <t>Backtest harness was IO-bound and CPU-bound when running 750d windows: serial OHLCV reads, redundant fundamental fetches inside the per-day loop, full-array recompute on every signal evaluation. 750d run was taking 4-8h.</t>
+          <t>Single buy_min_score per regime; needs band-specific filtering (e.g., choppy may benefit from 70-90 only).</t>
         </is>
       </c>
       <c r="G162" s="5" t="inlineStr">
         <is>
-          <t>Four optimizations: (1) batch OHLCV reads parallel via thread pool; (2) memoize fundamentals lookup per ticker; (3) precompute regime classifications once per simulated day rather than per signal; (4) skip redundant point-in-time membership checks when universe is static.</t>
-        </is>
-      </c>
-      <c r="H162" s="2" t="inlineStr"/>
-      <c r="I162" s="5" t="inlineStr"/>
+          <t>Extend regime4_thresholds with optional score_band [lo, hi] per regime. Update decision_engine to honor band. Backtest each band per regime on 750d window.</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>2-4 hrs</t>
+        </is>
+      </c>
+      <c r="I162" s="5" t="inlineStr">
+        <is>
+          <t>Sequence: AFTER Sunday QUANT-1 re-validation.</t>
+        </is>
+      </c>
       <c r="J162" s="5" t="inlineStr">
         <is>
-          <t>4-fold speedup on 250d backtests (~6h → ~1.5h). Critical for the WF auto-validation loop closure (running 4 folds × grid search becomes feasible overnight).</t>
+          <t>Infrastructure shipped 2026-05-10. score_band_buy: [lo, hi] shorthand added at analysis.py:6655 area, overrides both buy_min_score + buy_max_score when present in regime4_thresholds. Backward compat: existing buy_min_score/buy_max_score (Q1-step6) still work. Variant playbook entry: config/variants/H_score_band_per_regime.json. Bands left UNSET in main config — user opts in by editing config when evidence collected per regime.</t>
         </is>
       </c>
       <c r="K162" s="12" t="inlineStr">
@@ -9411,22 +9435,22 @@
       </c>
       <c r="M162" s="3" t="inlineStr">
         <is>
-          <t>94c0c5a01</t>
+          <t>pending-this-commit</t>
         </is>
       </c>
       <c r="N162" s="8" t="inlineStr">
         <is>
-          <t>1. time python3 backtest.py --window 250d → expect &lt;1.5h on M1/M2 (was 4-8h). 2. Memory peak &lt;4GB (was OOM-ing on 750d runs). 3. PF/WR/total_return must MATCH the pre-optimization run within rounding (no behavior change, just speed).</t>
-        </is>
-      </c>
-    </row>
-    <row r="163" ht="105" customHeight="1">
+          <t>(1) python3 backtest.py --portfolio --days 250 --config-override config/variants/H_score_band_per_regime.json → cache/portfolio_backtest.json shows trades within band. (2) Set regime4_thresholds.&lt;regime&gt;.score_band_buy=[X, Y] in config.json → live engine should reject scores outside [X, Y].</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="60" customHeight="1">
       <c r="A163" s="2" t="n">
         <v>162</v>
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>QUANT-3</t>
+          <t>QUANT-4</t>
         </is>
       </c>
       <c r="C163" s="9" t="inlineStr">
@@ -9441,32 +9465,32 @@
       </c>
       <c r="E163" s="6" t="inlineStr">
         <is>
-          <t>Score-band filters per regime (e.g., min 70 in choppy)</t>
+          <t>Walk-forward fold persistence (Supabase dual-write)</t>
         </is>
       </c>
       <c r="F163" s="5" t="inlineStr">
         <is>
-          <t>Single buy_min_score per regime; needs band-specific filtering (e.g., choppy may benefit from 70-90 only).</t>
+          <t>Walk-forward runs write to local cache only — hard to cross-compare or audit historical decisions.</t>
         </is>
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>Extend regime4_thresholds with optional score_band [lo, hi] per regime. Update decision_engine to honor band. Backtest each band per regime on 750d window.</t>
+          <t>Extend hedge_fund_enhancers / walk_forward_v2 to dual-write fold results to Supabase walk_forward_runs + walk_forward_folds (mirror existing backtest_runs/backtest_trades).</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>2-4 hrs</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I163" s="5" t="inlineStr">
         <is>
-          <t>Sequence: AFTER Sunday QUANT-1 re-validation.</t>
+          <t>Win: cross-run analytics + audit trail.</t>
         </is>
       </c>
       <c r="J163" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure shipped 2026-05-10. score_band_buy: [lo, hi] shorthand added at analysis.py:6655 area, overrides both buy_min_score + buy_max_score when present in regime4_thresholds. Backward compat: existing buy_min_score/buy_max_score (Q1-step6) still work. Variant playbook entry: config/variants/H_score_band_per_regime.json. Bands left UNSET in main config — user opts in by editing config when evidence collected per regime.</t>
+          <t>Low priority — local cache works for now. · Pure best-effort dual-write: swallows Supabase failures so WF execution never fails. Live in backtest/walk_forward_v2.py:642 right after JSON write.</t>
         </is>
       </c>
       <c r="K163" s="12" t="inlineStr">
@@ -9481,22 +9505,22 @@
       </c>
       <c r="M163" s="3" t="inlineStr">
         <is>
-          <t>pending-this-commit</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N163" s="8" t="inlineStr">
         <is>
-          <t>(1) python3 backtest.py --portfolio --days 250 --config-override config/variants/H_score_band_per_regime.json → cache/portfolio_backtest.json shows trades within band. (2) Set regime4_thresholds.&lt;regime&gt;.score_band_buy=[X, Y] in config.json → live engine should reject scores outside [X, Y].</t>
-        </is>
-      </c>
-    </row>
-    <row r="164" ht="60" customHeight="1">
+          <t>After WF run finishes: psql/Supabase → SELECT * FROM walk_forward_folds WHERE run_id LIKE 'wf_%' ORDER BY id DESC LIMIT 4 → 4 fold rows present matching cache/walk_forward_v2_results.json folds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="105" customHeight="1">
       <c r="A164" s="2" t="n">
         <v>163</v>
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>QUANT-4</t>
+          <t>QUANT-6</t>
         </is>
       </c>
       <c r="C164" s="9" t="inlineStr">
@@ -9511,32 +9535,32 @@
       </c>
       <c r="E164" s="6" t="inlineStr">
         <is>
-          <t>Walk-forward fold persistence (Supabase dual-write)</t>
+          <t>Regime-conditional entries (rules vary per regime)</t>
         </is>
       </c>
       <c r="F164" s="5" t="inlineStr">
         <is>
-          <t>Walk-forward runs write to local cache only — hard to cross-compare or audit historical decisions.</t>
+          <t>Same 5-pillar gates apply across all 4 regimes — real regimes have different optimal entry rules.</t>
         </is>
       </c>
       <c r="G164" s="5" t="inlineStr">
         <is>
-          <t>Extend hedge_fund_enhancers / walk_forward_v2 to dual-write fold results to Supabase walk_forward_runs + walk_forward_folds (mirror existing backtest_runs/backtest_trades).</t>
+          <t>Define per-regime entry rule sets (entry_quality minimum, ATR multiplier on stops, hold-period default). Wire into analysis.py gate logic. Backtest per-regime to measure differential.</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>1 hr</t>
+          <t>4-6 hrs</t>
         </is>
       </c>
       <c r="I164" s="5" t="inlineStr">
         <is>
-          <t>Win: cross-run analytics + audit trail.</t>
+          <t>Risk: MEDIUM (more knobs = more overfit risk).</t>
         </is>
       </c>
       <c r="J164" s="5" t="inlineStr">
         <is>
-          <t>Low priority — local cache works for now. · Pure best-effort dual-write: swallows Supabase failures so WF execution never fails. Live in backtest/walk_forward_v2.py:642 right after JSON write.</t>
+          <t>Infrastructure shipped 2026-05-10 — regime4_thresholds.&lt;regime&gt;.entry_quality_rules now overrides global config.entry_quality_rules when present. analysis.py:6762 area block extended to read regime-specific rules first. Variant playbook: config/variants/I_regime_entry_rules.json with hypothesized rules per regime (FRESH-only in choppy, full breadth in trending, AVOID-bar in risk-off). Bands left UNSET in main config (no behavior change) — user opts in.</t>
         </is>
       </c>
       <c r="K164" s="12" t="inlineStr">
@@ -9551,22 +9575,22 @@
       </c>
       <c r="M164" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N164" s="8" t="inlineStr">
         <is>
-          <t>After WF run finishes: psql/Supabase → SELECT * FROM walk_forward_folds WHERE run_id LIKE 'wf_%' ORDER BY id DESC LIMIT 4 → 4 fold rows present matching cache/walk_forward_v2_results.json folds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="165" ht="105" customHeight="1">
+          <t>python3 backtest.py --portfolio --days 250 --config-override config/variants/I_regime_entry_rules.json. Compare per-regime trade counts vs baseline — choppy regime trades should drop sharply (FRESH-only).</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="60" customHeight="1">
       <c r="A165" s="2" t="n">
         <v>164</v>
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>QUANT-6</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="C165" s="9" t="inlineStr">
@@ -9576,37 +9600,37 @@
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Quant / Forensics</t>
         </is>
       </c>
       <c r="E165" s="6" t="inlineStr">
         <is>
-          <t>Regime-conditional entries (rules vary per regime)</t>
+          <t>Catalyst trade decomposition tool</t>
         </is>
       </c>
       <c r="F165" s="5" t="inlineStr">
         <is>
-          <t>Same 5-pillar gates apply across all 4 regimes — real regimes have different optimal entry rules.</t>
+          <t>Need to know WHICH catalyst sub-types drive performance (vs just the meta family).</t>
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>Define per-regime entry rule sets (entry_quality minimum, ATR multiplier on stops, hold-period default). Wire into analysis.py gate logic. Backtest per-regime to measure differential.</t>
+          <t>decompose_catalyst_trades.py — outputs cache/catalyst_decomposition_*.html. Found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 (n=134) — at meta-family granularity. Per-subtype attribution still pending.</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>4-6 hrs</t>
+          <t>shipped (tool); pending (subtype attribution)</t>
         </is>
       </c>
       <c r="I165" s="5" t="inlineStr">
         <is>
-          <t>Risk: MEDIUM (more knobs = more overfit risk).</t>
+          <t>Win: forensic visibility into catalyst sub-performance.</t>
         </is>
       </c>
       <c r="J165" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure shipped 2026-05-10 — regime4_thresholds.&lt;regime&gt;.entry_quality_rules now overrides global config.entry_quality_rules when present. analysis.py:6762 area block extended to read regime-specific rules first. Variant playbook: config/variants/I_regime_entry_rules.json with hypothesized rules per regime (FRESH-only in choppy, full breadth in trending, AVOID-bar in risk-off). Bands left UNSET in main config (no behavior change) — user opts in.</t>
+          <t>A5-followup wired the meta-family Wilson rule into signal_filter (status DRAFT until subtype attribution).</t>
         </is>
       </c>
       <c r="K165" s="12" t="inlineStr">
@@ -9616,27 +9640,27 @@
       </c>
       <c r="L165" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M165" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N165" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --portfolio --days 250 --config-override config/variants/I_regime_entry_rules.json. Compare per-regime trade counts vs baseline — choppy regime trades should drop sharply (FRESH-only).</t>
-        </is>
-      </c>
-    </row>
-    <row r="166" ht="60" customHeight="1">
+          <t>Open cache/catalyst_decomposition_2026-05-09.html → see ranked sub-strategies. Top survivor: 'pullback excl. Breakout/TC' n=134 WR 53% PF 1.83.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="120" customHeight="1">
       <c r="A166" s="2" t="n">
         <v>165</v>
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>A5-followup</t>
         </is>
       </c>
       <c r="C166" s="9" t="inlineStr">
@@ -9646,37 +9670,37 @@
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>Quant / Forensics</t>
+          <t>Quant / Signal Filter</t>
         </is>
       </c>
       <c r="E166" s="6" t="inlineStr">
         <is>
-          <t>Catalyst trade decomposition tool</t>
+          <t>Add Wilson-backed pullback rule to signal_filter._validations (DRAFT)</t>
         </is>
       </c>
       <c r="F166" s="5" t="inlineStr">
         <is>
-          <t>Need to know WHICH catalyst sub-types drive performance (vs just the meta family).</t>
+          <t>A5 found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 over n=134 — but at meta-family granularity. Per-subtype attribution (EMA21 vs EMA50 vs Bounce-off-Support) needed before activating; composition risk too high.</t>
         </is>
       </c>
       <c r="G166" s="5" t="inlineStr">
         <is>
-          <t>decompose_catalyst_trades.py — outputs cache/catalyst_decomposition_*.html. Found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 (n=134) — at meta-family granularity. Per-subtype attribution still pending.</t>
+          <t>Added _validations entry pullback_bull_701_pullback_or_fresh + draft whitelist rule. _enabled stays false until per-subtype split is verified.</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>shipped (tool); pending (subtype attribution)</t>
+          <t>shipped (DRAFT)</t>
         </is>
       </c>
       <c r="I166" s="5" t="inlineStr">
         <is>
-          <t>Win: forensic visibility into catalyst sub-performance.</t>
+          <t>Risk: activating without subtype attribution may re-enable EMA21 Pullback (which has its own bad evidence WR 11.9% n=59).</t>
         </is>
       </c>
       <c r="J166" s="5" t="inlineStr">
         <is>
-          <t>A5-followup wired the meta-family Wilson rule into signal_filter (status DRAFT until subtype attribution).</t>
+          <t>Per-subtype attribution computed from signal_log (n=550 closed). Updated config.setup_score_multiplier with evidence-based values: TC 0.0→1.0 (positive expectancy n=140), VCP 0.0→1.3 (avg +5.77% n=80), 10-Week Pullback 1.5× (high-edge), EMA21 Pullback kept killed (Wilson LB 5.9%), 52wk Breakout kept killed, Pocket Pivot 0.85→0.7. Full _validations block written to config.json with Wilson LB, avg PnL, n per setup. GATE-1 confirmed QUANT-1 was starving the system at 0 BUYs over 3 months — reverted today.</t>
         </is>
       </c>
       <c r="K166" s="12" t="inlineStr">
@@ -9686,7 +9710,7 @@
       </c>
       <c r="L166" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M166" s="3" t="inlineStr">
@@ -9696,17 +9720,17 @@
       </c>
       <c r="N166" s="8" t="inlineStr">
         <is>
-          <t>Open cache/catalyst_decomposition_2026-05-09.html → see ranked sub-strategies. Top survivor: 'pullback excl. Breakout/TC' n=134 WR 53% PF 1.83.</t>
-        </is>
-      </c>
-    </row>
-    <row r="167" ht="120" customHeight="1">
+          <t>Run python3 swing_trade.py — should produce non-zero BUYs (was 0 with QUANT-1 config). Confirm setup_score_multiplier loaded by checking log line "active config" or grep "Trend Continuation" in scan output. Spot-check a TC ticker in V2 dashboard — setup_size_multiplier should show 1.0× not 0.0×.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="75" customHeight="1">
       <c r="A167" s="2" t="n">
         <v>166</v>
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>A5-followup</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="C167" s="9" t="inlineStr">
@@ -9716,37 +9740,37 @@
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>Quant / Signal Filter</t>
+          <t>Quant / Stop Engine</t>
         </is>
       </c>
       <c r="E167" s="6" t="inlineStr">
         <is>
-          <t>Add Wilson-backed pullback rule to signal_filter._validations (DRAFT)</t>
+          <t>Stop confluence with Fibonacci + EMA 50</t>
         </is>
       </c>
       <c r="F167" s="5" t="inlineStr">
         <is>
-          <t>A5 found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 over n=134 — but at meta-family granularity. Per-subtype attribution (EMA21 vs EMA50 vs Bounce-off-Support) needed before activating; composition risk too high.</t>
+          <t>ATR-based stops were placed in isolation, ignoring proven structural levels (Fib retracements + EMA50). Vinod's coaching: snap stops to confluence so the stop sits at a level the market is already respecting.</t>
         </is>
       </c>
       <c r="G167" s="5" t="inlineStr">
         <is>
-          <t>Added _validations entry pullback_bull_701_pullback_or_fresh + draft whitelist rule. _enabled stays false until per-subtype split is verified.</t>
+          <t>compute_trade_plan in analysis.py:5223 — after ATR stop calculated, snap to highest-of-{Fib 0.382/0.5/0.618, EMA50} that's BELOW entry within 1.0% tolerance. Pulls stop UP to confluence (preserves R:R) when valid. Config: scoring.stop_confluence (enabled by default).</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>shipped (DRAFT)</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I167" s="5" t="inlineStr">
         <is>
-          <t>Risk: activating without subtype attribution may re-enable EMA21 Pullback (which has its own bad evidence WR 11.9% n=59).</t>
+          <t>Win: stops at structural levels reduce noise stop-outs.</t>
         </is>
       </c>
       <c r="J167" s="5" t="inlineStr">
         <is>
-          <t>Per-subtype attribution computed from signal_log (n=550 closed). Updated config.setup_score_multiplier with evidence-based values: TC 0.0→1.0 (positive expectancy n=140), VCP 0.0→1.3 (avg +5.77% n=80), 10-Week Pullback 1.5× (high-edge), EMA21 Pullback kept killed (Wilson LB 5.9%), 52wk Breakout kept killed, Pocket Pivot 0.85→0.7. Full _validations block written to config.json with Wilson LB, avg PnL, n per setup. GATE-1 confirmed QUANT-1 was starving the system at 0 BUYs over 3 months — reverted today.</t>
+          <t>Longs only. Try/except wrapped — never fails trade_plan.</t>
         </is>
       </c>
       <c r="K167" s="12" t="inlineStr">
@@ -9756,27 +9780,27 @@
       </c>
       <c r="L167" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M167" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>3d4eb71d7</t>
         </is>
       </c>
       <c r="N167" s="8" t="inlineStr">
         <is>
-          <t>Run python3 swing_trade.py — should produce non-zero BUYs (was 0 with QUANT-1 config). Confirm setup_score_multiplier loaded by checking log line "active config" or grep "Trend Continuation" in scan output. Spot-check a TC ticker in V2 dashboard — setup_size_multiplier should show 1.0× not 0.0×.</t>
-        </is>
-      </c>
-    </row>
-    <row r="168" ht="75" customHeight="1">
+          <t>Run: python3 swing_trade.py deep HPE → Plan tab → confirm stop is near a Fib retracement OR EMA50 (within 1%). Should NOT be a flat 1.25×ATR distance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="60" customHeight="1">
       <c r="A168" s="2" t="n">
         <v>167</v>
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="C168" s="9" t="inlineStr">
@@ -9791,17 +9815,17 @@
       </c>
       <c r="E168" s="6" t="inlineStr">
         <is>
-          <t>Stop confluence with Fibonacci + EMA 50</t>
+          <t>VWAP/AVWAP below stop = risk_flag</t>
         </is>
       </c>
       <c r="F168" s="5" t="inlineStr">
         <is>
-          <t>ATR-based stops were placed in isolation, ignoring proven structural levels (Fib retracements + EMA50). Vinod's coaching: snap stops to confluence so the stop sits at a level the market is already respecting.</t>
+          <t>When VWAP-20d or AVWAP-swing-low is below the stop, the trade is structurally weak (price already lost the volume-weighted reference). Vinod: this is a 'hard check.'</t>
         </is>
       </c>
       <c r="G168" s="5" t="inlineStr">
         <is>
-          <t>compute_trade_plan in analysis.py:5223 — after ATR stop calculated, snap to highest-of-{Fib 0.382/0.5/0.618, EMA50} that's BELOW entry within 1.0% tolerance. Pulls stop UP to confluence (preserves R:R) when valid. Config: scoring.stop_confluence (enabled by default).</t>
+          <t>After plan finalized, append plan['risk_flags'] entry severity=high if VWAP-20d or AVWAP-swing-low &lt; stop (longs). Soft-flag, does NOT block BUY (decision_engine surfaces).</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
@@ -9811,12 +9835,12 @@
       </c>
       <c r="I168" s="5" t="inlineStr">
         <is>
-          <t>Win: stops at structural levels reduce noise stop-outs.</t>
+          <t>Win: surfaces structurally weak trades without over-blocking.</t>
         </is>
       </c>
       <c r="J168" s="5" t="inlineStr">
         <is>
-          <t>Longs only. Try/except wrapped — never fails trade_plan.</t>
+          <t>Vinod said 'hard check' but blocking would over-fire — flag is right level.</t>
         </is>
       </c>
       <c r="K168" s="12" t="inlineStr">
@@ -9836,17 +9860,17 @@
       </c>
       <c r="N168" s="8" t="inlineStr">
         <is>
-          <t>Run: python3 swing_trade.py deep HPE → Plan tab → confirm stop is near a Fib retracement OR EMA50 (within 1%). Should NOT be a flat 1.25×ATR distance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="169" ht="60" customHeight="1">
+          <t>Find a ticker where VWAP &lt; stop. Run: python3 swing_trade.py deep &lt;TICKER&gt; → Plan tab → confirm risk_flags includes 'vwap_below_stop' with severity=high.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="75" customHeight="1">
       <c r="A169" s="2" t="n">
         <v>168</v>
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>K5</t>
         </is>
       </c>
       <c r="C169" s="9" t="inlineStr">
@@ -9856,22 +9880,22 @@
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>Quant / Stop Engine</t>
+          <t>Quant / Targets</t>
         </is>
       </c>
       <c r="E169" s="6" t="inlineStr">
         <is>
-          <t>VWAP/AVWAP below stop = risk_flag</t>
+          <t>Elliott Wave classification + Fib-extension targets</t>
         </is>
       </c>
       <c r="F169" s="5" t="inlineStr">
         <is>
-          <t>When VWAP-20d or AVWAP-swing-low is below the stop, the trade is structurally weak (price already lost the volume-weighted reference). Vinod: this is a 'hard check.'</t>
+          <t>Default targets are ATR/resistance-based — under-target Wave-3 expansions. Vinod on HPE: 'Wave 3 Impulse, T1 50.37, T2 55.75' — Fib extensions of swing.</t>
         </is>
       </c>
       <c r="G169" s="5" t="inlineStr">
         <is>
-          <t>After plan finalized, append plan['risk_flags'] entry severity=high if VWAP-20d or AVWAP-swing-low &lt; stop (longs). Soft-flag, does NOT block BUY (decision_engine surfaces).</t>
+          <t>New classify_elliott_wave(df, lookback=90, fib_extensions=[1.272, 1.618]) heuristic Wave-3 detector. When confidence ≥ medium, override default targets with Fib extensions IF higher and within reason (T1 ≤ +50%, T2 ≤ +100% sanity bound). Exposes plan['elliott_wave'] for Models tab.</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -9881,12 +9905,12 @@
       </c>
       <c r="I169" s="5" t="inlineStr">
         <is>
-          <t>Win: surfaces structurally weak trades without over-blocking.</t>
+          <t>Win: more aspirational targets in confirmed impulse waves.</t>
         </is>
       </c>
       <c r="J169" s="5" t="inlineStr">
         <is>
-          <t>Vinod said 'hard check' but blocking would over-fire — flag is right level.</t>
+          <t>Wave 2 corrective + low-confidence Wave 3 informational only — don't override default targets.</t>
         </is>
       </c>
       <c r="K169" s="12" t="inlineStr">
@@ -9901,22 +9925,22 @@
       </c>
       <c r="M169" s="3" t="inlineStr">
         <is>
-          <t>3d4eb71d7</t>
+          <t>302e9ea00</t>
         </is>
       </c>
       <c r="N169" s="8" t="inlineStr">
         <is>
-          <t>Find a ticker where VWAP &lt; stop. Run: python3 swing_trade.py deep &lt;TICKER&gt; → Plan tab → confirm risk_flags includes 'vwap_below_stop' with severity=high.</t>
-        </is>
-      </c>
-    </row>
-    <row r="170" ht="75" customHeight="1">
+          <t>python3 swing_trade.py deep HPE → Models tab → Elliott section shows wave=3, type=impulse, T1/T2 as Fib extensions (1.272×, 1.618× of swing).</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="90" customHeight="1">
       <c r="A170" s="2" t="n">
         <v>169</v>
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>K5</t>
+          <t>K4</t>
         </is>
       </c>
       <c r="C170" s="9" t="inlineStr">
@@ -9926,37 +9950,37 @@
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>Quant / Targets</t>
+          <t>Quant / Technicals</t>
         </is>
       </c>
       <c r="E170" s="6" t="inlineStr">
         <is>
-          <t>Elliott Wave classification + Fib-extension targets</t>
+          <t>EMA 5 + EMA 13 added to Technical pillar (Vinod faster-stack)</t>
         </is>
       </c>
       <c r="F170" s="5" t="inlineStr">
         <is>
-          <t>Default targets are ATR/resistance-based — under-target Wave-3 expansions. Vinod on HPE: 'Wave 3 Impulse, T1 50.37, T2 55.75' — Fib extensions of swing.</t>
+          <t>Vinod coaching: faster EMAs (5/13) catch short-term momentum changes the swing-trade horizon (2-5d) needs.</t>
         </is>
       </c>
       <c r="G170" s="5" t="inlineStr">
         <is>
-          <t>New classify_elliott_wave(df, lookback=90, fib_extensions=[1.272, 1.618]) heuristic Wave-3 detector. When confidence ≥ medium, override default targets with Fib extensions IF higher and within reason (T1 ≤ +50%, T2 ≤ +100% sanity bound). Exposes plan['elliott_wave'] for Models tab.</t>
+          <t>EMAs already computed (analysis.py:2775-2779) + ema5_above_13 already drives Holy Grail trigger (line 2839). Exposed raw ema5 + ema13 values in indicators dict (line 2876) so Technicals tab can display them. NO direct score weight added per OPERATING MINDSET principle 7 — score-weight decision pending 30 days of signal_log evidence.</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>shipped (additive only)</t>
         </is>
       </c>
       <c r="I170" s="5" t="inlineStr">
         <is>
-          <t>Win: more aspirational targets in confirmed impulse waves.</t>
+          <t>Win: visible to user without changing scoring (no overfit risk). Score weight decision deferred until backtest evidence.</t>
         </is>
       </c>
       <c r="J170" s="5" t="inlineStr">
         <is>
-          <t>Wave 2 corrective + low-confidence Wave 3 informational only — don't override default targets.</t>
+          <t>Score weight pending 30-day signal corpus + backtest validation.</t>
         </is>
       </c>
       <c r="K170" s="12" t="inlineStr">
@@ -9966,17 +9990,17 @@
       </c>
       <c r="L170" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M170" s="3" t="inlineStr">
         <is>
-          <t>302e9ea00</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N170" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep HPE → Models tab → Elliott section shows wave=3, type=impulse, T1/T2 as Fib extensions (1.272×, 1.618× of swing).</t>
+          <t>python3 swing_trade.py deep AAPL → Technicals tab → confirm EMA 5 and EMA 13 both display with current values. ema5_above_13 boolean visible.</t>
         </is>
       </c>
     </row>
@@ -9986,7 +10010,7 @@
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>BREADTH-ALIGN</t>
         </is>
       </c>
       <c r="C171" s="9" t="inlineStr">
@@ -9996,39 +10020,27 @@
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>Quant / Technicals</t>
+          <t>Regime Classifier</t>
         </is>
       </c>
       <c r="E171" s="6" t="inlineStr">
         <is>
-          <t>EMA 5 + EMA 13 added to Technical pillar (Vinod faster-stack)</t>
+          <t>Align live breadth source with V4 backtest validation (SP500-only)</t>
         </is>
       </c>
       <c r="F171" s="5" t="inlineStr">
         <is>
-          <t>Vinod coaching: faster EMAs (5/13) catch short-term momentum changes the swing-trade horizon (2-5d) needs.</t>
+          <t>Live get_market_breadth iterated full scan universe (SP500 ∪ R1000 ∪ custom, ~1000 names), producing ~13pp higher breadth than V4 backtest validation (SP500 only, ~503 names). Today: live=64.0 vs backtest=50.9. V4 regime thresholds were validated on backtest definition, so live regime classifier fired differently than tested.</t>
         </is>
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
-          <t>EMAs already computed (analysis.py:2775-2779) + ema5_above_13 already drives Holy Grail trigger (line 2839). Exposed raw ema5 + ema13 values in indicators dict (line 2876) so Technicals tab can display them. NO direct score weight added per OPERATING MINDSET principle 7 — score-weight decision pending 30 days of signal_log evidence.</t>
-        </is>
-      </c>
-      <c r="H171" s="2" t="inlineStr">
-        <is>
-          <t>shipped (additive only)</t>
-        </is>
-      </c>
-      <c r="I171" s="5" t="inlineStr">
-        <is>
-          <t>Win: visible to user without changing scoring (no overfit risk). Score weight decision deferred until backtest evidence.</t>
-        </is>
-      </c>
-      <c r="J171" s="5" t="inlineStr">
-        <is>
-          <t>Score weight pending 30-day signal corpus + backtest validation.</t>
-        </is>
-      </c>
+          <t>Add universe_filter param to data_fetcher.get_market_breadth. Caller (swing_trade.py:869) passes set(get_sp500()). Updated regime_classifier._validations to mark caveat resolved.</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr"/>
+      <c r="I171" s="5" t="inlineStr"/>
+      <c r="J171" s="5" t="inlineStr"/>
       <c r="K171" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -10041,22 +10053,18 @@
       </c>
       <c r="M171" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="N171" s="8" t="inlineStr">
-        <is>
-          <t>python3 swing_trade.py deep AAPL → Technicals tab → confirm EMA 5 and EMA 13 both display with current values. ema5_above_13 boolean visible.</t>
-        </is>
-      </c>
-    </row>
-    <row r="172" ht="90" customHeight="1">
+          <t>4442fa300</t>
+        </is>
+      </c>
+      <c r="N171" s="8" t="inlineStr"/>
+    </row>
+    <row r="172" ht="45" customHeight="1">
       <c r="A172" s="2" t="n">
         <v>171</v>
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>BREADTH-ALIGN</t>
+          <t>RISK-CB-PAPER-OFF</t>
         </is>
       </c>
       <c r="C172" s="9" t="inlineStr">
@@ -10066,22 +10074,22 @@
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>Regime Classifier</t>
+          <t>Risk / Paper</t>
         </is>
       </c>
       <c r="E172" s="6" t="inlineStr">
         <is>
-          <t>Align live breadth source with V4 backtest validation (SP500-only)</t>
+          <t>Circuit breaker fully disabled for paper trading</t>
         </is>
       </c>
       <c r="F172" s="5" t="inlineStr">
         <is>
-          <t>Live get_market_breadth iterated full scan universe (SP500 ∪ R1000 ∪ custom, ~1000 names), producing ~13pp higher breadth than V4 backtest validation (SP500 only, ~503 names). Today: live=64.0 vs backtest=50.9. V4 regime thresholds were validated on backtest definition, so live regime classifier fired differently than tested.</t>
+          <t>drawdown circuit breaker OFF (config disabled flag honored in portfolio_tracker), 90-day Slack review reminder via daily scan</t>
         </is>
       </c>
       <c r="G172" s="5" t="inlineStr">
         <is>
-          <t>Add universe_filter param to data_fetcher.get_market_breadth. Caller (swing_trade.py:869) passes set(get_sp500()). Updated regime_classifier._validations to mark caveat resolved.</t>
+          <t>config.json circuit_breaker + portfolio_tracker + swing_trade reminder</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr"/>
@@ -10094,23 +10102,23 @@
       </c>
       <c r="L172" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="M172" s="3" t="inlineStr">
         <is>
-          <t>4442fa300</t>
+          <t>d85c5ac2d</t>
         </is>
       </c>
       <c r="N172" s="8" t="inlineStr"/>
     </row>
-    <row r="173" ht="45" customHeight="1">
+    <row r="173" ht="105" customHeight="1">
       <c r="A173" s="2" t="n">
         <v>172</v>
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>RISK-CB-PAPER-OFF</t>
+          <t>RULE-8GATE</t>
         </is>
       </c>
       <c r="C173" s="9" t="inlineStr">
@@ -10120,27 +10128,31 @@
       </c>
       <c r="D173" s="5" t="inlineStr">
         <is>
-          <t>Risk / Paper</t>
+          <t>Rule Engine / Visualization</t>
         </is>
       </c>
       <c r="E173" s="6" t="inlineStr">
         <is>
-          <t>Circuit breaker fully disabled for paper trading</t>
+          <t>Surface 8-gate decision cascade in Why-this-is-X tab</t>
         </is>
       </c>
       <c r="F173" s="5" t="inlineStr">
         <is>
-          <t>drawdown circuit breaker OFF (config disabled flag honored in portfolio_tracker), 90-day Slack review reminder via daily scan</t>
+          <t>Decision engine runs 8 gates per pick (regime, score-min, RR, sector, conviction, etc) but the Why-this-is-X tab showed only the final verdict + 5 pillars. Audit trail (gates_evaluated[], audit_trail.decided_by, caveats[]) was emitted by the engine but never displayed.</t>
         </is>
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>config.json circuit_breaker + portfolio_tracker + swing_trade reminder</t>
+          <t>Added Stage 2.5 'Decision Engine — 8-Gate Cascade' to subtabs/ruleengine/pipeline.js. Surfaces T.gates_evaluated array with pass/fail mark per gate, T.audit_trail.decided_by, and T.caveats (soft-gate non-blocking). Layered on top of the legacy Stage 2 pre-trade gate as fallback.</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr"/>
       <c r="I173" s="5" t="inlineStr"/>
-      <c r="J173" s="5" t="inlineStr"/>
+      <c r="J173" s="5" t="inlineStr">
+        <is>
+          <t>Visualization-only commit. Backend already emits gates_evaluated. Useful for debugging "why was this filtered to WATCH" — surfaces the exact gate failure to the user.</t>
+        </is>
+      </c>
       <c r="K173" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -10148,23 +10160,27 @@
       </c>
       <c r="L173" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M173" s="3" t="inlineStr">
         <is>
-          <t>d85c5ac2d</t>
-        </is>
-      </c>
-      <c r="N173" s="8" t="inlineStr"/>
-    </row>
-    <row r="174" ht="105" customHeight="1">
+          <t>40f8452b8</t>
+        </is>
+      </c>
+      <c r="N173" s="8" t="inlineStr">
+        <is>
+          <t>1. Open elite-detail.html?t=NVDA → click "Why this is X" sub-tab. 2. Look for "STAGE 2.5 — Decision Engine 8-Gate Cascade" between the existing Stage 2 (Pre-trade Gate) and Stage 3 (5-Pillar Scoring). 3. Each gate row shows ✓ or ✗ + reason. 4. Caveats card shows soft-gate caveats (non-blocking warnings). 5. Falls through silently if T.gates_evaluated is empty (engine didn't run on this bundle — legacy verdict path).</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="90" customHeight="1">
       <c r="A174" s="2" t="n">
         <v>173</v>
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>RULE-8GATE</t>
+          <t>BREAKOUT-BYPASS-LIVE</t>
         </is>
       </c>
       <c r="C174" s="9" t="inlineStr">
@@ -10174,31 +10190,27 @@
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>Rule Engine / Visualization</t>
+          <t>Signals · Gating</t>
         </is>
       </c>
       <c r="E174" s="6" t="inlineStr">
         <is>
-          <t>Surface 8-gate decision cascade in Why-this-is-X tab</t>
+          <t>Breakout-alpha entry_quality bypass enabled</t>
         </is>
       </c>
       <c r="F174" s="5" t="inlineStr">
         <is>
-          <t>Decision engine runs 8 gates per pick (regime, score-min, RR, sector, conviction, etc) but the Why-this-is-X tab showed only the final verdict + 5 pillars. Audit trail (gates_evaluated[], audit_trail.decided_by, caveats[]) was emitted by the engine but never displayed.</t>
+          <t>Alpha setups (VCP/52wk/10WP) were demoted to WATCH by entry_quality EXTENDED/MISSED gate (their natural state) + hidden under broad families. Surfaced granular setup_type in scanner + enabled entry_quality_breakout_bypass for alpha sub-types only (TC/BE excluded). Regime score floor still applies. Paper observation; backtest cant validate verdict changes.</t>
         </is>
       </c>
       <c r="G174" s="5" t="inlineStr">
         <is>
-          <t>Added Stage 2.5 'Decision Engine — 8-Gate Cascade' to subtabs/ruleengine/pipeline.js. Surfaces T.gates_evaluated array with pass/fail mark per gate, T.audit_trail.decided_by, and T.caveats (soft-gate non-blocking). Layered on top of the legacy Stage 2 pre-trade gate as fallback.</t>
+          <t>config.entry_quality_breakout_bypass._enabled=true + analysis.make_decision bypass + server setup_type surfacing</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr"/>
       <c r="I174" s="5" t="inlineStr"/>
-      <c r="J174" s="5" t="inlineStr">
-        <is>
-          <t>Visualization-only commit. Backend already emits gates_evaluated. Useful for debugging "why was this filtered to WATCH" — surfaces the exact gate failure to the user.</t>
-        </is>
-      </c>
+      <c r="J174" s="5" t="inlineStr"/>
       <c r="K174" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -10206,27 +10218,23 @@
       </c>
       <c r="L174" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="M174" s="3" t="inlineStr">
         <is>
-          <t>40f8452b8</t>
-        </is>
-      </c>
-      <c r="N174" s="8" t="inlineStr">
-        <is>
-          <t>1. Open elite-detail.html?t=NVDA → click "Why this is X" sub-tab. 2. Look for "STAGE 2.5 — Decision Engine 8-Gate Cascade" between the existing Stage 2 (Pre-trade Gate) and Stage 3 (5-Pillar Scoring). 3. Each gate row shows ✓ or ✗ + reason. 4. Caveats card shows soft-gate caveats (non-blocking warnings). 5. Falls through silently if T.gates_evaluated is empty (engine didn't run on this bundle — legacy verdict path).</t>
-        </is>
-      </c>
-    </row>
-    <row r="175" ht="90" customHeight="1">
+          <t>cc4338d9d</t>
+        </is>
+      </c>
+      <c r="N174" s="8" t="inlineStr"/>
+    </row>
+    <row r="175" ht="60" customHeight="1">
       <c r="A175" s="2" t="n">
         <v>174</v>
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>BREAKOUT-BYPASS-LIVE</t>
+          <t>CONVICTION-VERDICT-ALIGN</t>
         </is>
       </c>
       <c r="C175" s="9" t="inlineStr">
@@ -10236,22 +10244,22 @@
       </c>
       <c r="D175" s="5" t="inlineStr">
         <is>
-          <t>Signals · Gating</t>
+          <t>Signals · Sizing</t>
         </is>
       </c>
       <c r="E175" s="6" t="inlineStr">
         <is>
-          <t>Breakout-alpha entry_quality bypass enabled</t>
+          <t>Verdict=BUY masked 0-conviction names in scanner + executor</t>
         </is>
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
-          <t>Alpha setups (VCP/52wk/10WP) were demoted to WATCH by entry_quality EXTENDED/MISSED gate (their natural state) + hidden under broad families. Surfaced granular setup_type in scanner + enabled entry_quality_breakout_bypass for alpha sub-types only (TC/BE excluded). Regime score floor still applies. Paper observation; backtest cant validate verdict changes.</t>
+          <t>10 of 12 BUY-verdict names in risk_on_choppy were conviction=AVOID/size_mult 0; scanner ranked + executor traded them as if real buys, killing user confidence + buying 0-conviction names (ARMK/PBI/WDC)</t>
         </is>
       </c>
       <c r="G175" s="5" t="inlineStr">
         <is>
-          <t>config.entry_quality_breakout_bypass._enabled=true + analysis.make_decision bypass + server setup_type surfacing</t>
+          <t>executor.py conviction gate (skip 0-size, scale by size_mult); surface-signal.jsx conviction-aware Top Buys sort + tier column in Essentials</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr"/>
@@ -10269,18 +10277,18 @@
       </c>
       <c r="M175" s="3" t="inlineStr">
         <is>
-          <t>cc4338d9d</t>
+          <t>6a5a50549</t>
         </is>
       </c>
       <c r="N175" s="8" t="inlineStr"/>
     </row>
-    <row r="176" ht="60" customHeight="1">
+    <row r="176" ht="45" customHeight="1">
       <c r="A176" s="2" t="n">
         <v>175</v>
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>CONVICTION-VERDICT-ALIGN</t>
+          <t>CONFIG-1</t>
         </is>
       </c>
       <c r="C176" s="9" t="inlineStr">
@@ -10290,27 +10298,39 @@
       </c>
       <c r="D176" s="5" t="inlineStr">
         <is>
-          <t>Signals · Sizing</t>
+          <t>Strategy / Config</t>
         </is>
       </c>
       <c r="E176" s="6" t="inlineStr">
         <is>
-          <t>Verdict=BUY masked 0-conviction names in scanner + executor</t>
+          <t>Restore regime4_thresholds to documented baseline + variant playbook</t>
         </is>
       </c>
       <c r="F176" s="5" t="inlineStr">
         <is>
-          <t>10 of 12 BUY-verdict names in risk_on_choppy were conviction=AVOID/size_mult 0; scanner ranked + executor traded them as if real buys, killing user confidence + buying 0-conviction names (ARMK/PBI/WDC)</t>
+          <t>2026-05-08 raised buy_min to 80/80/85; produced 0 live BUYs. The 80 floor was not saving us — Variant F is the actual loser-cut.</t>
         </is>
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>executor.py conviction gate (skip 0-size, scale by size_mult); surface-signal.jsx conviction-aware Top Buys sort + tier column in Essentials</t>
-        </is>
-      </c>
-      <c r="H176" s="2" t="inlineStr"/>
-      <c r="I176" s="5" t="inlineStr"/>
-      <c r="J176" s="5" t="inlineStr"/>
+          <t>Restored: trending 65, choppy 72, risk-off 78 (per CLAUDE.md 4-Regime Detection table). Created config/variants/A/E2/G.json. Updated CLAUDE.md with 4 lessons.</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>30 min</t>
+        </is>
+      </c>
+      <c r="I176" s="5" t="inlineStr">
+        <is>
+          <t>High — restores live BUY flow without losing Variant F protection</t>
+        </is>
+      </c>
+      <c r="J176" s="5" t="inlineStr">
+        <is>
+          <t>Caveat: alone does not unblock todays top-5 WATCH (entry_quality blocked).</t>
+        </is>
+      </c>
       <c r="K176" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -10318,23 +10338,27 @@
       </c>
       <c r="L176" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M176" s="3" t="inlineStr">
         <is>
-          <t>6a5a50549</t>
-        </is>
-      </c>
-      <c r="N176" s="8" t="inlineStr"/>
-    </row>
-    <row r="177" ht="45" customHeight="1">
+          <t>363984181</t>
+        </is>
+      </c>
+      <c r="N176" s="8" t="inlineStr">
+        <is>
+          <t>config/config.json regime4_thresholds.risk_on_trending.buy_min_score = 65. Run /Swing-Trade — BUYs &gt; 0 when market gives FRESH entries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="90" customHeight="1">
       <c r="A177" s="2" t="n">
         <v>176</v>
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>CONFIG-1</t>
+          <t>EW-V1</t>
         </is>
       </c>
       <c r="C177" s="9" t="inlineStr">
@@ -10344,37 +10368,37 @@
       </c>
       <c r="D177" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Config</t>
+          <t>Strategy / Elliott Wave</t>
         </is>
       </c>
       <c r="E177" s="6" t="inlineStr">
         <is>
-          <t>Restore regime4_thresholds to documented baseline + variant playbook</t>
+          <t>EW Rule Gate v1.0 — 8-state classifier</t>
         </is>
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
-          <t>2026-05-08 raised buy_min to 80/80/85; produced 0 live BUYs. The 80 floor was not saving us — Variant F is the actual loser-cut.</t>
+          <t>Legacy classify_elliott_wave was heuristic Wave-3 detector only — 2 states (impulse/corrective). Needed full spec: 8 engine states, 3 absolute impulse rules, fractal pivots, Fibonacci retracements (23.6-88.6%) and extensions (100-423.6%), multi-timeframe alignment.</t>
         </is>
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>Restored: trending 65, choppy 72, risk-off 78 (per CLAUDE.md 4-Regime Detection table). Created config/variants/A/E2/G.json. Updated CLAUDE.md with 4 lessons.</t>
+          <t>New classify_elliott_wave_bhe() implements full BHE v1.0 spec. Fractal pivot detector via i±2 rule. 8 states with score 0-4 contribution. Rule 1 (W2 &lt; W1 start) invalidation. Multi-TF ready (Primary/Intermediate/Minor) — daily-only in Phase 1, weekly/4H wire-in Phase 2. Sibling gate_g3_quant_veto() combines EW + Monte Carlo + Wyckoff for the quant veto.</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>2 hrs</t>
         </is>
       </c>
       <c r="I177" s="5" t="inlineStr">
         <is>
-          <t>High — restores live BUY flow without losing Variant F protection</t>
+          <t>Low / High (transparency + future-proof)</t>
         </is>
       </c>
       <c r="J177" s="5" t="inlineStr">
         <is>
-          <t>Caveat: alone does not unblock todays top-5 WATCH (entry_quality blocked).</t>
+          <t>Runs in parallel to legacy classify_elliott_wave for backward compat. New result on plan as elliott_wave_v1. Smoke-tested: synthetic uptrend → WAVE3_IMPULSE score 4, T1/T2 from 1.618×/2.618×W1 fib extension.</t>
         </is>
       </c>
       <c r="K177" s="12" t="inlineStr">
@@ -10389,22 +10413,22 @@
       </c>
       <c r="M177" s="3" t="inlineStr">
         <is>
-          <t>363984181</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N177" s="8" t="inlineStr">
         <is>
-          <t>config/config.json regime4_thresholds.risk_on_trending.buy_min_score = 65. Run /Swing-Trade — BUYs &gt; 0 when market gives FRESH entries.</t>
-        </is>
-      </c>
-    </row>
-    <row r="178" ht="90" customHeight="1">
+          <t>python3 -c "from analysis import classify_elliott_wave_bhe, gate_g3_quant_veto; ..." with synthetic uptrend → WAVE3_IMPULSE / score 4. Open a ticker on elite-detail Models tab → elliott_wave_v1 field should populate with ew_state + score + t1/t2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="75" customHeight="1">
       <c r="A178" s="2" t="n">
         <v>177</v>
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>EW-V1</t>
+          <t>STRUCT-TARGETS-M21-INFRA</t>
         </is>
       </c>
       <c r="C178" s="9" t="inlineStr">
@@ -10414,39 +10438,27 @@
       </c>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Elliott Wave</t>
+          <t>Strategy / Targets</t>
         </is>
       </c>
       <c r="E178" s="6" t="inlineStr">
         <is>
-          <t>EW Rule Gate v1.0 — 8-state classifier</t>
+          <t>Structural targets · M2.1 — engine infra (cache, endpoint, precompute, flag)</t>
         </is>
       </c>
       <c r="F178" s="5" t="inlineStr">
         <is>
-          <t>Legacy classify_elliott_wave was heuristic Wave-3 detector only — 2 states (impulse/corrective). Needed full spec: 8 engine states, 3 absolute impulse rules, fractal pivots, Fibonacci retracements (23.6-88.6%) and extensions (100-423.6%), multi-timeframe alignment.</t>
+          <t>Shipped 2026-05-13: target_engine.py cache layer (12h TTL, atomic writes), GET /v2/trade_engine FastAPI endpoint (hybrid pre-compute + on-demand), scripts/precompute_targets.py batch runner (SP500 + R1000 + watchlist), run_daily_scan.sh hook at 06:00 only, config flag use_structural_targets:false.</t>
         </is>
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>New classify_elliott_wave_bhe() implements full BHE v1.0 spec. Fractal pivot detector via i±2 rule. 8 states with score 0-4 contribution. Rule 1 (W2 &lt; W1 start) invalidation. Multi-TF ready (Primary/Intermediate/Minor) — daily-only in Phase 1, weekly/4H wire-in Phase 2. Sibling gate_g3_quant_veto() combines EW + Monte Carlo + Wyckoff for the quant veto.</t>
-        </is>
-      </c>
-      <c r="H178" s="2" t="inlineStr">
-        <is>
-          <t>2 hrs</t>
-        </is>
-      </c>
-      <c r="I178" s="5" t="inlineStr">
-        <is>
-          <t>Low / High (transparency + future-proof)</t>
-        </is>
-      </c>
-      <c r="J178" s="5" t="inlineStr">
-        <is>
-          <t>Runs in parallel to legacy classify_elliott_wave for backward compat. New result on plan as elliott_wave_v1. Smoke-tested: synthetic uptrend → WAVE3_IMPULSE score 4, T1/T2 from 1.618×/2.618×W1 fib extension.</t>
-        </is>
-      </c>
+          <t>All five infra pieces wired and verified: 2,359× cache speedup, 8 ROST/AVGO/AAPL/NVDA cache files written, server.py syntax valid, feature flag confirmed OFF in config/config.json. Flag stays false until M2.5 cutover.</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr"/>
+      <c r="I178" s="5" t="inlineStr"/>
+      <c r="J178" s="5" t="inlineStr"/>
       <c r="K178" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -10454,7 +10466,7 @@
       </c>
       <c r="L178" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="M178" s="3" t="inlineStr">
@@ -10462,19 +10474,15 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="N178" s="8" t="inlineStr">
-        <is>
-          <t>python3 -c "from analysis import classify_elliott_wave_bhe, gate_g3_quant_veto; ..." with synthetic uptrend → WAVE3_IMPULSE / score 4. Open a ticker on elite-detail Models tab → elliott_wave_v1 field should populate with ew_state + score + t1/t2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="179" ht="75" customHeight="1">
+      <c r="N178" s="8" t="inlineStr"/>
+    </row>
+    <row r="179" ht="90" customHeight="1">
       <c r="A179" s="2" t="n">
         <v>178</v>
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>STRUCT-TARGETS-M21-INFRA</t>
+          <t>STRUCT-TARGETS-M22-DATA</t>
         </is>
       </c>
       <c r="C179" s="9" t="inlineStr">
@@ -10489,17 +10497,17 @@
       </c>
       <c r="E179" s="6" t="inlineStr">
         <is>
-          <t>Structural targets · M2.1 — engine infra (cache, endpoint, precompute, flag)</t>
+          <t>Structural targets · M2.2 — parallel fields in data.json (non-destructive)</t>
         </is>
       </c>
       <c r="F179" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-13: target_engine.py cache layer (12h TTL, atomic writes), GET /v2/trade_engine FastAPI endpoint (hybrid pre-compute + on-demand), scripts/precompute_targets.py batch runner (SP500 + R1000 + watchlist), run_daily_scan.sh hook at 06:00 only, config flag use_structural_targets:false.</t>
+          <t>Shipped 2026-05-13: build_data.py:compact_row now overlays t1_structural, t2_structural, t1_confluence, t1_sources, t1_behavior, t1_p_reach, t1_action, t1_r_multiple (and t2_* counterparts) onto every pickrow when config.use_structural_targets=true. Legacy t1/t2 (ATR-based) remain untouched — every existing consumer keeps working.</t>
         </is>
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>All five infra pieces wired and verified: 2,359× cache speedup, 8 ROST/AVGO/AAPL/NVDA cache files written, server.py syntax valid, feature flag confirmed OFF in config/config.json. Flag stays false until M2.5 cutover.</t>
+          <t>Gated by _structural_flag_enabled() lazy-loader; reads cache/target_engine/{TICKER}_{MODE}.json; emits structural_modes summary block (swing/position/invest) plus _te_mode_primary, _te_decision, _te_warnings diagnostics. Three-case unit test validated: flag-off no-op, flag-on with cache attaches fields, flag-on without cache no-op.</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr"/>
@@ -10528,7 +10536,7 @@
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>STRUCT-TARGETS-M22-DATA</t>
+          <t>STRUCT-TARGETS-M23-MODES</t>
         </is>
       </c>
       <c r="C180" s="9" t="inlineStr">
@@ -10543,17 +10551,17 @@
       </c>
       <c r="E180" s="6" t="inlineStr">
         <is>
-          <t>Structural targets · M2.2 — parallel fields in data.json (non-destructive)</t>
+          <t>Structural targets · M2.3 — mode completeness (short-gate, ETF degrade, earnings flag, INVEST stub)</t>
         </is>
       </c>
       <c r="F180" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-13: build_data.py:compact_row now overlays t1_structural, t2_structural, t1_confluence, t1_sources, t1_behavior, t1_p_reach, t1_action, t1_r_multiple (and t2_* counterparts) onto every pickrow when config.use_structural_targets=true. Legacy t1/t2 (ATR-based) remain untouched — every existing consumer keeps working.</t>
+          <t>Shipped 2026-05-13: target_engine.analyze_trade now (1) rejects direction=short with short_not_supported_v1 warning, (2) detects ETFs via _KNOWN_ETF_TICKERS list and degrades swing-floor 3→2 with etf_degraded warning, (3) flags earnings_imminent when EODHD calendar shows report within 7d, (4) falls back to analyst-PT-based INVEST stub when invest mode produces no structural T1.</t>
         </is>
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>Gated by _structural_flag_enabled() lazy-loader; reads cache/target_engine/{TICKER}_{MODE}.json; emits structural_modes summary block (swing/position/invest) plus _te_mode_primary, _te_decision, _te_warnings diagnostics. Three-case unit test validated: flag-off no-op, flag-on with cache attaches fields, flag-on without cache no-op.</t>
+          <t>TradeAnalysis dataclass extended with is_etf:bool, catalyst:dict, invest_stub:bool fields. All four paths green in unit tests: SHORT reject clean, SPY/QQQ/XLF flagged ETF, AMAT earnings-1d flag fired, AAPL invest_stub=true with analyst_pt × 1.0/1.3 targets.</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr"/>
@@ -10576,13 +10584,13 @@
       </c>
       <c r="N180" s="8" t="inlineStr"/>
     </row>
-    <row r="181" ht="90" customHeight="1">
+    <row r="181" ht="75" customHeight="1">
       <c r="A181" s="2" t="n">
         <v>180</v>
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>STRUCT-TARGETS-M23-MODES</t>
+          <t>STRUCT-TARGETS-M24-VALIDATION</t>
         </is>
       </c>
       <c r="C181" s="9" t="inlineStr">
@@ -10597,17 +10605,17 @@
       </c>
       <c r="E181" s="6" t="inlineStr">
         <is>
-          <t>Structural targets · M2.3 — mode completeness (short-gate, ETF degrade, earnings flag, INVEST stub)</t>
+          <t>Structural targets · M2.4 — regression suite + monitoring</t>
         </is>
       </c>
       <c r="F181" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-13: target_engine.analyze_trade now (1) rejects direction=short with short_not_supported_v1 warning, (2) detects ETFs via _KNOWN_ETF_TICKERS list and degrades swing-floor 3→2 with etf_degraded warning, (3) flags earnings_imminent when EODHD calendar shows report within 7d, (4) falls back to analyst-PT-based INVEST stub when invest mode produces no structural T1.</t>
+          <t>Shipped 2026-05-13: scripts/te_regression.py runs 20-ticker validation set (mega/mid/small cap + 5 ETFs) across swing+position modes, captures decision/warnings/latency/cache-status/T1-T2 vs legacy ATR diff_pct. Writes cache/logs/te_regression_&lt;TS&gt;.json + .md + append-only te_regression.log.</t>
         </is>
       </c>
       <c r="G181" s="5" t="inlineStr">
         <is>
-          <t>TradeAnalysis dataclass extended with is_etf:bool, catalyst:dict, invest_stub:bool fields. All four paths green in unit tests: SHORT reject clean, SPY/QQQ/XLF flagged ETF, AMAT earnings-1d flag fired, AAPL invest_stub=true with analyst_pt × 1.0/1.3 targets.</t>
+          <t>Baseline run 2026-05-13: 36/40 trade, 4 reject, 0 errors, median 7ms (cache-warm). ETF graceful-degrade fired 10 rows, earnings-imminent fired 2 (AMAT 1d). Use --quick for 5-ticker smoke, --fail-threshold N to set exit-code threshold. Exit 1 if errors &gt; threshold (default 5), exit 2 if no results.</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr"/>
@@ -10636,7 +10644,7 @@
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>STRUCT-TARGETS-M24-VALIDATION</t>
+          <t>TARGET-CAP-SWEEP</t>
         </is>
       </c>
       <c r="C182" s="9" t="inlineStr">
@@ -10646,22 +10654,22 @@
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Targets</t>
+          <t>Strategy/Target Sanity</t>
         </is>
       </c>
       <c r="E182" s="6" t="inlineStr">
         <is>
-          <t>Structural targets · M2.4 — regression suite + monitoring</t>
+          <t>Sweep for naive swing-high-as-target pattern across all scanners</t>
         </is>
       </c>
       <c r="F182" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-13: scripts/te_regression.py runs 20-ticker validation set (mega/mid/small cap + 5 ETFs) across swing+position modes, captures decision/warnings/latency/cache-status/T1-T2 vs legacy ATR diff_pct. Writes cache/logs/te_regression_&lt;TS&gt;.json + .md + append-only te_regression.log.</t>
+          <t>mean_reversion.py:354 (target2 = high.iloc[-20:].max() uncapped, latent) and pullback_scanner.py:113 (target = high_252 uncapped, UI API) had the same class of bug as weekly_pullback.py. Both fixed proactively. analysis.py:7766 calculate_trade_plan also has it but is dead code (no callers).</t>
         </is>
       </c>
       <c r="G182" s="5" t="inlineStr">
         <is>
-          <t>Baseline run 2026-05-13: 36/40 trade, 4 reject, 0 errors, median 7ms (cache-warm). ETF graceful-degrade fired 10 rows, earnings-imminent fired 2 (AMAT 1d). Use --quick for 5-ticker smoke, --fail-threshold N to set exit-code threshold. Exit 1 if errors &gt; threshold (default 5), exit 2 if no results.</t>
+          <t>Cap target2 at price*1.10 in mean_reversion.py, cap target at price*1.15 in pullback_scanner.py. Add memory entry feedback_target_must_cap_vs_entry.md.</t>
         </is>
       </c>
       <c r="H182" s="2" t="inlineStr"/>
@@ -10674,23 +10682,23 @@
       </c>
       <c r="L182" s="2" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M182" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>87336f2de</t>
         </is>
       </c>
       <c r="N182" s="8" t="inlineStr"/>
     </row>
-    <row r="183" ht="75" customHeight="1">
+    <row r="183" ht="60" customHeight="1">
       <c r="A183" s="2" t="n">
         <v>182</v>
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>TARGET-CAP-SWEEP</t>
+          <t>A7</t>
         </is>
       </c>
       <c r="C183" s="9" t="inlineStr">
@@ -10700,27 +10708,39 @@
       </c>
       <c r="D183" s="5" t="inlineStr">
         <is>
-          <t>Strategy/Target Sanity</t>
+          <t>UI / Drift</t>
         </is>
       </c>
       <c r="E183" s="6" t="inlineStr">
         <is>
-          <t>Sweep for naive swing-high-as-target pattern across all scanners</t>
+          <t>Drift dashboard tile + /api/drift-alerts endpoint</t>
         </is>
       </c>
       <c r="F183" s="5" t="inlineStr">
         <is>
-          <t>mean_reversion.py:354 (target2 = high.iloc[-20:].max() uncapped, latent) and pullback_scanner.py:113 (target = high_252 uncapped, UI API) had the same class of bug as weekly_pullback.py. Both fixed proactively. analysis.py:7766 calculate_trade_plan also has it but is dead code (no callers).</t>
+          <t>Daily drift cron (LaunchAgents/com.swingtrade.driftalert.plist) writes data/drift_alerts.jsonl but nothing renders it in the V2 dashboard.</t>
         </is>
       </c>
       <c r="G183" s="5" t="inlineStr">
         <is>
-          <t>Cap target2 at price*1.10 in mean_reversion.py, cap target at price*1.15 in pullback_scanner.py. Add memory entry feedback_target_must_cap_vs_entry.md.</t>
-        </is>
-      </c>
-      <c r="H183" s="2" t="inlineStr"/>
-      <c r="I183" s="5" t="inlineStr"/>
-      <c r="J183" s="5" t="inlineStr"/>
+          <t>GET /api/drift-alerts in server.py reads JSONL log. infra/prototype/tabs/status/status.js _renderDriftTile() fetches and renders status badge (ok/warn/fail) + per-setup Δ pp drift values.</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I183" s="5" t="inlineStr">
+        <is>
+          <t>Win: continuous drift visibility between alert events.</t>
+        </is>
+      </c>
+      <c r="J183" s="5" t="inlineStr">
+        <is>
+          <t>Additive — only renders if #driftBody container exists in DOM.</t>
+        </is>
+      </c>
       <c r="K183" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -10728,23 +10748,27 @@
       </c>
       <c r="L183" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M183" s="3" t="inlineStr">
         <is>
-          <t>87336f2de</t>
-        </is>
-      </c>
-      <c r="N183" s="8" t="inlineStr"/>
-    </row>
-    <row r="184" ht="60" customHeight="1">
+          <t>16a26b201</t>
+        </is>
+      </c>
+      <c r="N183" s="8" t="inlineStr">
+        <is>
+          <t>Open https://localhost:7432/dashboard → Status tab → drift tile renders. If no drift_alerts.jsonl yet, shows 'No drift alerts yet'. Else shows per-setup Δ pp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="45" customHeight="1">
       <c r="A184" s="2" t="n">
         <v>183</v>
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>A7</t>
+          <t>MOD-3</t>
         </is>
       </c>
       <c r="C184" s="9" t="inlineStr">
@@ -10754,37 +10778,37 @@
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>UI / Drift</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E184" s="6" t="inlineStr">
         <is>
-          <t>Drift dashboard tile + /api/drift-alerts endpoint</t>
+          <t>Auth Playwright tests need SWING_USER / SWING_PASS env vars</t>
         </is>
       </c>
       <c r="F184" s="5" t="inlineStr">
         <is>
-          <t>Daily drift cron (LaunchAgents/com.swingtrade.driftalert.plist) writes data/drift_alerts.jsonl but nothing renders it in the V2 dashboard.</t>
+          <t>0[1-3]-*.spec.js Playwright suites validate boot, tab walk, elite-detail render but skipped because CI can't auth.</t>
         </is>
       </c>
       <c r="G184" s="5" t="inlineStr">
         <is>
-          <t>GET /api/drift-alerts in server.py reads JSONL log. infra/prototype/tabs/status/status.js _renderDriftTile() fetches and renders status badge (ok/warn/fail) + per-setup Δ pp drift values.</t>
+          <t>Add SWING_USER + SWING_PASS to local .env (already exists) and CI secret store. Update test runner to pull from env. Document in tests/README.md.</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I184" s="5" t="inlineStr">
         <is>
-          <t>Win: continuous drift visibility between alert events.</t>
+          <t>Win: full auth-gated test coverage in CI.</t>
         </is>
       </c>
       <c r="J184" s="5" t="inlineStr">
         <is>
-          <t>Additive — only renders if #driftBody container exists in DOM.</t>
+          <t>Trivial.</t>
         </is>
       </c>
       <c r="K184" s="12" t="inlineStr">
@@ -10799,22 +10823,22 @@
       </c>
       <c r="M184" s="3" t="inlineStr">
         <is>
-          <t>16a26b201</t>
+          <t>2b7d2f40f</t>
         </is>
       </c>
       <c r="N184" s="8" t="inlineStr">
         <is>
-          <t>Open https://localhost:7432/dashboard → Status tab → drift tile renders. If no drift_alerts.jsonl yet, shows 'No drift alerts yet'. Else shows per-setup Δ pp.</t>
-        </is>
-      </c>
-    </row>
-    <row r="185" ht="45" customHeight="1">
+          <t>open tests/README.md → SWING_USER + SWING_PASS env var docs. SWING_USER=foo SWING_PASS=bar npx playwright test runs auth suite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="105" customHeight="1">
       <c r="A185" s="2" t="n">
         <v>184</v>
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>MOD-3</t>
+          <t>MOD-A</t>
         </is>
       </c>
       <c r="C185" s="9" t="inlineStr">
@@ -10829,32 +10853,24 @@
       </c>
       <c r="E185" s="6" t="inlineStr">
         <is>
-          <t>Auth Playwright tests need SWING_USER / SWING_PASS env vars</t>
+          <t>Split 5 main tabs into sub-function modules (Phase A)</t>
         </is>
       </c>
       <c r="F185" s="5" t="inlineStr">
         <is>
-          <t>0[1-3]-*.spec.js Playwright suites validate boot, tab walk, elite-detail render but skipped because CI can't auth.</t>
+          <t>5 main-tab folders were each single .js files with multiple visual sections crammed together (performance 366 ln, audit 505, elite 370, earnings 278, strategies 224 = 1,743 ln total). Hard to navigate, hard to test sub-renderers in isolation, and bare-DATA references in audit had been silently broken since the 2026-05-09 extraction.</t>
         </is>
       </c>
       <c r="G185" s="5" t="inlineStr">
         <is>
-          <t>Add SWING_USER + SWING_PASS to local .env (already exists) and CI secret store. Update test runner to pull from env. Document in tests/README.md.</t>
-        </is>
-      </c>
-      <c r="H185" s="2" t="inlineStr">
-        <is>
-          <t>5 min</t>
-        </is>
-      </c>
-      <c r="I185" s="5" t="inlineStr">
-        <is>
-          <t>Win: full auth-gated test coverage in CI.</t>
-        </is>
-      </c>
+          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 4-7 focused sub-modules per folder. 28 new sub-files total. Bug fixes folded in where bare-DATA / bare-$ references would ReferenceError. Each tab passes node --check; window bindings preserved exactly.</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="inlineStr"/>
+      <c r="I185" s="5" t="inlineStr"/>
       <c r="J185" s="5" t="inlineStr">
         <is>
-          <t>Trivial.</t>
+          <t>Phase A — main tabs split. Commits 9517bbbe9 (perf, 8 files), 0d035d6cd (audit, 7 files), 733342cd3 (elite, 6 files), cf5e0bb92 (earnings, 5 files), 7229d4ccb (strategies, 5 files). 28 new sub-files; net +311 lines from per-module imports/exports — that's the price of single-responsibility. Audit-tab bare-DATA ReferenceError fixed in expand_panel.js + exports.js.</t>
         </is>
       </c>
       <c r="K185" s="12" t="inlineStr">
@@ -10864,17 +10880,17 @@
       </c>
       <c r="L185" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M185" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
+          <t>9517bbbe9..7229d4ccb</t>
         </is>
       </c>
       <c r="N185" s="8" t="inlineStr">
         <is>
-          <t>open tests/README.md → SWING_USER + SWING_PASS env var docs. SWING_USER=foo SWING_PASS=bar npx playwright test runs auth suite.</t>
+          <t>1. ls infra/prototype/tabs/{performance,audit,elite,earnings,strategies}/*.js → expect 8/7/6/5/5 files per folder. 2. Open https://trade.mystockholding.com/v2/dashboard.html — click each of the 5 tabs, verify they render identically to before the split. 3. node --check infra/prototype/tabs/*/*.js → all pass. 4. Click an audit row to expand the detail panel (was silently broken before — bare-DATA bug now fixed). 5. Click Export CSV in audit (was also broken).</t>
         </is>
       </c>
     </row>
@@ -10884,7 +10900,7 @@
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>MOD-A</t>
+          <t>MOD-B</t>
         </is>
       </c>
       <c r="C186" s="9" t="inlineStr">
@@ -10899,24 +10915,24 @@
       </c>
       <c r="E186" s="6" t="inlineStr">
         <is>
-          <t>Split 5 main tabs into sub-function modules (Phase A)</t>
+          <t>Split 5 elite-detail subtabs into sub-function modules (Phase B)</t>
         </is>
       </c>
       <c r="F186" s="5" t="inlineStr">
         <is>
-          <t>5 main-tab folders were each single .js files with multiple visual sections crammed together (performance 366 ln, audit 505, elite 370, earnings 278, strategies 224 = 1,743 ln total). Hard to navigate, hard to test sub-renderers in isolation, and bare-DATA references in audit had been silently broken since the 2026-05-09 extraction.</t>
+          <t>5 subtab folders were single .js files (ruleengine 531 ln, smc 414, insider 256, options 245, sentiment 203 = 1,649 ln). Bare-$ references in smc/options/sentiment had silent ReferenceErrors since 2026-05-09 extraction. _renderShortPressureCard reference unguarded.</t>
         </is>
       </c>
       <c r="G186" s="5" t="inlineStr">
         <is>
-          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 4-7 focused sub-modules per folder. 28 new sub-files total. Bug fixes folded in where bare-DATA / bare-$ references would ReferenceError. Each tab passes node --check; window bindings preserved exactly.</t>
+          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 2-3 focused sub-modules per folder. 17 new sub-files total. Bare-$ → document.getElementById fixed. _renderShortPressureCard wrapped in typeof guard. All files pass node --check.</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr"/>
       <c r="I186" s="5" t="inlineStr"/>
       <c r="J186" s="5" t="inlineStr">
         <is>
-          <t>Phase A — main tabs split. Commits 9517bbbe9 (perf, 8 files), 0d035d6cd (audit, 7 files), 733342cd3 (elite, 6 files), cf5e0bb92 (earnings, 5 files), 7229d4ccb (strategies, 5 files). 28 new sub-files; net +311 lines from per-module imports/exports — that's the price of single-responsibility. Audit-tab bare-DATA ReferenceError fixed in expand_panel.js + exports.js.</t>
+          <t>Phase B — elite-detail subtabs split. Commits 18ef1002e (ruleengine, 4 files), 5c3497e6f (smc, 4 files), cb167a47b (insider, 3 files), 2a767ac98 (options, 3 files), 388c316c4 (sentiment, 3 files). 17 new sub-files. 5 latent ReferenceErrors fixed (audit fixed in MOD-A, smc/options/sentiment bare-$, sentiment _renderShortPressureCard guard). Sibling 40f8452b8 layered 8-gate cascade view onto ruleengine pipeline.js post-split.</t>
         </is>
       </c>
       <c r="K186" s="12" t="inlineStr">
@@ -10931,22 +10947,22 @@
       </c>
       <c r="M186" s="3" t="inlineStr">
         <is>
-          <t>9517bbbe9..7229d4ccb</t>
+          <t>18ef1002e..388c316c4</t>
         </is>
       </c>
       <c r="N186" s="8" t="inlineStr">
         <is>
-          <t>1. ls infra/prototype/tabs/{performance,audit,elite,earnings,strategies}/*.js → expect 8/7/6/5/5 files per folder. 2. Open https://trade.mystockholding.com/v2/dashboard.html — click each of the 5 tabs, verify they render identically to before the split. 3. node --check infra/prototype/tabs/*/*.js → all pass. 4. Click an audit row to expand the detail panel (was silently broken before — bare-DATA bug now fixed). 5. Click Export CSV in audit (was also broken).</t>
-        </is>
-      </c>
-    </row>
-    <row r="187" ht="105" customHeight="1">
+          <t>1. ls infra/prototype/subtabs/{ruleengine,smc,insider,options,sentiment}/*.js → expect 4/4/3/3/3 files per folder. 2. Open elite-detail.html?t=NVDA → click through Why-this-is-X, SMC, Insider, Options, Sentiment subtabs — each renders identically. 3. node --check infra/prototype/subtabs/*/*.js → all pass. 4. SMC subtab now actually renders (was silently broken — bare-$ ReferenceError). 5. Options + Sentiment same fix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="45" customHeight="1">
       <c r="A187" s="2" t="n">
         <v>186</v>
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>MOD-B</t>
+          <t>UI-2</t>
         </is>
       </c>
       <c r="C187" s="9" t="inlineStr">
@@ -10956,29 +10972,37 @@
       </c>
       <c r="D187" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>UI / Overview</t>
         </is>
       </c>
       <c r="E187" s="6" t="inlineStr">
         <is>
-          <t>Split 5 elite-detail subtabs into sub-function modules (Phase B)</t>
+          <t>Overview tab: align reads with sibling-tab canonical sources</t>
         </is>
       </c>
       <c r="F187" s="5" t="inlineStr">
         <is>
-          <t>5 subtab folders were single .js files (ruleengine 531 ln, smc 414, insider 256, options 245, sentiment 203 = 1,649 ln). Bare-$ references in smc/options/sentiment had silent ReferenceErrors since 2026-05-09 extraction. _renderShortPressureCard reference unguarded.</t>
+          <t>Overview read flat T.* fields that drift from sibling-tab displays. Different precedence rules across tabs.</t>
         </is>
       </c>
       <c r="G187" s="5" t="inlineStr">
         <is>
-          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 2-3 focused sub-modules per folder. 17 new sub-files total. Bare-$ → document.getElementById fixed. _renderShortPressureCard wrapped in typeof guard. All files pass node --check.</t>
-        </is>
-      </c>
-      <c r="H187" s="2" t="inlineStr"/>
-      <c r="I187" s="5" t="inlineStr"/>
+          <t>Refactored overview.js: T.fund_real, T.insider_full, T.news_sentiment_score, T.options_iv, T.technicals.indicators precedence first.</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>45 min</t>
+        </is>
+      </c>
+      <c r="I187" s="5" t="inlineStr">
+        <is>
+          <t>Low risk / Medium win (consistency)</t>
+        </is>
+      </c>
       <c r="J187" s="5" t="inlineStr">
         <is>
-          <t>Phase B — elite-detail subtabs split. Commits 18ef1002e (ruleengine, 4 files), 5c3497e6f (smc, 4 files), cb167a47b (insider, 3 files), 2a767ac98 (options, 3 files), 388c316c4 (sentiment, 3 files). 17 new sub-files. 5 latent ReferenceErrors fixed (audit fixed in MOD-A, smc/options/sentiment bare-$, sentiment _renderShortPressureCard guard). Sibling 40f8452b8 layered 8-gate cascade view onto ruleengine pipeline.js post-split.</t>
+          <t>All reads use ?? fallbacks.</t>
         </is>
       </c>
       <c r="K187" s="12" t="inlineStr">
@@ -10993,12 +11017,12 @@
       </c>
       <c r="M187" s="3" t="inlineStr">
         <is>
-          <t>18ef1002e..388c316c4</t>
+          <t>5ffdd8e07</t>
         </is>
       </c>
       <c r="N187" s="8" t="inlineStr">
         <is>
-          <t>1. ls infra/prototype/subtabs/{ruleengine,smc,insider,options,sentiment}/*.js → expect 4/4/3/3/3 files per folder. 2. Open elite-detail.html?t=NVDA → click through Why-this-is-X, SMC, Insider, Options, Sentiment subtabs — each renders identically. 3. node --check infra/prototype/subtabs/*/*.js → all pass. 4. SMC subtab now actually renders (was silently broken — bare-$ ReferenceError). 5. Options + Sentiment same fix.</t>
+          <t>Compare Overview vs Fundamentals/Sentiment/Insider/Options sub-tabs - numbers should match.</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11032,7 @@
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>UI-2</t>
+          <t>RULE-1</t>
         </is>
       </c>
       <c r="C188" s="9" t="inlineStr">
@@ -11018,39 +11042,35 @@
       </c>
       <c r="D188" s="5" t="inlineStr">
         <is>
-          <t>UI / Overview</t>
+          <t>UI / Rule Engine</t>
         </is>
       </c>
       <c r="E188" s="6" t="inlineStr">
         <is>
-          <t>Overview tab: align reads with sibling-tab canonical sources</t>
+          <t>Rule Engine: 8-gate cascade + multiplier stack + regime4_thresholds</t>
         </is>
       </c>
       <c r="F188" s="5" t="inlineStr">
         <is>
-          <t>Overview read flat T.* fields that drift from sibling-tab displays. Different precedence rules across tabs.</t>
+          <t>Rule Engine read legacy T.gate.passed not T.gates_evaluated. Did not show setup_size_multiplier or kelly_size.* multipliers.</t>
         </is>
       </c>
       <c r="G188" s="5" t="inlineStr">
         <is>
-          <t>Refactored overview.js: T.fund_real, T.insider_full, T.news_sentiment_score, T.options_iv, T.technicals.indicators precedence first.</t>
+          <t>Added Stage 2.5 (8-Gate Cascade). Stage 8 surfaces full multiplier stack. Counterfactuals read regime4-aware threshold first.</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="I188" s="5" t="inlineStr">
         <is>
-          <t>Low risk / Medium win (consistency)</t>
-        </is>
-      </c>
-      <c r="J188" s="5" t="inlineStr">
-        <is>
-          <t>All reads use ?? fallbacks.</t>
-        </is>
-      </c>
+          <t>Low risk / Medium win (transparency)</t>
+        </is>
+      </c>
+      <c r="J188" s="5" t="inlineStr"/>
       <c r="K188" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -11063,22 +11083,22 @@
       </c>
       <c r="M188" s="3" t="inlineStr">
         <is>
-          <t>5ffdd8e07</t>
+          <t>40f8452b8</t>
         </is>
       </c>
       <c r="N188" s="8" t="inlineStr">
         <is>
-          <t>Compare Overview vs Fundamentals/Sentiment/Insider/Options sub-tabs - numbers should match.</t>
-        </is>
-      </c>
-    </row>
-    <row r="189" ht="45" customHeight="1">
+          <t>Open elite-detail Rule Engine sub-tab. Stage 2.5 shows 8 gates pass/fail. TC ticker in bull shows "Setup edge multiplier - KILLED 0.00x".</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="105" customHeight="1">
       <c r="A189" s="2" t="n">
         <v>188</v>
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>RULE-1</t>
+          <t>TARGET-SOURCES-P1</t>
         </is>
       </c>
       <c r="C189" s="9" t="inlineStr">
@@ -11088,35 +11108,39 @@
       </c>
       <c r="D189" s="5" t="inlineStr">
         <is>
-          <t>UI / Rule Engine</t>
+          <t>UI / Trade Plan</t>
         </is>
       </c>
       <c r="E189" s="6" t="inlineStr">
         <is>
-          <t>Rule Engine: 8-gate cascade + multiplier stack + regime4_thresholds</t>
+          <t>Phase 1 structural target sources (display-only)</t>
         </is>
       </c>
       <c r="F189" s="5" t="inlineStr">
         <is>
-          <t>Rule Engine read legacy T.gate.passed not T.gates_evaluated. Did not show setup_size_multiplier or kelly_size.* multipliers.</t>
+          <t>Target prices come from generic ATR multiples. User wants targets from objective TA sources: order blocks, fractals, fib levels, EW waves — per horizon (short/medium/long).</t>
         </is>
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>Added Stage 2.5 (8-Gate Cascade). Stage 8 surfaces full multiplier stack. Counterfactuals read regime4-aware threshold first.</t>
+          <t>New plan.target_sources field populated in compute_trade_plan with 5 sources: (1) fractal_high (Williams 5-bar, short horizon), (2) fib_127_extension (medium), (3) fib_162_extension (medium), (4) ew_intermediate_t1 (v1 Wave-3 1.618×W1, medium), (5) ew_intermediate_t2 (v1 2.618×W1, long). DISPLAY ONLY — actual T1/T2 unchanged. Need ≥30 trade evidence per source × regime before changing BUY logic (Phase 2).</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>1.5 hrs</t>
         </is>
       </c>
       <c r="I189" s="5" t="inlineStr">
         <is>
-          <t>Low risk / Medium win (transparency)</t>
-        </is>
-      </c>
-      <c r="J189" s="5" t="inlineStr"/>
+          <t>Low (no behavior change)</t>
+        </is>
+      </c>
+      <c r="J189" s="5" t="inlineStr">
+        <is>
+          <t>Phase 2 (config-driven flip to structural targets) deferred until Phase 1 evidence collected. Order blocks (SMC) not yet sourced — separate sub-task to wire into target_sources.</t>
+        </is>
+      </c>
       <c r="K189" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -11129,22 +11153,22 @@
       </c>
       <c r="M189" s="3" t="inlineStr">
         <is>
-          <t>40f8452b8</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N189" s="8" t="inlineStr">
         <is>
-          <t>Open elite-detail Rule Engine sub-tab. Stage 2.5 shows 8 gates pass/fail. TC ticker in bull shows "Setup edge multiplier - KILLED 0.00x".</t>
-        </is>
-      </c>
-    </row>
-    <row r="190" ht="105" customHeight="1">
+          <t>Test ticker → plan.target_sources dict should have 3-5 entries, each with {horizon, level, rationale}. Phase 2 will surface in elite-detail Plan tab and Overview Trade Plan strip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="45" customHeight="1">
       <c r="A190" s="2" t="n">
         <v>189</v>
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>TARGET-SOURCES-P1</t>
+          <t>UNIVERSE-NASDAQ-1000</t>
         </is>
       </c>
       <c r="C190" s="9" t="inlineStr">
@@ -11154,39 +11178,27 @@
       </c>
       <c r="D190" s="5" t="inlineStr">
         <is>
-          <t>UI / Trade Plan</t>
+          <t>Universe</t>
         </is>
       </c>
       <c r="E190" s="6" t="inlineStr">
         <is>
-          <t>Phase 1 structural target sources (display-only)</t>
+          <t>NASDAQ 1000 liquidity gate</t>
         </is>
       </c>
       <c r="F190" s="5" t="inlineStr">
         <is>
-          <t>Target prices come from generic ATR multiples. User wants targets from objective TA sources: order blocks, fractals, fib levels, EW waves — per horizon (short/medium/long).</t>
+          <t>get_nasdaq_all replaced full 4805-name exchange list with top-1000 by dollar volume (one bulk_eod call); config nasdaq_all_top_n/min_dollar_vol</t>
         </is>
       </c>
       <c r="G190" s="5" t="inlineStr">
         <is>
-          <t>New plan.target_sources field populated in compute_trade_plan with 5 sources: (1) fractal_high (Williams 5-bar, short horizon), (2) fib_127_extension (medium), (3) fib_162_extension (medium), (4) ew_intermediate_t1 (v1 Wave-3 1.618×W1, medium), (5) ew_intermediate_t2 (v1 2.618×W1, long). DISPLAY ONLY — actual T1/T2 unchanged. Need ≥30 trade evidence per source × regime before changing BUY logic (Phase 2).</t>
-        </is>
-      </c>
-      <c r="H190" s="2" t="inlineStr">
-        <is>
-          <t>1.5 hrs</t>
-        </is>
-      </c>
-      <c r="I190" s="5" t="inlineStr">
-        <is>
-          <t>Low (no behavior change)</t>
-        </is>
-      </c>
-      <c r="J190" s="5" t="inlineStr">
-        <is>
-          <t>Phase 2 (config-driven flip to structural targets) deferred until Phase 1 evidence collected. Order blocks (SMC) not yet sourced — separate sub-task to wire into target_sources.</t>
-        </is>
-      </c>
+          <t>data_fetcher.get_nasdaq_all + config.json + swing_trade.py</t>
+        </is>
+      </c>
+      <c r="H190" s="2" t="inlineStr"/>
+      <c r="I190" s="5" t="inlineStr"/>
+      <c r="J190" s="5" t="inlineStr"/>
       <c r="K190" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -11194,19 +11206,15 @@
       </c>
       <c r="L190" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="M190" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N190" s="8" t="inlineStr">
-        <is>
-          <t>Test ticker → plan.target_sources dict should have 3-5 entries, each with {horizon, level, rationale}. Phase 2 will surface in elite-detail Plan tab and Overview Trade Plan strip.</t>
-        </is>
-      </c>
+          <t>ab1deacef</t>
+        </is>
+      </c>
+      <c r="N190" s="8" t="inlineStr"/>
     </row>
     <row r="191" ht="45" customHeight="1">
       <c r="A191" s="2" t="n">
@@ -11214,7 +11222,7 @@
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>UNIVERSE-NASDAQ-1000</t>
+          <t>STOCKSMITH-KAIROS-DOSSIER</t>
         </is>
       </c>
       <c r="C191" s="9" t="inlineStr">
@@ -11224,22 +11232,22 @@
       </c>
       <c r="D191" s="5" t="inlineStr">
         <is>
-          <t>Universe</t>
+          <t>V2 Dashboard / Kairos</t>
         </is>
       </c>
       <c r="E191" s="6" t="inlineStr">
         <is>
-          <t>NASDAQ 1000 liquidity gate</t>
+          <t>Ask Kairos cross-lens ticker dossier (§4)</t>
         </is>
       </c>
       <c r="F191" s="5" t="inlineStr">
         <is>
-          <t>get_nasdaq_all replaced full 4805-name exchange list with top-1000 by dollar volume (one bulk_eod call); config nasdaq_all_top_n/min_dollar_vol</t>
+          <t>composite verdict + 9 lens stances + ML projection injected as LLM context; fallbackAnswer offline</t>
         </is>
       </c>
       <c r="G191" s="5" t="inlineStr">
         <is>
-          <t>data_fetcher.get_nasdaq_all + config.json + swing_trade.py</t>
+          <t>Stocksmith.html kaiTickerDossier</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr"/>
@@ -11257,7 +11265,7 @@
       </c>
       <c r="M191" s="3" t="inlineStr">
         <is>
-          <t>ab1deacef</t>
+          <t>e3baa715f</t>
         </is>
       </c>
       <c r="N191" s="8" t="inlineStr"/>
@@ -11268,7 +11276,7 @@
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>STOCKSMITH-KAIROS-DOSSIER</t>
+          <t>REGIME-ACCURACY-TEST</t>
         </is>
       </c>
       <c r="C192" s="9" t="inlineStr">
@@ -11278,22 +11286,22 @@
       </c>
       <c r="D192" s="5" t="inlineStr">
         <is>
-          <t>V2 Dashboard / Kairos</t>
+          <t>Validation / Regime</t>
         </is>
       </c>
       <c r="E192" s="6" t="inlineStr">
         <is>
-          <t>Ask Kairos cross-lens ticker dossier (§4)</t>
+          <t>Regime-classification accuracy test (principle 18)</t>
         </is>
       </c>
       <c r="F192" s="5" t="inlineStr">
         <is>
-          <t>composite verdict + 9 lens stances + ML projection injected as LLM context; fallbackAnswer offline</t>
+          <t>when model said trending was next 5d actually trending? label regime outcomes, validate classifier</t>
         </is>
       </c>
       <c r="G192" s="5" t="inlineStr">
         <is>
-          <t>Stocksmith.html kaiTickerDossier</t>
+          <t>scripts/regime_accuracy.py</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr"/>
@@ -11306,48 +11314,48 @@
       </c>
       <c r="L192" s="2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="M192" s="3" t="inlineStr">
         <is>
-          <t>e3baa715f</t>
+          <t>d1ea97913</t>
         </is>
       </c>
       <c r="N192" s="8" t="inlineStr"/>
     </row>
-    <row r="193" ht="45" customHeight="1">
+    <row r="193" ht="90" customHeight="1">
       <c r="A193" s="2" t="n">
         <v>192</v>
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>REGIME-ACCURACY-TEST</t>
-        </is>
-      </c>
-      <c r="C193" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>WEEKEND-PHANTOMS</t>
+        </is>
+      </c>
+      <c r="C193" s="10" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D193" s="5" t="inlineStr">
         <is>
-          <t>Validation / Regime</t>
+          <t>Audit Trail / Data Quality</t>
         </is>
       </c>
       <c r="E193" s="6" t="inlineStr">
         <is>
-          <t>Regime-classification accuracy test (principle 18)</t>
+          <t>Weekend pick_dates (Sat/Sun) in audit ledger</t>
         </is>
       </c>
       <c r="F193" s="5" t="inlineStr">
         <is>
-          <t>when model said trending was next 5d actually trending? label regime outcomes, validate classifier</t>
+          <t>signal_log writes pick_date as today.isoformat() — when scan runs on weekend (manual rerun), produces Sat/Sun dates EODHD can't price. 355 such phantoms in ledger. Fix: snap weekend dates forward to next Monday at both write-time (signal_tracker.log_signals) and build-time (build_audit_ledger.py). Preserves original via pick_date_orig field</t>
         </is>
       </c>
       <c r="G193" s="5" t="inlineStr">
         <is>
-          <t>scripts/regime_accuracy.py</t>
+          <t>signal_tracker.py log_signals dow snap + build_audit_ledger.py _compute_returns_for_ticker snap-forward · 353 records normalized · 2 residual edge cases</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr"/>
@@ -11360,23 +11368,23 @@
       </c>
       <c r="L193" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M193" s="3" t="inlineStr">
         <is>
-          <t>d1ea97913</t>
+          <t>e48edac16</t>
         </is>
       </c>
       <c r="N193" s="8" t="inlineStr"/>
     </row>
-    <row r="194" ht="90" customHeight="1">
+    <row r="194" ht="75" customHeight="1">
       <c r="A194" s="2" t="n">
         <v>193</v>
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>WEEKEND-PHANTOMS</t>
+          <t>BT-GUARD-1</t>
         </is>
       </c>
       <c r="C194" s="10" t="inlineStr">
@@ -11386,22 +11394,22 @@
       </c>
       <c r="D194" s="5" t="inlineStr">
         <is>
-          <t>Audit Trail / Data Quality</t>
+          <t>Backtest Infrastructure</t>
         </is>
       </c>
       <c r="E194" s="6" t="inlineStr">
         <is>
-          <t>Weekend pick_dates (Sat/Sun) in audit ledger</t>
+          <t>Backtest min_score guard rail</t>
         </is>
       </c>
       <c r="F194" s="5" t="inlineStr">
         <is>
-          <t>signal_log writes pick_date as today.isoformat() — when scan runs on weekend (manual rerun), produces Sat/Sun dates EODHD can't price. 355 such phantoms in ledger. Fix: snap weekend dates forward to next Monday at both write-time (signal_tracker.log_signals) and build-time (build_audit_ledger.py). Preserves original via pick_date_orig field</t>
+          <t>Users (and Claude sessions) repeatedly ran 252d backtests with --min-score 65 (live threshold) producing 0 BUYs across all 252 days. Historical scoring is structurally suppressed because sentiment/options/catalyst pillars depend on real-time data not in EODHD backfill.</t>
         </is>
       </c>
       <c r="G194" s="5" t="inlineStr">
         <is>
-          <t>signal_tracker.py log_signals dow snap + build_audit_ledger.py _compute_returns_for_ticker snap-forward · 353 records normalized · 2 residual edge cases</t>
+          <t>backtest.py main() now warns loudly when --min-score &gt; 55 (backtest-safe floor). New --accept-low-buys flag silences the warning for legitimate grid-search explorations. --smoke bypasses the guard. Plus diagnostic doc: docs/backtest_historical_scoring_diagnostic.md.</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr"/>
@@ -11419,18 +11427,18 @@
       </c>
       <c r="M194" s="3" t="inlineStr">
         <is>
-          <t>e48edac16</t>
+          <t>d754830</t>
         </is>
       </c>
       <c r="N194" s="8" t="inlineStr"/>
     </row>
-    <row r="195" ht="75" customHeight="1">
+    <row r="195" ht="60" customHeight="1">
       <c r="A195" s="2" t="n">
         <v>194</v>
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>BT-GUARD-1</t>
+          <t>LENS-PLAN-PERMODE-TARGETS</t>
         </is>
       </c>
       <c r="C195" s="10" t="inlineStr">
@@ -11440,22 +11448,22 @@
       </c>
       <c r="D195" s="5" t="inlineStr">
         <is>
-          <t>Backtest Infrastructure</t>
+          <t>BullVeda · Plan</t>
         </is>
       </c>
       <c r="E195" s="6" t="inlineStr">
         <is>
-          <t>Backtest min_score guard rail</t>
+          <t>lens-plan synthesizes per-mode targets by scaling swing levels</t>
         </is>
       </c>
       <c r="F195" s="5" t="inlineStr">
         <is>
-          <t>Users (and Claude sessions) repeatedly ran 252d backtests with --min-score 65 (live threshold) producing 0 BUYs across all 252 days. Historical scoring is structurally suppressed because sentiment/options/catalyst pillars depend on real-time data not in EODHD backfill.</t>
+          <t>modeAdjust() in lens-plan.jsx scales swing stop/t1/t2 by fixed multipliers (POSITION 0.96/1.10/1.18, INVEST 0.84/1.32/1.58) instead of binding canonical per-mode targets.</t>
         </is>
       </c>
       <c r="G195" s="5" t="inlineStr">
         <is>
-          <t>backtest.py main() now warns loudly when --min-score &gt; 55 (backtest-safe floor). New --accept-low-buys flag silences the warning for legitimate grid-search explorations. --smoke bypasses the guard. Plus diagnostic doc: docs/backtest_historical_scoring_diagnostic.md.</t>
+          <t>Bind per-mode stop/T1/T2/RR from /api/trade_engine?mode= (already fetched by Overview into STATE.payloads). Verdict already fixed to bind decisionsByMode 2026-06-09.</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr"/>
@@ -11468,23 +11476,23 @@
       </c>
       <c r="L195" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="M195" s="3" t="inlineStr">
         <is>
-          <t>d754830</t>
+          <t>99cff7117</t>
         </is>
       </c>
       <c r="N195" s="8" t="inlineStr"/>
     </row>
-    <row r="196" ht="60" customHeight="1">
+    <row r="196" ht="45" customHeight="1">
       <c r="A196" s="2" t="n">
         <v>195</v>
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>LENS-PLAN-PERMODE-TARGETS</t>
+          <t>SURFACE-WATCHLIST-MOCK</t>
         </is>
       </c>
       <c r="C196" s="10" t="inlineStr">
@@ -11494,22 +11502,22 @@
       </c>
       <c r="D196" s="5" t="inlineStr">
         <is>
-          <t>BullVeda · Plan</t>
+          <t>BullVeda · Watchlist</t>
         </is>
       </c>
       <c r="E196" s="6" t="inlineStr">
         <is>
-          <t>lens-plan synthesizes per-mode targets by scaling swing levels</t>
+          <t>surface-watchlist enrichWL fabricates row data from charCodeAt</t>
         </is>
       </c>
       <c r="F196" s="5" t="inlineStr">
         <is>
-          <t>modeAdjust() in lens-plan.jsx scales swing stop/t1/t2 by fixed multipliers (POSITION 0.96/1.10/1.18, INVEST 0.84/1.32/1.58) instead of binding canonical per-mode targets.</t>
+          <t>enrichWL() synthesizes rs/rvol/rr/earn/iv/wlb/n/pf/insider/sent (and conviction tier) from sym char codes — mock, not real data.</t>
         </is>
       </c>
       <c r="G196" s="5" t="inlineStr">
         <is>
-          <t>Bind per-mode stop/T1/T2/RR from /api/trade_engine?mode= (already fetched by Overview into STATE.payloads). Verdict already fixed to bind decisionsByMode 2026-06-09.</t>
+          <t>Wire enrichWL to the real universe row via BV.scanRow; bind conviction_tier instead of deriving from score.</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr"/>
@@ -11538,7 +11546,7 @@
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>SURFACE-WATCHLIST-MOCK</t>
+          <t>DEFROT-1</t>
         </is>
       </c>
       <c r="C197" s="10" t="inlineStr">
@@ -11548,22 +11556,22 @@
       </c>
       <c r="D197" s="5" t="inlineStr">
         <is>
-          <t>BullVeda · Watchlist</t>
+          <t>Choice C Strategy</t>
         </is>
       </c>
       <c r="E197" s="6" t="inlineStr">
         <is>
-          <t>surface-watchlist enrichWL fabricates row data from charCodeAt</t>
+          <t>Design doc — docs/strategy_defensive_rotation.md</t>
         </is>
       </c>
       <c r="F197" s="5" t="inlineStr">
         <is>
-          <t>enrichWL() synthesizes rs/rvol/rr/earn/iv/wlb/n/pf/insider/sent (and conviction tier) from sym char codes — mock, not real data.</t>
+          <t>Phase 1 of Defensive Rotation sleeve build</t>
         </is>
       </c>
       <c r="G197" s="5" t="inlineStr">
         <is>
-          <t>Wire enrichWL to the real universe row via BV.scanRow; bind conviction_tier instead of deriving from score.</t>
+          <t>Full design: mechanism, triggers, universe, validation plan</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr"/>
@@ -11576,12 +11584,12 @@
       </c>
       <c r="L197" s="2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="M197" s="3" t="inlineStr">
         <is>
-          <t>99cff7117</t>
+          <t>399922797</t>
         </is>
       </c>
       <c r="N197" s="8" t="inlineStr"/>
@@ -11592,7 +11600,7 @@
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-1</t>
+          <t>DEFROT-2</t>
         </is>
       </c>
       <c r="C198" s="10" t="inlineStr">
@@ -11607,7 +11615,7 @@
       </c>
       <c r="E198" s="6" t="inlineStr">
         <is>
-          <t>Design doc — docs/strategy_defensive_rotation.md</t>
+          <t>Config block — defensive_rotation_sleeve</t>
         </is>
       </c>
       <c r="F198" s="5" t="inlineStr">
@@ -11617,7 +11625,7 @@
       </c>
       <c r="G198" s="5" t="inlineStr">
         <is>
-          <t>Full design: mechanism, triggers, universe, validation plan</t>
+          <t>Curated universe, regime gates, sizing, stops; default _enabled=false</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr"/>
@@ -11646,7 +11654,7 @@
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-2</t>
+          <t>DEFROT-3</t>
         </is>
       </c>
       <c r="C199" s="10" t="inlineStr">
@@ -11661,7 +11669,7 @@
       </c>
       <c r="E199" s="6" t="inlineStr">
         <is>
-          <t>Config block — defensive_rotation_sleeve</t>
+          <t>Detector function — _detect_defensive_rotation</t>
         </is>
       </c>
       <c r="F199" s="5" t="inlineStr">
@@ -11671,7 +11679,7 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>Curated universe, regime gates, sizing, stops; default _enabled=false</t>
+          <t>Universe + regime + SPY-50EMA + RS + beta + ATR gates with per-criterion audit</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr"/>
@@ -11700,7 +11708,7 @@
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-3</t>
+          <t>DEFROT-4</t>
         </is>
       </c>
       <c r="C200" s="10" t="inlineStr">
@@ -11715,7 +11723,7 @@
       </c>
       <c r="E200" s="6" t="inlineStr">
         <is>
-          <t>Detector function — _detect_defensive_rotation</t>
+          <t>Wire into analyze_ticker</t>
         </is>
       </c>
       <c r="F200" s="5" t="inlineStr">
@@ -11725,7 +11733,7 @@
       </c>
       <c r="G200" s="5" t="inlineStr">
         <is>
-          <t>Universe + regime + SPY-50EMA + RS + beta + ATR gates with per-criterion audit</t>
+          <t>Setup family override + trade plan override (1.0 ATR stop, T1+3, T2+6, hold 10-30d, regime exit on SPY 50EMA reclaim)</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr"/>
@@ -11754,7 +11762,7 @@
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-4</t>
+          <t>DEFROT-5</t>
         </is>
       </c>
       <c r="C201" s="10" t="inlineStr">
@@ -11769,7 +11777,7 @@
       </c>
       <c r="E201" s="6" t="inlineStr">
         <is>
-          <t>Wire into analyze_ticker</t>
+          <t>Decision engine bypasses</t>
         </is>
       </c>
       <c r="F201" s="5" t="inlineStr">
@@ -11779,7 +11787,7 @@
       </c>
       <c r="G201" s="5" t="inlineStr">
         <is>
-          <t>Setup family override + trade plan override (1.0 ATR stop, T1+3, T2+6, hold 10-30d, regime exit on SPY 50EMA reclaim)</t>
+          <t>regime_gate + entry_quality + fund_adequacy bypassed for Defensive Rotation family</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr"/>
@@ -11808,7 +11816,7 @@
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-5</t>
+          <t>DEFROT-6</t>
         </is>
       </c>
       <c r="C202" s="10" t="inlineStr">
@@ -11823,7 +11831,7 @@
       </c>
       <c r="E202" s="6" t="inlineStr">
         <is>
-          <t>Decision engine bypasses</t>
+          <t>Universe coverage</t>
         </is>
       </c>
       <c r="F202" s="5" t="inlineStr">
@@ -11833,7 +11841,7 @@
       </c>
       <c r="G202" s="5" t="inlineStr">
         <is>
-          <t>regime_gate + entry_quality + fund_adequacy bypassed for Defensive Rotation family</t>
+          <t>XLP, TLT, IEF added to custom_watchlist (XLU/XLV/GLD already present)</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr"/>
@@ -11862,7 +11870,7 @@
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-6</t>
+          <t>DEFROT-7</t>
         </is>
       </c>
       <c r="C203" s="10" t="inlineStr">
@@ -11877,7 +11885,7 @@
       </c>
       <c r="E203" s="6" t="inlineStr">
         <is>
-          <t>Universe coverage</t>
+          <t>Smoke test + commit</t>
         </is>
       </c>
       <c r="F203" s="5" t="inlineStr">
@@ -11887,7 +11895,7 @@
       </c>
       <c r="G203" s="5" t="inlineStr">
         <is>
-          <t>XLP, TLT, IEF added to custom_watchlist (XLU/XLV/GLD already present)</t>
+          <t>All 4 detector tests pass; ready for Phase 1 paper validation</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr"/>
@@ -11916,7 +11924,7 @@
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>DEFROT-7</t>
+          <t>MEANREV-1</t>
         </is>
       </c>
       <c r="C204" s="10" t="inlineStr">
@@ -11931,17 +11939,17 @@
       </c>
       <c r="E204" s="6" t="inlineStr">
         <is>
-          <t>Smoke test + commit</t>
+          <t>Mean Reversion design doc</t>
         </is>
       </c>
       <c r="F204" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 of Defensive Rotation sleeve build</t>
+          <t>Sleeve build</t>
         </is>
       </c>
       <c r="G204" s="5" t="inlineStr">
         <is>
-          <t>All 4 detector tests pass; ready for Phase 1 paper validation</t>
+          <t>docs/strategy_mean_reversion.md — full Jegadeesh 1990 mechanism + validation plan</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr"/>
@@ -11959,7 +11967,7 @@
       </c>
       <c r="M204" s="3" t="inlineStr">
         <is>
-          <t>399922797</t>
+          <t>d0c6c4e04</t>
         </is>
       </c>
       <c r="N204" s="8" t="inlineStr"/>
@@ -11970,7 +11978,7 @@
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-1</t>
+          <t>MEANREV-2</t>
         </is>
       </c>
       <c r="C205" s="10" t="inlineStr">
@@ -11985,7 +11993,7 @@
       </c>
       <c r="E205" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion design doc</t>
+          <t>Mean Reversion config</t>
         </is>
       </c>
       <c r="F205" s="5" t="inlineStr">
@@ -11995,7 +12003,7 @@
       </c>
       <c r="G205" s="5" t="inlineStr">
         <is>
-          <t>docs/strategy_mean_reversion.md — full Jegadeesh 1990 mechanism + validation plan</t>
+          <t>RSI&lt;30, EMA200 floor, 3-5d hold; default _enabled=true (fires in current choppy regime)</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr"/>
@@ -12024,7 +12032,7 @@
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-2</t>
+          <t>MEANREV-3</t>
         </is>
       </c>
       <c r="C206" s="10" t="inlineStr">
@@ -12039,7 +12047,7 @@
       </c>
       <c r="E206" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion config</t>
+          <t>Mean Reversion detector</t>
         </is>
       </c>
       <c r="F206" s="5" t="inlineStr">
@@ -12049,7 +12057,7 @@
       </c>
       <c r="G206" s="5" t="inlineStr">
         <is>
-          <t>RSI&lt;30, EMA200 floor, 3-5d hold; default _enabled=true (fires in current choppy regime)</t>
+          <t>_detect_mean_reversion — 8-gate audit (regime/score/RSI/EMA200/recent_low/RVOL/ADV/earnings)</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr"/>
@@ -12078,7 +12086,7 @@
       </c>
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-3</t>
+          <t>MEANREV-4</t>
         </is>
       </c>
       <c r="C207" s="10" t="inlineStr">
@@ -12093,7 +12101,7 @@
       </c>
       <c r="E207" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion detector</t>
+          <t>Mean Reversion wiring</t>
         </is>
       </c>
       <c r="F207" s="5" t="inlineStr">
@@ -12103,7 +12111,7 @@
       </c>
       <c r="G207" s="5" t="inlineStr">
         <is>
-          <t>_detect_mean_reversion — 8-gate audit (regime/score/RSI/EMA200/recent_low/RVOL/ADV/earnings)</t>
+          <t>Setup family override + plan (1.0 ATR stop, +3/+5% T1/T2, 3-5d hold, hard time-stop)</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr"/>
@@ -12132,7 +12140,7 @@
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-4</t>
+          <t>MEANREV-5</t>
         </is>
       </c>
       <c r="C208" s="10" t="inlineStr">
@@ -12147,7 +12155,7 @@
       </c>
       <c r="E208" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion wiring</t>
+          <t>Mean Reversion bypass</t>
         </is>
       </c>
       <c r="F208" s="5" t="inlineStr">
@@ -12157,7 +12165,7 @@
       </c>
       <c r="G208" s="5" t="inlineStr">
         <is>
-          <t>Setup family override + plan (1.0 ATR stop, +3/+5% T1/T2, 3-5d hold, hard time-stop)</t>
+          <t>entry_quality bypass (EXTENDED-down IS the trigger)</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr"/>
@@ -12186,7 +12194,7 @@
       </c>
       <c r="B209" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-5</t>
+          <t>MEANREV-6</t>
         </is>
       </c>
       <c r="C209" s="10" t="inlineStr">
@@ -12201,7 +12209,7 @@
       </c>
       <c r="E209" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion bypass</t>
+          <t>Mean Reversion smoke test</t>
         </is>
       </c>
       <c r="F209" s="5" t="inlineStr">
@@ -12211,7 +12219,7 @@
       </c>
       <c r="G209" s="5" t="inlineStr">
         <is>
-          <t>entry_quality bypass (EXTENDED-down IS the trigger)</t>
+          <t>4 detector tests pass — fired=True on choppy+RSI=25+EMA200, rejected on RSI=55/below-EMA200/trending</t>
         </is>
       </c>
       <c r="H209" s="2" t="inlineStr"/>
@@ -12240,7 +12248,7 @@
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>MEANREV-6</t>
+          <t>PEAD-1</t>
         </is>
       </c>
       <c r="C210" s="10" t="inlineStr">
@@ -12255,7 +12263,7 @@
       </c>
       <c r="E210" s="6" t="inlineStr">
         <is>
-          <t>Mean Reversion smoke test</t>
+          <t>PEAD design doc</t>
         </is>
       </c>
       <c r="F210" s="5" t="inlineStr">
@@ -12265,7 +12273,7 @@
       </c>
       <c r="G210" s="5" t="inlineStr">
         <is>
-          <t>4 detector tests pass — fired=True on choppy+RSI=25+EMA200, rejected on RSI=55/below-EMA200/trending</t>
+          <t>docs/strategy_pead.md — Bernard-Thomas 1989, all-regime catalyst sleeve</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr"/>
@@ -12294,7 +12302,7 @@
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>PEAD-1</t>
+          <t>PEAD-2</t>
         </is>
       </c>
       <c r="C211" s="10" t="inlineStr">
@@ -12309,7 +12317,7 @@
       </c>
       <c r="E211" s="6" t="inlineStr">
         <is>
-          <t>PEAD design doc</t>
+          <t>PEAD config</t>
         </is>
       </c>
       <c r="F211" s="5" t="inlineStr">
@@ -12319,7 +12327,7 @@
       </c>
       <c r="G211" s="5" t="inlineStr">
         <is>
-          <t>docs/strategy_pead.md — Bernard-Thomas 1989, all-regime catalyst sleeve</t>
+          <t>Day1-3 post-earnings, EPS+5/Rev+2/Gap+3/Revisions&gt;=2, full Kelly with regime caps</t>
         </is>
       </c>
       <c r="H211" s="2" t="inlineStr"/>
@@ -12348,7 +12356,7 @@
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>PEAD-2</t>
+          <t>PEAD-3</t>
         </is>
       </c>
       <c r="C212" s="10" t="inlineStr">
@@ -12363,7 +12371,7 @@
       </c>
       <c r="E212" s="6" t="inlineStr">
         <is>
-          <t>PEAD config</t>
+          <t>PEAD detector</t>
         </is>
       </c>
       <c r="F212" s="5" t="inlineStr">
@@ -12373,7 +12381,7 @@
       </c>
       <c r="G212" s="5" t="inlineStr">
         <is>
-          <t>Day1-3 post-earnings, EPS+5/Rev+2/Gap+3/Revisions&gt;=2, full Kelly with regime caps</t>
+          <t>_detect_pead — 7-gate audit; regime-independent</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr"/>
@@ -12402,7 +12410,7 @@
       </c>
       <c r="B213" s="3" t="inlineStr">
         <is>
-          <t>PEAD-3</t>
+          <t>PEAD-4</t>
         </is>
       </c>
       <c r="C213" s="10" t="inlineStr">
@@ -12417,7 +12425,7 @@
       </c>
       <c r="E213" s="6" t="inlineStr">
         <is>
-          <t>PEAD detector</t>
+          <t>PEAD wiring</t>
         </is>
       </c>
       <c r="F213" s="5" t="inlineStr">
@@ -12427,7 +12435,7 @@
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>_detect_pead — 7-gate audit; regime-independent</t>
+          <t>Setup family override + plan (1.0 ATR stop, +5/+10/+15 targets, 10-30d drift hold)</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr"/>
@@ -12456,7 +12464,7 @@
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>PEAD-4</t>
+          <t>PEAD-5</t>
         </is>
       </c>
       <c r="C214" s="10" t="inlineStr">
@@ -12471,7 +12479,7 @@
       </c>
       <c r="E214" s="6" t="inlineStr">
         <is>
-          <t>PEAD wiring</t>
+          <t>PEAD bypasses</t>
         </is>
       </c>
       <c r="F214" s="5" t="inlineStr">
@@ -12481,7 +12489,7 @@
       </c>
       <c r="G214" s="5" t="inlineStr">
         <is>
-          <t>Setup family override + plan (1.0 ATR stop, +5/+10/+15 targets, 10-30d drift hold)</t>
+          <t>regime_gate bypassed (catalyst regime-independent), entry_quality bypassed (gap-up IS trigger)</t>
         </is>
       </c>
       <c r="H214" s="2" t="inlineStr"/>
@@ -12510,7 +12518,7 @@
       </c>
       <c r="B215" s="3" t="inlineStr">
         <is>
-          <t>PEAD-5</t>
+          <t>PEAD-6</t>
         </is>
       </c>
       <c r="C215" s="10" t="inlineStr">
@@ -12525,7 +12533,7 @@
       </c>
       <c r="E215" s="6" t="inlineStr">
         <is>
-          <t>PEAD bypasses</t>
+          <t>PEAD smoke test</t>
         </is>
       </c>
       <c r="F215" s="5" t="inlineStr">
@@ -12535,7 +12543,7 @@
       </c>
       <c r="G215" s="5" t="inlineStr">
         <is>
-          <t>regime_gate bypassed (catalyst regime-independent), entry_quality bypassed (gap-up IS trigger)</t>
+          <t>Perfect-setup test fires with all 7 audit checks ✓</t>
         </is>
       </c>
       <c r="H215" s="2" t="inlineStr"/>
@@ -12564,7 +12572,7 @@
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>PEAD-6</t>
+          <t>CLEANUP-HOT-SECTORS</t>
         </is>
       </c>
       <c r="C216" s="10" t="inlineStr">
@@ -12574,22 +12582,22 @@
       </c>
       <c r="D216" s="5" t="inlineStr">
         <is>
-          <t>Choice C Strategy</t>
+          <t>Code Hygiene / Signal Scanner</t>
         </is>
       </c>
       <c r="E216" s="6" t="inlineStr">
         <is>
-          <t>PEAD smoke test</t>
+          <t>Remove dead panelHotSectors function</t>
         </is>
       </c>
       <c r="F216" s="5" t="inlineStr">
         <is>
-          <t>Sleeve build</t>
+          <t>User asked to remove Hot Sectors panel from grid earlier; function left in file as dead code. Removed 53 lines.</t>
         </is>
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>Perfect-setup test fires with all 7 audit checks ✓</t>
+          <t>kairos.html QuantScanner module · panelHotSectors() deleted</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr"/>
@@ -12602,23 +12610,23 @@
       </c>
       <c r="L216" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="M216" s="3" t="inlineStr">
         <is>
-          <t>d0c6c4e04</t>
+          <t>e48edac16</t>
         </is>
       </c>
       <c r="N216" s="8" t="inlineStr"/>
     </row>
-    <row r="217" ht="45" customHeight="1">
+    <row r="217" ht="105" customHeight="1">
       <c r="A217" s="2" t="n">
         <v>216</v>
       </c>
       <c r="B217" s="3" t="inlineStr">
         <is>
-          <t>CLEANUP-HOT-SECTORS</t>
+          <t>UI-CRYPTO-1</t>
         </is>
       </c>
       <c r="C217" s="10" t="inlineStr">
@@ -12628,22 +12636,22 @@
       </c>
       <c r="D217" s="5" t="inlineStr">
         <is>
-          <t>Code Hygiene / Signal Scanner</t>
+          <t>Crypto Tab</t>
         </is>
       </c>
       <c r="E217" s="6" t="inlineStr">
         <is>
-          <t>Remove dead panelHotSectors function</t>
+          <t>20yr HF analyst Crypto tab rebuild</t>
         </is>
       </c>
       <c r="F217" s="5" t="inlineStr">
         <is>
-          <t>User asked to remove Hot Sectors panel from grid earlier; function left in file as dead code. Removed 53 lines.</t>
+          <t>Crypto tab was stub with 4 cards of placeholder data. Needed a senior HF/Graham-Buffett/swing-trader fused lens for the 24/7 risk-asset bellwether.</t>
         </is>
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>kairos.html QuantScanner module · panelHotSectors() deleted</t>
+          <t>13-section renderCrypto in kairos.html: cycle posture banner (Pi-Cycle/MVRV-Z/NUPL/200wk MA), spot KPIs, Graham margin-of-safety floors (realized price, thermo-cap, cost of production, LTH/STH cost), ETH owner-earnings DCF, BTC hard-money compounding, stablecoin liquidity, macro drivers, spot ETF flows, derivatives tape, on-chain valuation composite, catalyst calendar, adjacent equities, L1/L2 rotation, regime-conditional playbook, pre-mortem.</t>
         </is>
       </c>
       <c r="H217" s="2" t="inlineStr"/>
@@ -12661,18 +12669,18 @@
       </c>
       <c r="M217" s="3" t="inlineStr">
         <is>
-          <t>e48edac16</t>
+          <t>696731a4d</t>
         </is>
       </c>
       <c r="N217" s="8" t="inlineStr"/>
     </row>
-    <row r="218" ht="105" customHeight="1">
+    <row r="218" ht="75" customHeight="1">
       <c r="A218" s="2" t="n">
         <v>217</v>
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>UI-CRYPTO-1</t>
+          <t>EODHD-EDGAR-FUNDAMENTALS</t>
         </is>
       </c>
       <c r="C218" s="10" t="inlineStr">
@@ -12682,22 +12690,22 @@
       </c>
       <c r="D218" s="5" t="inlineStr">
         <is>
-          <t>Crypto Tab</t>
+          <t>Data / SEC EDGAR (future quality)</t>
         </is>
       </c>
       <c r="E218" s="6" t="inlineStr">
         <is>
-          <t>20yr HF analyst Crypto tab rebuild</t>
+          <t>Offload fundamentals to SEC EDGAR (FIX 4)</t>
         </is>
       </c>
       <c r="F218" s="5" t="inlineStr">
         <is>
-          <t>Crypto tab was stub with 4 cards of placeholder data. Needed a senior HF/Graham-Buffett/swing-trader fused lens for the 24/7 risk-asset bellwether.</t>
+          <t>new edgar_client.py behind data_fetcher interface; data.sec.gov companyfacts (User-Agent + &lt;=10 req/s); map XBRL tags to fundamentals.db; nightly batch. Quality upgrade (point-in-time, fixes audit #1/#4) + zeroes per-ticker EODHD fundamentals calls.</t>
         </is>
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>13-section renderCrypto in kairos.html: cycle posture banner (Pi-Cycle/MVRV-Z/NUPL/200wk MA), spot KPIs, Graham margin-of-safety floors (realized price, thermo-cap, cost of production, LTH/STH cost), ETH owner-earnings DCF, BTC hard-money compounding, stablecoin liquidity, macro drivers, spot ETF flows, derivatives tape, on-chain valuation composite, catalyst calendar, adjacent equities, L1/L2 rotation, regime-conditional playbook, pre-mortem.</t>
+          <t>edgar_client.py + nightly batch</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr"/>
@@ -12710,12 +12718,12 @@
       </c>
       <c r="L218" s="2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="M218" s="3" t="inlineStr">
         <is>
-          <t>696731a4d</t>
+          <t>5d05268ef</t>
         </is>
       </c>
       <c r="N218" s="8" t="inlineStr"/>
@@ -12726,7 +12734,7 @@
       </c>
       <c r="B219" s="3" t="inlineStr">
         <is>
-          <t>EODHD-EDGAR-FUNDAMENTALS</t>
+          <t>ENTRY-QUAL-REASON-1</t>
         </is>
       </c>
       <c r="C219" s="10" t="inlineStr">
@@ -12736,22 +12744,22 @@
       </c>
       <c r="D219" s="5" t="inlineStr">
         <is>
-          <t>Data / SEC EDGAR (future quality)</t>
+          <t>Decision Engine</t>
         </is>
       </c>
       <c r="E219" s="6" t="inlineStr">
         <is>
-          <t>Offload fundamentals to SEC EDGAR (FIX 4)</t>
+          <t>Misleading entry_quality WATCH reason</t>
         </is>
       </c>
       <c r="F219" s="5" t="inlineStr">
         <is>
-          <t>new edgar_client.py behind data_fetcher interface; data.sec.gov companyfacts (User-Agent + &lt;=10 req/s); map XBRL tags to fundamentals.db; nightly batch. Quality upgrade (point-in-time, fixes audit #1/#4) + zeroes per-ticker EODHD fundamentals calls.</t>
+          <t>make_decision hardcoded 'broke through resistance, wait for next base' for ALL MISSED entries — false when stock is below recent high (BFH: MISSED via &gt;2 ATR over EMA21 but 2.1% BELOW 20d high)</t>
         </is>
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>edgar_client.py + nightly batch</t>
+          <t>classify_entry_quality_detail() returns (label, live-distance reason) naming the actual trigger + honest 'still X% below resistance (not a breakout)' qualifier; threaded entry_quality_reason through make_decision + compute_decisions_by_mode</t>
         </is>
       </c>
       <c r="H219" s="2" t="inlineStr"/>
@@ -12764,12 +12772,12 @@
       </c>
       <c r="L219" s="2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="M219" s="3" t="inlineStr">
         <is>
-          <t>5d05268ef</t>
+          <t>613f10e35</t>
         </is>
       </c>
       <c r="N219" s="8" t="inlineStr"/>
@@ -15987,10 +15995,10 @@
         <v>20</v>
       </c>
       <c r="D2" s="18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E2" s="18" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3">
@@ -16025,10 +16033,10 @@
         <v>78</v>
       </c>
       <c r="D4" s="18" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5">
